--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P180"/>
+  <dimension ref="A1:R180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -429,16 +429,18 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="39" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="39" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,50 +476,60 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Ultimo post Facebook</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Ultimo post Instagram</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Ultima revisione Google</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Ultima revisione The Fork</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Ultima revisione Tripadvisor</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Orari apertura</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Orari chiusura</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Social attivo?</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Menzioni notizie</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Note aggiuntive</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Data verifica</t>
         </is>
@@ -554,52 +566,52 @@
           <t>chef-andrea-larossa</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026.0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Pranzo e cena</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Dom sera; Lun e Mar</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Si (Michelin 2026 1 stella)</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026.</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -636,52 +648,52 @@
           <t>chiodilatininewfood</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Gen 2026</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026.0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Pranzo e cena</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Dom e Lun</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Si (Morsi Magazine gen 2026)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Cucina plant-based.</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -718,32 +730,32 @@
           <t>cannavacciuolobistrotorino</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026. Chef Gabriele Bertoli.</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -780,32 +792,32 @@
           <t>ristorantecondividere</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1 stella Michelin 2026. Chef Federico Zanasi.</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -842,32 +854,32 @@
           <t>lapistarestaurant</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Confermato sulla guida 2026. Ristorante panoramico.</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -904,32 +916,32 @@
           <t>opera_torino</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Confermato sulla guida 2026.</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -961,32 +973,32 @@
           <t>ristorante_santommaso10</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>Guida Michelin 2026</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Confermato sulla guida 2026.</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>16/04/2026</t>
         </is>
@@ -1011,24 +1023,26 @@
       <c r="D9" s="1" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="inlineStr"/>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
-      <c r="I9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr"/>
-      <c r="O9" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P9" s="1" t="inlineStr">
+      <c r="O9" s="1" t="inlineStr"/>
+      <c r="P9" s="1" t="inlineStr"/>
+      <c r="Q9" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R9" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1060,52 +1074,52 @@
           <t>ballatoiobistrot</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2025.0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>12:30/19:30</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Dom sera; Lun</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Si (Moondo, BCool Guide)</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Bistrot piemontese in centro.</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -1142,24 +1156,26 @@
           <t>betweenristorante</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
-      <c r="I11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr"/>
-      <c r="O11" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P11" s="1" t="inlineStr">
+      <c r="O11" s="1" t="inlineStr"/>
+      <c r="P11" s="1" t="inlineStr"/>
+      <c r="Q11" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R11" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1184,24 +1200,26 @@
       <c r="D12" s="1" t="inlineStr"/>
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr"/>
-      <c r="I12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr"/>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P12" s="1" t="inlineStr">
+      <c r="O12" s="1" t="inlineStr"/>
+      <c r="P12" s="1" t="inlineStr"/>
+      <c r="Q12" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R12" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1223,32 +1241,32 @@
           <t>011/5096561</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Confermato aperto (recensioni nov 2025, sito attivo)</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>17/04/2026</t>
         </is>
@@ -1285,24 +1303,26 @@
           <t>contesto_alimentare</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
-      <c r="I14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr"/>
-      <c r="O14" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P14" s="1" t="inlineStr">
+      <c r="O14" s="1" t="inlineStr"/>
+      <c r="P14" s="1" t="inlineStr"/>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R14" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1339,24 +1359,26 @@
           <t>cubiquetorino</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
-      <c r="I15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr"/>
-      <c r="O15" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P15" s="1" t="inlineStr">
+      <c r="O15" s="1" t="inlineStr"/>
+      <c r="P15" s="1" t="inlineStr"/>
+      <c r="Q15" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R15" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1393,24 +1415,26 @@
           <t>gaudenziovinoecucina</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
-      <c r="I16" s="1" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr"/>
-      <c r="O16" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P16" s="1" t="inlineStr">
+      <c r="O16" s="1" t="inlineStr"/>
+      <c r="P16" s="1" t="inlineStr"/>
+      <c r="Q16" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R16" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1447,24 +1471,26 @@
           <t>Ildepositobistrot</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
-      <c r="I17" s="1" t="inlineStr"/>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr"/>
-      <c r="O17" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P17" s="1" t="inlineStr">
+      <c r="O17" s="1" t="inlineStr"/>
+      <c r="P17" s="1" t="inlineStr"/>
+      <c r="Q17" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R17" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1501,24 +1527,26 @@
           <t>ristoranteinsieme</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
-      <c r="I18" s="1" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr"/>
-      <c r="O18" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P18" s="1" t="inlineStr">
+      <c r="O18" s="1" t="inlineStr"/>
+      <c r="P18" s="1" t="inlineStr"/>
+      <c r="Q18" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R18" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1555,24 +1583,26 @@
           <t>la_limonaia_</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
-      <c r="I19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J19" s="1" t="inlineStr"/>
       <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr"/>
-      <c r="O19" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P19" s="1" t="inlineStr">
+      <c r="O19" s="1" t="inlineStr"/>
+      <c r="P19" s="1" t="inlineStr"/>
+      <c r="Q19" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R19" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1609,24 +1639,26 @@
           <t>trattoria.la_madia</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr"/>
-      <c r="O20" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P20" s="1" t="inlineStr">
+      <c r="O20" s="1" t="inlineStr"/>
+      <c r="P20" s="1" t="inlineStr"/>
+      <c r="Q20" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R20" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1663,24 +1695,26 @@
           <t>magazzino52</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr"/>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P21" s="1" t="inlineStr">
+      <c r="O21" s="1" t="inlineStr"/>
+      <c r="P21" s="1" t="inlineStr"/>
+      <c r="Q21" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R21" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1705,24 +1739,26 @@
       <c r="D22" s="1" t="inlineStr"/>
       <c r="E22" s="1" t="inlineStr"/>
       <c r="F22" s="1" t="inlineStr"/>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr"/>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr"/>
-      <c r="O22" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P22" s="1" t="inlineStr">
+      <c r="O22" s="1" t="inlineStr"/>
+      <c r="P22" s="1" t="inlineStr"/>
+      <c r="Q22" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R22" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1759,24 +1795,26 @@
           <t>raffaleo_ristorante_enoteca</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr"/>
-      <c r="I23" s="1" t="inlineStr"/>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr"/>
-      <c r="O23" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P23" s="1" t="inlineStr">
+      <c r="O23" s="1" t="inlineStr"/>
+      <c r="P23" s="1" t="inlineStr"/>
+      <c r="Q23" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R23" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1809,24 +1847,26 @@
           <t>razzo__</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G24" s="1" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr"/>
-      <c r="I24" s="1" t="inlineStr"/>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr"/>
-      <c r="O24" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P24" s="1" t="inlineStr">
+      <c r="O24" s="1" t="inlineStr"/>
+      <c r="P24" s="1" t="inlineStr"/>
+      <c r="Q24" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R24" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1863,24 +1903,26 @@
           <t>costardibros</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G25" s="1" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr"/>
-      <c r="I25" s="1" t="inlineStr"/>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr"/>
-      <c r="O25" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P25" s="1" t="inlineStr">
+      <c r="O25" s="1" t="inlineStr"/>
+      <c r="P25" s="1" t="inlineStr"/>
+      <c r="Q25" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R25" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1913,24 +1955,26 @@
           <t>siloscucinasincera</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G26" s="1" t="inlineStr"/>
       <c r="H26" s="1" t="inlineStr"/>
-      <c r="I26" s="1" t="inlineStr"/>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr"/>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P26" s="1" t="inlineStr">
+      <c r="O26" s="1" t="inlineStr"/>
+      <c r="P26" s="1" t="inlineStr"/>
+      <c r="Q26" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R26" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1955,24 +1999,26 @@
       <c r="D27" s="1" t="inlineStr"/>
       <c r="E27" s="1" t="inlineStr"/>
       <c r="F27" s="1" t="inlineStr"/>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G27" s="1" t="inlineStr"/>
       <c r="H27" s="1" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr"/>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J27" s="1" t="inlineStr"/>
       <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr"/>
-      <c r="O27" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P27" s="1" t="inlineStr">
+      <c r="O27" s="1" t="inlineStr"/>
+      <c r="P27" s="1" t="inlineStr"/>
+      <c r="Q27" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R27" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -1997,24 +2043,26 @@
       <c r="D28" s="1" t="inlineStr"/>
       <c r="E28" s="1" t="inlineStr"/>
       <c r="F28" s="1" t="inlineStr"/>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G28" s="1" t="inlineStr"/>
       <c r="H28" s="1" t="inlineStr"/>
-      <c r="I28" s="1" t="inlineStr"/>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J28" s="1" t="inlineStr"/>
       <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr"/>
-      <c r="O28" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P28" s="1" t="inlineStr">
+      <c r="O28" s="1" t="inlineStr"/>
+      <c r="P28" s="1" t="inlineStr"/>
+      <c r="Q28" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R28" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2051,24 +2099,26 @@
           <t>tuorloristorante</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G29" s="1" t="inlineStr"/>
       <c r="H29" s="1" t="inlineStr"/>
-      <c r="I29" s="1" t="inlineStr"/>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J29" s="1" t="inlineStr"/>
       <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr"/>
-      <c r="O29" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P29" s="1" t="inlineStr">
+      <c r="O29" s="1" t="inlineStr"/>
+      <c r="P29" s="1" t="inlineStr"/>
+      <c r="Q29" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R29" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2105,52 +2155,52 @@
           <t>aroma_ristorante</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>2026.0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>12:30/19:30</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Lun</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Si (Wheree Mar 2026)</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Cucina gourmet in Borgo Po.</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -2187,24 +2237,26 @@
           <t>ristoranteconsorzio</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G31" s="1" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr"/>
-      <c r="I31" s="1" t="inlineStr"/>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J31" s="1" t="inlineStr"/>
       <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr"/>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P31" s="1" t="inlineStr">
+      <c r="O31" s="1" t="inlineStr"/>
+      <c r="P31" s="1" t="inlineStr"/>
+      <c r="Q31" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R31" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2241,24 +2293,26 @@
           <t>cucina_rambaldi</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr"/>
-      <c r="I32" s="1" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J32" s="1" t="inlineStr"/>
       <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr"/>
-      <c r="O32" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P32" s="1" t="inlineStr">
+      <c r="O32" s="1" t="inlineStr"/>
+      <c r="P32" s="1" t="inlineStr"/>
+      <c r="Q32" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R32" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2283,24 +2337,26 @@
       <c r="D33" s="1" t="inlineStr"/>
       <c r="E33" s="1" t="inlineStr"/>
       <c r="F33" s="1" t="inlineStr"/>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr"/>
-      <c r="I33" s="1" t="inlineStr"/>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J33" s="1" t="inlineStr"/>
       <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr"/>
-      <c r="O33" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P33" s="1" t="inlineStr">
+      <c r="O33" s="1" t="inlineStr"/>
+      <c r="P33" s="1" t="inlineStr"/>
+      <c r="Q33" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R33" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2337,24 +2393,26 @@
           <t>feliceatestaccio</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
-      <c r="I34" s="1" t="inlineStr"/>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J34" s="1" t="inlineStr"/>
       <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P34" s="1" t="inlineStr">
+      <c r="O34" s="1" t="inlineStr"/>
+      <c r="P34" s="1" t="inlineStr"/>
+      <c r="Q34" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R34" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2391,24 +2449,26 @@
           <t>gousto_torino</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
-      <c r="I35" s="1" t="inlineStr"/>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J35" s="1" t="inlineStr"/>
       <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr"/>
-      <c r="O35" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P35" s="1" t="inlineStr">
+      <c r="O35" s="1" t="inlineStr"/>
+      <c r="P35" s="1" t="inlineStr"/>
+      <c r="Q35" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R35" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2433,24 +2493,26 @@
       <c r="D36" s="1" t="inlineStr"/>
       <c r="E36" s="1" t="inlineStr"/>
       <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="1" t="inlineStr"/>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J36" s="1" t="inlineStr"/>
       <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr"/>
-      <c r="O36" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P36" s="1" t="inlineStr">
+      <c r="O36" s="1" t="inlineStr"/>
+      <c r="P36" s="1" t="inlineStr"/>
+      <c r="Q36" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R36" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2475,24 +2537,26 @@
       <c r="D37" s="1" t="inlineStr"/>
       <c r="E37" s="1" t="inlineStr"/>
       <c r="F37" s="1" t="inlineStr"/>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr"/>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J37" s="1" t="inlineStr"/>
       <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P37" s="1" t="inlineStr">
+      <c r="O37" s="1" t="inlineStr"/>
+      <c r="P37" s="1" t="inlineStr"/>
+      <c r="Q37" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R37" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2517,24 +2581,26 @@
       <c r="D38" s="1" t="inlineStr"/>
       <c r="E38" s="1" t="inlineStr"/>
       <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr"/>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J38" s="1" t="inlineStr"/>
       <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P38" s="1" t="inlineStr">
+      <c r="O38" s="1" t="inlineStr"/>
+      <c r="P38" s="1" t="inlineStr"/>
+      <c r="Q38" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R38" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2559,24 +2625,26 @@
       <c r="D39" s="1" t="inlineStr"/>
       <c r="E39" s="1" t="inlineStr"/>
       <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr"/>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J39" s="1" t="inlineStr"/>
       <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P39" s="1" t="inlineStr">
+      <c r="O39" s="1" t="inlineStr"/>
+      <c r="P39" s="1" t="inlineStr"/>
+      <c r="Q39" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R39" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2601,24 +2669,26 @@
       <c r="D40" s="1" t="inlineStr"/>
       <c r="E40" s="1" t="inlineStr"/>
       <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr"/>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J40" s="1" t="inlineStr"/>
       <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P40" s="1" t="inlineStr">
+      <c r="O40" s="1" t="inlineStr"/>
+      <c r="P40" s="1" t="inlineStr"/>
+      <c r="Q40" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R40" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2655,24 +2725,26 @@
           <t>fanfaron_bistrot</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="1" t="inlineStr"/>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P41" s="1" t="inlineStr">
+      <c r="O41" s="1" t="inlineStr"/>
+      <c r="P41" s="1" t="inlineStr"/>
+      <c r="Q41" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R41" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2709,24 +2781,26 @@
           <t>lescodelle_torino</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
-      <c r="I42" s="1" t="inlineStr"/>
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J42" s="1" t="inlineStr"/>
       <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P42" s="1" t="inlineStr">
+      <c r="O42" s="1" t="inlineStr"/>
+      <c r="P42" s="1" t="inlineStr"/>
+      <c r="Q42" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R42" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2763,24 +2837,26 @@
           <t>le_vitel_etonne</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
-      <c r="I43" s="1" t="inlineStr"/>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J43" s="1" t="inlineStr"/>
       <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P43" s="1" t="inlineStr">
+      <c r="O43" s="1" t="inlineStr"/>
+      <c r="P43" s="1" t="inlineStr"/>
+      <c r="Q43" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R43" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2817,24 +2893,26 @@
           <t>madama_piola</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
-      <c r="I44" s="1" t="inlineStr"/>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J44" s="1" t="inlineStr"/>
       <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P44" s="1" t="inlineStr">
+      <c r="O44" s="1" t="inlineStr"/>
+      <c r="P44" s="1" t="inlineStr"/>
+      <c r="Q44" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R44" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2871,24 +2949,26 @@
           <t>andirivieniosteria</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr"/>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J45" s="1" t="inlineStr"/>
       <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P45" s="1" t="inlineStr">
+      <c r="O45" s="1" t="inlineStr"/>
+      <c r="P45" s="1" t="inlineStr"/>
+      <c r="Q45" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R45" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2925,24 +3005,26 @@
           <t>sangiorstorino</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr"/>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J46" s="1" t="inlineStr"/>
       <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P46" s="1" t="inlineStr">
+      <c r="O46" s="1" t="inlineStr"/>
+      <c r="P46" s="1" t="inlineStr"/>
+      <c r="Q46" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R46" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -2979,24 +3061,26 @@
           <t>Scannabuecaffe</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr"/>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J47" s="1" t="inlineStr"/>
       <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P47" s="1" t="inlineStr">
+      <c r="O47" s="1" t="inlineStr"/>
+      <c r="P47" s="1" t="inlineStr"/>
+      <c r="Q47" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R47" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3029,24 +3113,26 @@
           <t>smokingwinebar</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G48" s="1" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr"/>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J48" s="1" t="inlineStr"/>
       <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P48" s="1" t="inlineStr">
+      <c r="O48" s="1" t="inlineStr"/>
+      <c r="P48" s="1" t="inlineStr"/>
+      <c r="Q48" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R48" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3083,24 +3169,26 @@
           <t>trattoria_amicizia</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
-      <c r="I49" s="1" t="inlineStr"/>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J49" s="1" t="inlineStr"/>
       <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P49" s="1" t="inlineStr">
+      <c r="O49" s="1" t="inlineStr"/>
+      <c r="P49" s="1" t="inlineStr"/>
+      <c r="Q49" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R49" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3125,24 +3213,26 @@
       <c r="D50" s="1" t="inlineStr"/>
       <c r="E50" s="1" t="inlineStr"/>
       <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G50" s="1" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr"/>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J50" s="1" t="inlineStr"/>
       <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P50" s="1" t="inlineStr">
+      <c r="O50" s="1" t="inlineStr"/>
+      <c r="P50" s="1" t="inlineStr"/>
+      <c r="Q50" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R50" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3167,24 +3257,26 @@
       <c r="D51" s="1" t="inlineStr"/>
       <c r="E51" s="1" t="inlineStr"/>
       <c r="F51" s="1" t="inlineStr"/>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G51" s="1" t="inlineStr"/>
       <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J51" s="1" t="inlineStr"/>
       <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr"/>
-      <c r="O51" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P51" s="1" t="inlineStr">
+      <c r="O51" s="1" t="inlineStr"/>
+      <c r="P51" s="1" t="inlineStr"/>
+      <c r="Q51" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R51" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3209,24 +3301,26 @@
       <c r="D52" s="1" t="inlineStr"/>
       <c r="E52" s="1" t="inlineStr"/>
       <c r="F52" s="1" t="inlineStr"/>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G52" s="1" t="inlineStr"/>
       <c r="H52" s="1" t="inlineStr"/>
-      <c r="I52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J52" s="1" t="inlineStr"/>
       <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr"/>
-      <c r="O52" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P52" s="1" t="inlineStr">
+      <c r="O52" s="1" t="inlineStr"/>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R52" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3263,24 +3357,26 @@
           <t>parlapatorino</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G53" s="1" t="inlineStr"/>
       <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J53" s="1" t="inlineStr"/>
       <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr"/>
-      <c r="O53" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P53" s="1" t="inlineStr">
+      <c r="O53" s="1" t="inlineStr"/>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R53" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3307,52 +3403,52 @@
           <t>osteriaantichesere</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>2026.0</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>19:00-22:30</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Dom; pranzo</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>Si (Michelin 2026 Bib Gourmand, Yelp Mar 2026)</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Famiglia Rota dal 1990.</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -3377,24 +3473,26 @@
       <c r="D55" s="1" t="inlineStr"/>
       <c r="E55" s="1" t="inlineStr"/>
       <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G55" s="1" t="inlineStr"/>
       <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr"/>
+      <c r="I55" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J55" s="1" t="inlineStr"/>
       <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr"/>
-      <c r="O55" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P55" s="1" t="inlineStr">
+      <c r="O55" s="1" t="inlineStr"/>
+      <c r="P55" s="1" t="inlineStr"/>
+      <c r="Q55" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R55" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3419,24 +3517,26 @@
       <c r="D56" s="1" t="inlineStr"/>
       <c r="E56" s="1" t="inlineStr"/>
       <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G56" s="1" t="inlineStr"/>
       <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr"/>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J56" s="1" t="inlineStr"/>
       <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr"/>
-      <c r="O56" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P56" s="1" t="inlineStr">
+      <c r="O56" s="1" t="inlineStr"/>
+      <c r="P56" s="1" t="inlineStr"/>
+      <c r="Q56" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R56" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3461,24 +3561,26 @@
       <c r="D57" s="1" t="inlineStr"/>
       <c r="E57" s="1" t="inlineStr"/>
       <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G57" s="1" t="inlineStr"/>
       <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr"/>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J57" s="1" t="inlineStr"/>
       <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr"/>
-      <c r="O57" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P57" s="1" t="inlineStr">
+      <c r="O57" s="1" t="inlineStr"/>
+      <c r="P57" s="1" t="inlineStr"/>
+      <c r="Q57" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R57" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3515,24 +3617,26 @@
           <t>ducesari</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G58" s="1" t="inlineStr"/>
       <c r="H58" s="1" t="inlineStr"/>
-      <c r="I58" s="1" t="inlineStr"/>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J58" s="1" t="inlineStr"/>
       <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr"/>
-      <c r="O58" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P58" s="1" t="inlineStr">
+      <c r="O58" s="1" t="inlineStr"/>
+      <c r="P58" s="1" t="inlineStr"/>
+      <c r="Q58" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R58" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3569,24 +3673,26 @@
           <t>fratellibruzzone</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G59" s="1" t="inlineStr"/>
       <c r="H59" s="1" t="inlineStr"/>
-      <c r="I59" s="1" t="inlineStr"/>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J59" s="1" t="inlineStr"/>
       <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr"/>
-      <c r="O59" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P59" s="1" t="inlineStr">
+      <c r="O59" s="1" t="inlineStr"/>
+      <c r="P59" s="1" t="inlineStr"/>
+      <c r="Q59" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R59" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3611,24 +3717,26 @@
       <c r="D60" s="1" t="inlineStr"/>
       <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G60" s="1" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr"/>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J60" s="1" t="inlineStr"/>
       <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr"/>
-      <c r="O60" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P60" s="1" t="inlineStr">
+      <c r="O60" s="1" t="inlineStr"/>
+      <c r="P60" s="1" t="inlineStr"/>
+      <c r="Q60" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R60" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3665,24 +3773,26 @@
           <t>le_ramine</t>
         </is>
       </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G61" s="1" t="inlineStr"/>
       <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr"/>
+      <c r="I61" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J61" s="1" t="inlineStr"/>
       <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr"/>
-      <c r="O61" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P61" s="1" t="inlineStr">
+      <c r="O61" s="1" t="inlineStr"/>
+      <c r="P61" s="1" t="inlineStr"/>
+      <c r="Q61" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R61" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3707,24 +3817,26 @@
       <c r="D62" s="1" t="inlineStr"/>
       <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="inlineStr"/>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G62" s="1" t="inlineStr"/>
       <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="1" t="inlineStr"/>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J62" s="1" t="inlineStr"/>
       <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr"/>
-      <c r="O62" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P62" s="1" t="inlineStr">
+      <c r="O62" s="1" t="inlineStr"/>
+      <c r="P62" s="1" t="inlineStr"/>
+      <c r="Q62" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R62" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3761,24 +3873,26 @@
           <t>osteria_nuova_torino</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G63" s="1" t="inlineStr"/>
       <c r="H63" s="1" t="inlineStr"/>
-      <c r="I63" s="1" t="inlineStr"/>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J63" s="1" t="inlineStr"/>
       <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr"/>
-      <c r="O63" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P63" s="1" t="inlineStr">
+      <c r="O63" s="1" t="inlineStr"/>
+      <c r="P63" s="1" t="inlineStr"/>
+      <c r="Q63" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R63" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3803,24 +3917,26 @@
       <c r="D64" s="1" t="inlineStr"/>
       <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="inlineStr"/>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G64" s="1" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr"/>
-      <c r="I64" s="1" t="inlineStr"/>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J64" s="1" t="inlineStr"/>
       <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr"/>
-      <c r="O64" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P64" s="1" t="inlineStr">
+      <c r="O64" s="1" t="inlineStr"/>
+      <c r="P64" s="1" t="inlineStr"/>
+      <c r="Q64" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R64" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3853,24 +3969,26 @@
           <t>hostariasenzapretese</t>
         </is>
       </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G65" s="1" t="inlineStr"/>
       <c r="H65" s="1" t="inlineStr"/>
-      <c r="I65" s="1" t="inlineStr"/>
+      <c r="I65" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J65" s="1" t="inlineStr"/>
       <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr"/>
-      <c r="O65" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P65" s="1" t="inlineStr">
+      <c r="O65" s="1" t="inlineStr"/>
+      <c r="P65" s="1" t="inlineStr"/>
+      <c r="Q65" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R65" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3895,24 +4013,26 @@
       <c r="D66" s="1" t="inlineStr"/>
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="inlineStr"/>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G66" s="1" t="inlineStr"/>
       <c r="H66" s="1" t="inlineStr"/>
-      <c r="I66" s="1" t="inlineStr"/>
+      <c r="I66" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J66" s="1" t="inlineStr"/>
       <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr"/>
-      <c r="O66" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P66" s="1" t="inlineStr">
+      <c r="O66" s="1" t="inlineStr"/>
+      <c r="P66" s="1" t="inlineStr"/>
+      <c r="Q66" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R66" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3937,24 +4057,26 @@
       <c r="D67" s="1" t="inlineStr"/>
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="inlineStr"/>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G67" s="1" t="inlineStr"/>
       <c r="H67" s="1" t="inlineStr"/>
-      <c r="I67" s="1" t="inlineStr"/>
+      <c r="I67" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J67" s="1" t="inlineStr"/>
       <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr"/>
-      <c r="O67" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P67" s="1" t="inlineStr">
+      <c r="O67" s="1" t="inlineStr"/>
+      <c r="P67" s="1" t="inlineStr"/>
+      <c r="Q67" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R67" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -3991,52 +4113,52 @@
           <t>azotea_to</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>2026.0</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>19:00-01:00</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>Dom</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>Si (Michelin 2026)</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>Cucina nikkei. Michelin 2026.</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -4061,24 +4183,26 @@
       <c r="D69" s="1" t="inlineStr"/>
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="inlineStr"/>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G69" s="1" t="inlineStr"/>
       <c r="H69" s="1" t="inlineStr"/>
-      <c r="I69" s="1" t="inlineStr"/>
+      <c r="I69" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J69" s="1" t="inlineStr"/>
       <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr"/>
-      <c r="O69" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P69" s="1" t="inlineStr">
+      <c r="O69" s="1" t="inlineStr"/>
+      <c r="P69" s="1" t="inlineStr"/>
+      <c r="Q69" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R69" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4115,24 +4239,26 @@
           <t>donburihouse_</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G70" s="1" t="inlineStr"/>
       <c r="H70" s="1" t="inlineStr"/>
-      <c r="I70" s="1" t="inlineStr"/>
+      <c r="I70" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J70" s="1" t="inlineStr"/>
       <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr"/>
-      <c r="O70" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P70" s="1" t="inlineStr">
+      <c r="O70" s="1" t="inlineStr"/>
+      <c r="P70" s="1" t="inlineStr"/>
+      <c r="Q70" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R70" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4169,24 +4295,26 @@
           <t>elbeso_torino</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G71" s="1" t="inlineStr"/>
       <c r="H71" s="1" t="inlineStr"/>
-      <c r="I71" s="1" t="inlineStr"/>
+      <c r="I71" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J71" s="1" t="inlineStr"/>
       <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr"/>
-      <c r="O71" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P71" s="1" t="inlineStr">
+      <c r="O71" s="1" t="inlineStr"/>
+      <c r="P71" s="1" t="inlineStr"/>
+      <c r="Q71" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R71" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4215,24 +4343,26 @@
           <t>kadeh.torino</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G72" s="1" t="inlineStr"/>
       <c r="H72" s="1" t="inlineStr"/>
-      <c r="I72" s="1" t="inlineStr"/>
+      <c r="I72" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J72" s="1" t="inlineStr"/>
       <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr"/>
-      <c r="O72" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P72" s="1" t="inlineStr">
+      <c r="O72" s="1" t="inlineStr"/>
+      <c r="P72" s="1" t="inlineStr"/>
+      <c r="Q72" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R72" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4269,24 +4399,26 @@
           <t>Kayessenzaperuviana</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G73" s="1" t="inlineStr"/>
       <c r="H73" s="1" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr"/>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J73" s="1" t="inlineStr"/>
       <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr"/>
-      <c r="O73" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P73" s="1" t="inlineStr">
+      <c r="O73" s="1" t="inlineStr"/>
+      <c r="P73" s="1" t="inlineStr"/>
+      <c r="Q73" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R73" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4315,24 +4447,26 @@
           <t>lao.torino</t>
         </is>
       </c>
-      <c r="G74" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G74" s="1" t="inlineStr"/>
       <c r="H74" s="1" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr"/>
+      <c r="I74" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J74" s="1" t="inlineStr"/>
       <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr"/>
-      <c r="O74" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P74" s="1" t="inlineStr">
+      <c r="O74" s="1" t="inlineStr"/>
+      <c r="P74" s="1" t="inlineStr"/>
+      <c r="Q74" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R74" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4365,24 +4499,26 @@
           <t>lostranierotorino</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G75" s="1" t="inlineStr"/>
       <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr"/>
+      <c r="I75" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J75" s="1" t="inlineStr"/>
       <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr"/>
-      <c r="O75" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P75" s="1" t="inlineStr">
+      <c r="O75" s="1" t="inlineStr"/>
+      <c r="P75" s="1" t="inlineStr"/>
+      <c r="Q75" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R75" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4419,24 +4555,26 @@
           <t>tuttofabrodo_official</t>
         </is>
       </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G76" s="1" t="inlineStr"/>
       <c r="H76" s="1" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr"/>
+      <c r="I76" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J76" s="1" t="inlineStr"/>
       <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr"/>
-      <c r="O76" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P76" s="1" t="inlineStr">
+      <c r="O76" s="1" t="inlineStr"/>
+      <c r="P76" s="1" t="inlineStr"/>
+      <c r="Q76" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R76" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4473,24 +4611,26 @@
           <t>ristorante.valeunperu</t>
         </is>
       </c>
-      <c r="G77" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G77" s="1" t="inlineStr"/>
       <c r="H77" s="1" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr"/>
+      <c r="I77" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J77" s="1" t="inlineStr"/>
       <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr"/>
-      <c r="O77" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P77" s="1" t="inlineStr">
+      <c r="O77" s="1" t="inlineStr"/>
+      <c r="P77" s="1" t="inlineStr"/>
+      <c r="Q77" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R77" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4515,24 +4655,26 @@
       <c r="D78" s="1" t="inlineStr"/>
       <c r="E78" s="1" t="inlineStr"/>
       <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G78" s="1" t="inlineStr"/>
       <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr"/>
+      <c r="I78" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J78" s="1" t="inlineStr"/>
       <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr"/>
-      <c r="O78" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P78" s="1" t="inlineStr">
+      <c r="O78" s="1" t="inlineStr"/>
+      <c r="P78" s="1" t="inlineStr"/>
+      <c r="Q78" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R78" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4561,24 +4703,26 @@
           <t>ristorante_wasabi_torino</t>
         </is>
       </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G79" s="1" t="inlineStr"/>
       <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr"/>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J79" s="1" t="inlineStr"/>
       <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr"/>
-      <c r="O79" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P79" s="1" t="inlineStr">
+      <c r="O79" s="1" t="inlineStr"/>
+      <c r="P79" s="1" t="inlineStr"/>
+      <c r="Q79" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R79" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4615,24 +4759,26 @@
           <t>ristorante_zheng_yang_torino</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G80" s="1" t="inlineStr"/>
       <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr"/>
+      <c r="I80" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J80" s="1" t="inlineStr"/>
       <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr"/>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
+      <c r="O80" s="1" t="inlineStr"/>
+      <c r="P80" s="1" t="inlineStr"/>
+      <c r="Q80" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R80" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4657,24 +4803,26 @@
       <c r="D81" s="1" t="inlineStr"/>
       <c r="E81" s="1" t="inlineStr"/>
       <c r="F81" s="1" t="inlineStr"/>
-      <c r="G81" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G81" s="1" t="inlineStr"/>
       <c r="H81" s="1" t="inlineStr"/>
-      <c r="I81" s="1" t="inlineStr"/>
+      <c r="I81" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J81" s="1" t="inlineStr"/>
       <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr"/>
-      <c r="O81" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P81" s="1" t="inlineStr">
+      <c r="O81" s="1" t="inlineStr"/>
+      <c r="P81" s="1" t="inlineStr"/>
+      <c r="Q81" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R81" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4707,24 +4855,26 @@
           <t>balikpizzeria</t>
         </is>
       </c>
-      <c r="G82" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G82" s="1" t="inlineStr"/>
       <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr"/>
+      <c r="I82" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J82" s="1" t="inlineStr"/>
       <c r="K82" s="1" t="inlineStr"/>
       <c r="L82" s="1" t="inlineStr"/>
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr"/>
-      <c r="O82" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P82" s="1" t="inlineStr">
+      <c r="O82" s="1" t="inlineStr"/>
+      <c r="P82" s="1" t="inlineStr"/>
+      <c r="Q82" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R82" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4761,24 +4911,26 @@
           <t>Berberepizzeria</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G83" s="1" t="inlineStr"/>
       <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr"/>
+      <c r="I83" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J83" s="1" t="inlineStr"/>
       <c r="K83" s="1" t="inlineStr"/>
       <c r="L83" s="1" t="inlineStr"/>
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr"/>
-      <c r="O83" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P83" s="1" t="inlineStr">
+      <c r="O83" s="1" t="inlineStr"/>
+      <c r="P83" s="1" t="inlineStr"/>
+      <c r="Q83" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R83" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4815,24 +4967,26 @@
           <t>_da_zero</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G84" s="1" t="inlineStr"/>
       <c r="H84" s="1" t="inlineStr"/>
-      <c r="I84" s="1" t="inlineStr"/>
+      <c r="I84" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J84" s="1" t="inlineStr"/>
       <c r="K84" s="1" t="inlineStr"/>
       <c r="L84" s="1" t="inlineStr"/>
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr"/>
-      <c r="O84" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P84" s="1" t="inlineStr">
+      <c r="O84" s="1" t="inlineStr"/>
+      <c r="P84" s="1" t="inlineStr"/>
+      <c r="Q84" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R84" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4857,24 +5011,26 @@
       <c r="D85" s="1" t="inlineStr"/>
       <c r="E85" s="1" t="inlineStr"/>
       <c r="F85" s="1" t="inlineStr"/>
-      <c r="G85" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G85" s="1" t="inlineStr"/>
       <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr"/>
+      <c r="I85" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J85" s="1" t="inlineStr"/>
       <c r="K85" s="1" t="inlineStr"/>
       <c r="L85" s="1" t="inlineStr"/>
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr"/>
-      <c r="O85" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P85" s="1" t="inlineStr">
+      <c r="O85" s="1" t="inlineStr"/>
+      <c r="P85" s="1" t="inlineStr"/>
+      <c r="Q85" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R85" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4911,24 +5067,26 @@
           <t>fuzion_torino</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G86" s="1" t="inlineStr"/>
       <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr"/>
+      <c r="I86" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J86" s="1" t="inlineStr"/>
       <c r="K86" s="1" t="inlineStr"/>
       <c r="L86" s="1" t="inlineStr"/>
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P86" s="1" t="inlineStr">
+      <c r="O86" s="1" t="inlineStr"/>
+      <c r="P86" s="1" t="inlineStr"/>
+      <c r="Q86" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R86" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -4953,24 +5111,26 @@
       <c r="D87" s="1" t="inlineStr"/>
       <c r="E87" s="1" t="inlineStr"/>
       <c r="F87" s="1" t="inlineStr"/>
-      <c r="G87" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G87" s="1" t="inlineStr"/>
       <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr"/>
+      <c r="I87" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J87" s="1" t="inlineStr"/>
       <c r="K87" s="1" t="inlineStr"/>
       <c r="L87" s="1" t="inlineStr"/>
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr"/>
-      <c r="O87" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P87" s="1" t="inlineStr">
+      <c r="O87" s="1" t="inlineStr"/>
+      <c r="P87" s="1" t="inlineStr"/>
+      <c r="Q87" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R87" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5003,24 +5163,26 @@
           <t>lasvolta_torino</t>
         </is>
       </c>
-      <c r="G88" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G88" s="1" t="inlineStr"/>
       <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr"/>
+      <c r="I88" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J88" s="1" t="inlineStr"/>
       <c r="K88" s="1" t="inlineStr"/>
       <c r="L88" s="1" t="inlineStr"/>
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr"/>
-      <c r="O88" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P88" s="1" t="inlineStr">
+      <c r="O88" s="1" t="inlineStr"/>
+      <c r="P88" s="1" t="inlineStr"/>
+      <c r="Q88" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R88" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5057,24 +5219,26 @@
           <t>aforisma_pizzeria_gourmet</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G89" s="1" t="inlineStr"/>
       <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr"/>
+      <c r="I89" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J89" s="1" t="inlineStr"/>
       <c r="K89" s="1" t="inlineStr"/>
       <c r="L89" s="1" t="inlineStr"/>
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr"/>
-      <c r="O89" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P89" s="1" t="inlineStr">
+      <c r="O89" s="1" t="inlineStr"/>
+      <c r="P89" s="1" t="inlineStr"/>
+      <c r="Q89" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R89" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5111,24 +5275,26 @@
           <t>sestogustotorino</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G90" s="1" t="inlineStr"/>
       <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr"/>
+      <c r="I90" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J90" s="1" t="inlineStr"/>
       <c r="K90" s="1" t="inlineStr"/>
       <c r="L90" s="1" t="inlineStr"/>
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr"/>
-      <c r="O90" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P90" s="1" t="inlineStr">
+      <c r="O90" s="1" t="inlineStr"/>
+      <c r="P90" s="1" t="inlineStr"/>
+      <c r="Q90" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R90" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5161,24 +5327,26 @@
           <t>artifact.to</t>
         </is>
       </c>
-      <c r="G91" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G91" s="1" t="inlineStr"/>
       <c r="H91" s="1" t="inlineStr"/>
-      <c r="I91" s="1" t="inlineStr"/>
+      <c r="I91" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J91" s="1" t="inlineStr"/>
       <c r="K91" s="1" t="inlineStr"/>
       <c r="L91" s="1" t="inlineStr"/>
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr"/>
-      <c r="O91" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P91" s="1" t="inlineStr">
+      <c r="O91" s="1" t="inlineStr"/>
+      <c r="P91" s="1" t="inlineStr"/>
+      <c r="Q91" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R91" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5203,24 +5371,26 @@
       <c r="D92" s="1" t="inlineStr"/>
       <c r="E92" s="1" t="inlineStr"/>
       <c r="F92" s="1" t="inlineStr"/>
-      <c r="G92" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G92" s="1" t="inlineStr"/>
       <c r="H92" s="1" t="inlineStr"/>
-      <c r="I92" s="1" t="inlineStr"/>
+      <c r="I92" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J92" s="1" t="inlineStr"/>
       <c r="K92" s="1" t="inlineStr"/>
       <c r="L92" s="1" t="inlineStr"/>
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr"/>
-      <c r="O92" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P92" s="1" t="inlineStr">
+      <c r="O92" s="1" t="inlineStr"/>
+      <c r="P92" s="1" t="inlineStr"/>
+      <c r="Q92" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R92" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5257,24 +5427,26 @@
           <t>caffesancarlo_torino</t>
         </is>
       </c>
-      <c r="G93" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G93" s="1" t="inlineStr"/>
       <c r="H93" s="1" t="inlineStr"/>
-      <c r="I93" s="1" t="inlineStr"/>
+      <c r="I93" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J93" s="1" t="inlineStr"/>
       <c r="K93" s="1" t="inlineStr"/>
       <c r="L93" s="1" t="inlineStr"/>
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr"/>
-      <c r="O93" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P93" s="1" t="inlineStr">
+      <c r="O93" s="1" t="inlineStr"/>
+      <c r="P93" s="1" t="inlineStr"/>
+      <c r="Q93" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R93" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5299,24 +5471,26 @@
       <c r="D94" s="1" t="inlineStr"/>
       <c r="E94" s="1" t="inlineStr"/>
       <c r="F94" s="1" t="inlineStr"/>
-      <c r="G94" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G94" s="1" t="inlineStr"/>
       <c r="H94" s="1" t="inlineStr"/>
-      <c r="I94" s="1" t="inlineStr"/>
+      <c r="I94" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J94" s="1" t="inlineStr"/>
       <c r="K94" s="1" t="inlineStr"/>
       <c r="L94" s="1" t="inlineStr"/>
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr"/>
-      <c r="O94" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P94" s="1" t="inlineStr">
+      <c r="O94" s="1" t="inlineStr"/>
+      <c r="P94" s="1" t="inlineStr"/>
+      <c r="Q94" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R94" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5353,24 +5527,26 @@
           <t>dappercoffeetorino</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G95" s="1" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
-      <c r="I95" s="1" t="inlineStr"/>
+      <c r="I95" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J95" s="1" t="inlineStr"/>
       <c r="K95" s="1" t="inlineStr"/>
       <c r="L95" s="1" t="inlineStr"/>
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr"/>
-      <c r="O95" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P95" s="1" t="inlineStr">
+      <c r="O95" s="1" t="inlineStr"/>
+      <c r="P95" s="1" t="inlineStr"/>
+      <c r="Q95" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R95" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5395,24 +5571,26 @@
       <c r="D96" s="1" t="inlineStr"/>
       <c r="E96" s="1" t="inlineStr"/>
       <c r="F96" s="1" t="inlineStr"/>
-      <c r="G96" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G96" s="1" t="inlineStr"/>
       <c r="H96" s="1" t="inlineStr"/>
-      <c r="I96" s="1" t="inlineStr"/>
+      <c r="I96" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J96" s="1" t="inlineStr"/>
       <c r="K96" s="1" t="inlineStr"/>
       <c r="L96" s="1" t="inlineStr"/>
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr"/>
-      <c r="O96" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P96" s="1" t="inlineStr">
+      <c r="O96" s="1" t="inlineStr"/>
+      <c r="P96" s="1" t="inlineStr"/>
+      <c r="Q96" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R96" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5449,24 +5627,26 @@
           <t>goccedicioccolato_torino</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G97" s="1" t="inlineStr"/>
       <c r="H97" s="1" t="inlineStr"/>
-      <c r="I97" s="1" t="inlineStr"/>
+      <c r="I97" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J97" s="1" t="inlineStr"/>
       <c r="K97" s="1" t="inlineStr"/>
       <c r="L97" s="1" t="inlineStr"/>
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr"/>
-      <c r="O97" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P97" s="1" t="inlineStr">
+      <c r="O97" s="1" t="inlineStr"/>
+      <c r="P97" s="1" t="inlineStr"/>
+      <c r="Q97" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R97" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5503,24 +5683,26 @@
           <t>orsolaboratoriocaffe</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G98" s="1" t="inlineStr"/>
       <c r="H98" s="1" t="inlineStr"/>
-      <c r="I98" s="1" t="inlineStr"/>
+      <c r="I98" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J98" s="1" t="inlineStr"/>
       <c r="K98" s="1" t="inlineStr"/>
       <c r="L98" s="1" t="inlineStr"/>
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr"/>
-      <c r="O98" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P98" s="1" t="inlineStr">
+      <c r="O98" s="1" t="inlineStr"/>
+      <c r="P98" s="1" t="inlineStr"/>
+      <c r="Q98" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R98" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5557,24 +5739,26 @@
           <t>pasticceriasabauda</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G99" s="1" t="inlineStr"/>
       <c r="H99" s="1" t="inlineStr"/>
-      <c r="I99" s="1" t="inlineStr"/>
+      <c r="I99" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J99" s="1" t="inlineStr"/>
       <c r="K99" s="1" t="inlineStr"/>
       <c r="L99" s="1" t="inlineStr"/>
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr"/>
-      <c r="O99" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P99" s="1" t="inlineStr">
+      <c r="O99" s="1" t="inlineStr"/>
+      <c r="P99" s="1" t="inlineStr"/>
+      <c r="Q99" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R99" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5607,24 +5791,26 @@
           <t>pasticceriavenier</t>
         </is>
       </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G100" s="1" t="inlineStr"/>
       <c r="H100" s="1" t="inlineStr"/>
-      <c r="I100" s="1" t="inlineStr"/>
+      <c r="I100" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J100" s="1" t="inlineStr"/>
       <c r="K100" s="1" t="inlineStr"/>
       <c r="L100" s="1" t="inlineStr"/>
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr"/>
-      <c r="O100" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P100" s="1" t="inlineStr">
+      <c r="O100" s="1" t="inlineStr"/>
+      <c r="P100" s="1" t="inlineStr"/>
+      <c r="Q100" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R100" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5657,24 +5843,26 @@
           <t>pressatocoffeebooks</t>
         </is>
       </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G101" s="1" t="inlineStr"/>
       <c r="H101" s="1" t="inlineStr"/>
-      <c r="I101" s="1" t="inlineStr"/>
+      <c r="I101" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J101" s="1" t="inlineStr"/>
       <c r="K101" s="1" t="inlineStr"/>
       <c r="L101" s="1" t="inlineStr"/>
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr"/>
-      <c r="O101" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P101" s="1" t="inlineStr">
+      <c r="O101" s="1" t="inlineStr"/>
+      <c r="P101" s="1" t="inlineStr"/>
+      <c r="Q101" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R101" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5699,24 +5887,26 @@
       <c r="D102" s="1" t="inlineStr"/>
       <c r="E102" s="1" t="inlineStr"/>
       <c r="F102" s="1" t="inlineStr"/>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G102" s="1" t="inlineStr"/>
       <c r="H102" s="1" t="inlineStr"/>
-      <c r="I102" s="1" t="inlineStr"/>
+      <c r="I102" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J102" s="1" t="inlineStr"/>
       <c r="K102" s="1" t="inlineStr"/>
       <c r="L102" s="1" t="inlineStr"/>
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr"/>
-      <c r="O102" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P102" s="1" t="inlineStr">
+      <c r="O102" s="1" t="inlineStr"/>
+      <c r="P102" s="1" t="inlineStr"/>
+      <c r="Q102" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R102" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5753,52 +5943,52 @@
           <t>adoniscreperie</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>Ott 2025</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>2026.0</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>12:00/19:30</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>Dom sera; Lun; Mar</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>Si (Guida Torino, Tripadvisor)</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>Creperie in stile bretone.</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="R103" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -5823,24 +6013,26 @@
       <c r="D104" s="1" t="inlineStr"/>
       <c r="E104" s="1" t="inlineStr"/>
       <c r="F104" s="1" t="inlineStr"/>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G104" s="1" t="inlineStr"/>
       <c r="H104" s="1" t="inlineStr"/>
-      <c r="I104" s="1" t="inlineStr"/>
+      <c r="I104" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J104" s="1" t="inlineStr"/>
       <c r="K104" s="1" t="inlineStr"/>
       <c r="L104" s="1" t="inlineStr"/>
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr"/>
-      <c r="O104" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P104" s="1" t="inlineStr">
+      <c r="O104" s="1" t="inlineStr"/>
+      <c r="P104" s="1" t="inlineStr"/>
+      <c r="Q104" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R104" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5877,24 +6069,26 @@
           <t>caffemulassano</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G105" s="1" t="inlineStr"/>
       <c r="H105" s="1" t="inlineStr"/>
-      <c r="I105" s="1" t="inlineStr"/>
+      <c r="I105" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J105" s="1" t="inlineStr"/>
       <c r="K105" s="1" t="inlineStr"/>
       <c r="L105" s="1" t="inlineStr"/>
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr"/>
-      <c r="O105" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P105" s="1" t="inlineStr">
+      <c r="O105" s="1" t="inlineStr"/>
+      <c r="P105" s="1" t="inlineStr"/>
+      <c r="Q105" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R105" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5931,24 +6125,26 @@
           <t>koitorino</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G106" s="1" t="inlineStr"/>
       <c r="H106" s="1" t="inlineStr"/>
-      <c r="I106" s="1" t="inlineStr"/>
+      <c r="I106" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J106" s="1" t="inlineStr"/>
       <c r="K106" s="1" t="inlineStr"/>
       <c r="L106" s="1" t="inlineStr"/>
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr"/>
-      <c r="O106" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P106" s="1" t="inlineStr">
+      <c r="O106" s="1" t="inlineStr"/>
+      <c r="P106" s="1" t="inlineStr"/>
+      <c r="Q106" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R106" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -5981,24 +6177,26 @@
           <t>kokoroyatorino</t>
         </is>
       </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G107" s="1" t="inlineStr"/>
       <c r="H107" s="1" t="inlineStr"/>
-      <c r="I107" s="1" t="inlineStr"/>
+      <c r="I107" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J107" s="1" t="inlineStr"/>
       <c r="K107" s="1" t="inlineStr"/>
       <c r="L107" s="1" t="inlineStr"/>
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr"/>
-      <c r="O107" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P107" s="1" t="inlineStr">
+      <c r="O107" s="1" t="inlineStr"/>
+      <c r="P107" s="1" t="inlineStr"/>
+      <c r="Q107" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R107" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6023,24 +6221,26 @@
       <c r="D108" s="1" t="inlineStr"/>
       <c r="E108" s="1" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr"/>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G108" s="1" t="inlineStr"/>
       <c r="H108" s="1" t="inlineStr"/>
-      <c r="I108" s="1" t="inlineStr"/>
+      <c r="I108" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J108" s="1" t="inlineStr"/>
       <c r="K108" s="1" t="inlineStr"/>
       <c r="L108" s="1" t="inlineStr"/>
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr"/>
-      <c r="O108" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P108" s="1" t="inlineStr">
+      <c r="O108" s="1" t="inlineStr"/>
+      <c r="P108" s="1" t="inlineStr"/>
+      <c r="Q108" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R108" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6065,24 +6265,26 @@
       <c r="D109" s="1" t="inlineStr"/>
       <c r="E109" s="1" t="inlineStr"/>
       <c r="F109" s="1" t="inlineStr"/>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G109" s="1" t="inlineStr"/>
       <c r="H109" s="1" t="inlineStr"/>
-      <c r="I109" s="1" t="inlineStr"/>
+      <c r="I109" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J109" s="1" t="inlineStr"/>
       <c r="K109" s="1" t="inlineStr"/>
       <c r="L109" s="1" t="inlineStr"/>
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr"/>
-      <c r="O109" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P109" s="1" t="inlineStr">
+      <c r="O109" s="1" t="inlineStr"/>
+      <c r="P109" s="1" t="inlineStr"/>
+      <c r="Q109" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R109" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6111,24 +6313,26 @@
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr"/>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G110" s="1" t="inlineStr"/>
       <c r="H110" s="1" t="inlineStr"/>
-      <c r="I110" s="1" t="inlineStr"/>
+      <c r="I110" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J110" s="1" t="inlineStr"/>
       <c r="K110" s="1" t="inlineStr"/>
       <c r="L110" s="1" t="inlineStr"/>
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr"/>
-      <c r="O110" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P110" s="1" t="inlineStr">
+      <c r="O110" s="1" t="inlineStr"/>
+      <c r="P110" s="1" t="inlineStr"/>
+      <c r="Q110" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R110" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6153,24 +6357,26 @@
       <c r="D111" s="1" t="inlineStr"/>
       <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr"/>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G111" s="1" t="inlineStr"/>
       <c r="H111" s="1" t="inlineStr"/>
-      <c r="I111" s="1" t="inlineStr"/>
+      <c r="I111" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J111" s="1" t="inlineStr"/>
       <c r="K111" s="1" t="inlineStr"/>
       <c r="L111" s="1" t="inlineStr"/>
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr"/>
-      <c r="O111" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P111" s="1" t="inlineStr">
+      <c r="O111" s="1" t="inlineStr"/>
+      <c r="P111" s="1" t="inlineStr"/>
+      <c r="Q111" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R111" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6207,24 +6413,26 @@
           <t>beppe_gallina</t>
         </is>
       </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G112" s="1" t="inlineStr"/>
       <c r="H112" s="1" t="inlineStr"/>
-      <c r="I112" s="1" t="inlineStr"/>
+      <c r="I112" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J112" s="1" t="inlineStr"/>
       <c r="K112" s="1" t="inlineStr"/>
       <c r="L112" s="1" t="inlineStr"/>
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr"/>
-      <c r="O112" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P112" s="1" t="inlineStr">
+      <c r="O112" s="1" t="inlineStr"/>
+      <c r="P112" s="1" t="inlineStr"/>
+      <c r="Q112" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R112" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6249,24 +6457,26 @@
       <c r="D113" s="1" t="inlineStr"/>
       <c r="E113" s="1" t="inlineStr"/>
       <c r="F113" s="1" t="inlineStr"/>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G113" s="1" t="inlineStr"/>
       <c r="H113" s="1" t="inlineStr"/>
-      <c r="I113" s="1" t="inlineStr"/>
+      <c r="I113" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J113" s="1" t="inlineStr"/>
       <c r="K113" s="1" t="inlineStr"/>
       <c r="L113" s="1" t="inlineStr"/>
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr"/>
-      <c r="O113" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P113" s="1" t="inlineStr">
+      <c r="O113" s="1" t="inlineStr"/>
+      <c r="P113" s="1" t="inlineStr"/>
+      <c r="Q113" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R113" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6303,24 +6513,26 @@
           <t>smithsbritish</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G114" s="1" t="inlineStr"/>
       <c r="H114" s="1" t="inlineStr"/>
-      <c r="I114" s="1" t="inlineStr"/>
+      <c r="I114" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J114" s="1" t="inlineStr"/>
       <c r="K114" s="1" t="inlineStr"/>
       <c r="L114" s="1" t="inlineStr"/>
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr"/>
-      <c r="O114" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P114" s="1" t="inlineStr">
+      <c r="O114" s="1" t="inlineStr"/>
+      <c r="P114" s="1" t="inlineStr"/>
+      <c r="Q114" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R114" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6345,24 +6557,26 @@
       <c r="D115" s="1" t="inlineStr"/>
       <c r="E115" s="1" t="inlineStr"/>
       <c r="F115" s="1" t="inlineStr"/>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G115" s="1" t="inlineStr"/>
       <c r="H115" s="1" t="inlineStr"/>
-      <c r="I115" s="1" t="inlineStr"/>
+      <c r="I115" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J115" s="1" t="inlineStr"/>
       <c r="K115" s="1" t="inlineStr"/>
       <c r="L115" s="1" t="inlineStr"/>
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr"/>
-      <c r="O115" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P115" s="1" t="inlineStr">
+      <c r="O115" s="1" t="inlineStr"/>
+      <c r="P115" s="1" t="inlineStr"/>
+      <c r="Q115" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R115" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6399,24 +6613,26 @@
           <t>tiffanybistrot</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G116" s="1" t="inlineStr"/>
       <c r="H116" s="1" t="inlineStr"/>
-      <c r="I116" s="1" t="inlineStr"/>
+      <c r="I116" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J116" s="1" t="inlineStr"/>
       <c r="K116" s="1" t="inlineStr"/>
       <c r="L116" s="1" t="inlineStr"/>
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr"/>
-      <c r="O116" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P116" s="1" t="inlineStr">
+      <c r="O116" s="1" t="inlineStr"/>
+      <c r="P116" s="1" t="inlineStr"/>
+      <c r="Q116" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R116" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6453,52 +6669,52 @@
           <t>bicerin.1763.torino</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>Gen 2026</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t>2026.0</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t>09:00-19:15</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="N117" t="inlineStr">
         <is>
           <t>Mer</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr">
+      <c r="O117" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr">
+      <c r="P117" t="inlineStr">
         <is>
           <t>Si (Torino Today gen 2026, Gambero Rosso 2026 3 tazze)</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr">
+      <c r="Q117" t="inlineStr">
         <is>
           <t>Storico caffe dal 1763.</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr">
+      <c r="R117" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -6535,24 +6751,26 @@
           <t>camellia.torino</t>
         </is>
       </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G118" s="1" t="inlineStr"/>
       <c r="H118" s="1" t="inlineStr"/>
-      <c r="I118" s="1" t="inlineStr"/>
+      <c r="I118" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J118" s="1" t="inlineStr"/>
       <c r="K118" s="1" t="inlineStr"/>
       <c r="L118" s="1" t="inlineStr"/>
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr"/>
-      <c r="O118" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P118" s="1" t="inlineStr">
+      <c r="O118" s="1" t="inlineStr"/>
+      <c r="P118" s="1" t="inlineStr"/>
+      <c r="Q118" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R118" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6581,24 +6799,26 @@
       </c>
       <c r="E119" s="1" t="inlineStr"/>
       <c r="F119" s="1" t="inlineStr"/>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G119" s="1" t="inlineStr"/>
       <c r="H119" s="1" t="inlineStr"/>
-      <c r="I119" s="1" t="inlineStr"/>
+      <c r="I119" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J119" s="1" t="inlineStr"/>
       <c r="K119" s="1" t="inlineStr"/>
       <c r="L119" s="1" t="inlineStr"/>
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr"/>
-      <c r="O119" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P119" s="1" t="inlineStr">
+      <c r="O119" s="1" t="inlineStr"/>
+      <c r="P119" s="1" t="inlineStr"/>
+      <c r="Q119" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R119" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6631,24 +6851,26 @@
           <t>kintsugiteandcakes</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G120" s="1" t="inlineStr"/>
       <c r="H120" s="1" t="inlineStr"/>
-      <c r="I120" s="1" t="inlineStr"/>
+      <c r="I120" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J120" s="1" t="inlineStr"/>
       <c r="K120" s="1" t="inlineStr"/>
       <c r="L120" s="1" t="inlineStr"/>
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr"/>
-      <c r="O120" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P120" s="1" t="inlineStr">
+      <c r="O120" s="1" t="inlineStr"/>
+      <c r="P120" s="1" t="inlineStr"/>
+      <c r="Q120" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R120" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6673,24 +6895,26 @@
       <c r="D121" s="1" t="inlineStr"/>
       <c r="E121" s="1" t="inlineStr"/>
       <c r="F121" s="1" t="inlineStr"/>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G121" s="1" t="inlineStr"/>
       <c r="H121" s="1" t="inlineStr"/>
-      <c r="I121" s="1" t="inlineStr"/>
+      <c r="I121" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J121" s="1" t="inlineStr"/>
       <c r="K121" s="1" t="inlineStr"/>
       <c r="L121" s="1" t="inlineStr"/>
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr"/>
-      <c r="O121" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P121" s="1" t="inlineStr">
+      <c r="O121" s="1" t="inlineStr"/>
+      <c r="P121" s="1" t="inlineStr"/>
+      <c r="Q121" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R121" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6723,24 +6947,26 @@
           <t>tarta.teatorteria</t>
         </is>
       </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G122" s="1" t="inlineStr"/>
       <c r="H122" s="1" t="inlineStr"/>
-      <c r="I122" s="1" t="inlineStr"/>
+      <c r="I122" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J122" s="1" t="inlineStr"/>
       <c r="K122" s="1" t="inlineStr"/>
       <c r="L122" s="1" t="inlineStr"/>
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr"/>
-      <c r="O122" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P122" s="1" t="inlineStr">
+      <c r="O122" s="1" t="inlineStr"/>
+      <c r="P122" s="1" t="inlineStr"/>
+      <c r="Q122" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R122" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6777,24 +7003,26 @@
           <t>thetea.torino</t>
         </is>
       </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G123" s="1" t="inlineStr"/>
       <c r="H123" s="1" t="inlineStr"/>
-      <c r="I123" s="1" t="inlineStr"/>
+      <c r="I123" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J123" s="1" t="inlineStr"/>
       <c r="K123" s="1" t="inlineStr"/>
       <c r="L123" s="1" t="inlineStr"/>
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr"/>
-      <c r="O123" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P123" s="1" t="inlineStr">
+      <c r="O123" s="1" t="inlineStr"/>
+      <c r="P123" s="1" t="inlineStr"/>
+      <c r="Q123" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R123" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6831,24 +7059,26 @@
           <t>olsentorteria</t>
         </is>
       </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G124" s="1" t="inlineStr"/>
       <c r="H124" s="1" t="inlineStr"/>
-      <c r="I124" s="1" t="inlineStr"/>
+      <c r="I124" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J124" s="1" t="inlineStr"/>
       <c r="K124" s="1" t="inlineStr"/>
       <c r="L124" s="1" t="inlineStr"/>
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr"/>
-      <c r="O124" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P124" s="1" t="inlineStr">
+      <c r="O124" s="1" t="inlineStr"/>
+      <c r="P124" s="1" t="inlineStr"/>
+      <c r="Q124" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R124" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6873,24 +7103,26 @@
       <c r="D125" s="1" t="inlineStr"/>
       <c r="E125" s="1" t="inlineStr"/>
       <c r="F125" s="1" t="inlineStr"/>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G125" s="1" t="inlineStr"/>
       <c r="H125" s="1" t="inlineStr"/>
-      <c r="I125" s="1" t="inlineStr"/>
+      <c r="I125" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J125" s="1" t="inlineStr"/>
       <c r="K125" s="1" t="inlineStr"/>
       <c r="L125" s="1" t="inlineStr"/>
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr"/>
-      <c r="O125" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P125" s="1" t="inlineStr">
+      <c r="O125" s="1" t="inlineStr"/>
+      <c r="P125" s="1" t="inlineStr"/>
+      <c r="Q125" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R125" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6927,24 +7159,26 @@
           <t>caffedellorologiotorino</t>
         </is>
       </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G126" s="1" t="inlineStr"/>
       <c r="H126" s="1" t="inlineStr"/>
-      <c r="I126" s="1" t="inlineStr"/>
+      <c r="I126" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J126" s="1" t="inlineStr"/>
       <c r="K126" s="1" t="inlineStr"/>
       <c r="L126" s="1" t="inlineStr"/>
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr"/>
-      <c r="O126" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P126" s="1" t="inlineStr">
+      <c r="O126" s="1" t="inlineStr"/>
+      <c r="P126" s="1" t="inlineStr"/>
+      <c r="Q126" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R126" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -6973,24 +7207,26 @@
           <t>cru.torino</t>
         </is>
       </c>
-      <c r="G127" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G127" s="1" t="inlineStr"/>
       <c r="H127" s="1" t="inlineStr"/>
-      <c r="I127" s="1" t="inlineStr"/>
+      <c r="I127" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J127" s="1" t="inlineStr"/>
       <c r="K127" s="1" t="inlineStr"/>
       <c r="L127" s="1" t="inlineStr"/>
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr"/>
-      <c r="O127" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P127" s="1" t="inlineStr">
+      <c r="O127" s="1" t="inlineStr"/>
+      <c r="P127" s="1" t="inlineStr"/>
+      <c r="Q127" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R127" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7015,24 +7251,26 @@
       <c r="D128" s="1" t="inlineStr"/>
       <c r="E128" s="1" t="inlineStr"/>
       <c r="F128" s="1" t="inlineStr"/>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G128" s="1" t="inlineStr"/>
       <c r="H128" s="1" t="inlineStr"/>
-      <c r="I128" s="1" t="inlineStr"/>
+      <c r="I128" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J128" s="1" t="inlineStr"/>
       <c r="K128" s="1" t="inlineStr"/>
       <c r="L128" s="1" t="inlineStr"/>
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr"/>
-      <c r="O128" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P128" s="1" t="inlineStr">
+      <c r="O128" s="1" t="inlineStr"/>
+      <c r="P128" s="1" t="inlineStr"/>
+      <c r="Q128" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R128" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7065,24 +7303,26 @@
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr"/>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G129" s="1" t="inlineStr"/>
       <c r="H129" s="1" t="inlineStr"/>
-      <c r="I129" s="1" t="inlineStr"/>
+      <c r="I129" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J129" s="1" t="inlineStr"/>
       <c r="K129" s="1" t="inlineStr"/>
       <c r="L129" s="1" t="inlineStr"/>
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr"/>
-      <c r="O129" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P129" s="1" t="inlineStr">
+      <c r="O129" s="1" t="inlineStr"/>
+      <c r="P129" s="1" t="inlineStr"/>
+      <c r="Q129" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R129" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7119,24 +7359,26 @@
           <t>palto.torino</t>
         </is>
       </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G130" s="1" t="inlineStr"/>
       <c r="H130" s="1" t="inlineStr"/>
-      <c r="I130" s="1" t="inlineStr"/>
+      <c r="I130" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J130" s="1" t="inlineStr"/>
       <c r="K130" s="1" t="inlineStr"/>
       <c r="L130" s="1" t="inlineStr"/>
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr"/>
-      <c r="O130" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P130" s="1" t="inlineStr">
+      <c r="O130" s="1" t="inlineStr"/>
+      <c r="P130" s="1" t="inlineStr"/>
+      <c r="Q130" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R130" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7169,24 +7411,26 @@
           <t>piattinicaffevini</t>
         </is>
       </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G131" s="1" t="inlineStr"/>
       <c r="H131" s="1" t="inlineStr"/>
-      <c r="I131" s="1" t="inlineStr"/>
+      <c r="I131" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J131" s="1" t="inlineStr"/>
       <c r="K131" s="1" t="inlineStr"/>
       <c r="L131" s="1" t="inlineStr"/>
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr"/>
-      <c r="O131" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P131" s="1" t="inlineStr">
+      <c r="O131" s="1" t="inlineStr"/>
+      <c r="P131" s="1" t="inlineStr"/>
+      <c r="Q131" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R131" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7223,24 +7467,26 @@
           <t>rossorubino.enoteca</t>
         </is>
       </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G132" s="1" t="inlineStr"/>
       <c r="H132" s="1" t="inlineStr"/>
-      <c r="I132" s="1" t="inlineStr"/>
+      <c r="I132" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J132" s="1" t="inlineStr"/>
       <c r="K132" s="1" t="inlineStr"/>
       <c r="L132" s="1" t="inlineStr"/>
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr"/>
-      <c r="O132" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P132" s="1" t="inlineStr">
+      <c r="O132" s="1" t="inlineStr"/>
+      <c r="P132" s="1" t="inlineStr"/>
+      <c r="Q132" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R132" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7265,24 +7511,26 @@
       <c r="D133" s="1" t="inlineStr"/>
       <c r="E133" s="1" t="inlineStr"/>
       <c r="F133" s="1" t="inlineStr"/>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G133" s="1" t="inlineStr"/>
       <c r="H133" s="1" t="inlineStr"/>
-      <c r="I133" s="1" t="inlineStr"/>
+      <c r="I133" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J133" s="1" t="inlineStr"/>
       <c r="K133" s="1" t="inlineStr"/>
       <c r="L133" s="1" t="inlineStr"/>
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr"/>
-      <c r="O133" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P133" s="1" t="inlineStr">
+      <c r="O133" s="1" t="inlineStr"/>
+      <c r="P133" s="1" t="inlineStr"/>
+      <c r="Q133" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R133" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7319,24 +7567,26 @@
           <t>tastumatorino</t>
         </is>
       </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G134" s="1" t="inlineStr"/>
       <c r="H134" s="1" t="inlineStr"/>
-      <c r="I134" s="1" t="inlineStr"/>
+      <c r="I134" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J134" s="1" t="inlineStr"/>
       <c r="K134" s="1" t="inlineStr"/>
       <c r="L134" s="1" t="inlineStr"/>
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr"/>
-      <c r="O134" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P134" s="1" t="inlineStr">
+      <c r="O134" s="1" t="inlineStr"/>
+      <c r="P134" s="1" t="inlineStr"/>
+      <c r="Q134" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R134" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7361,24 +7611,26 @@
       <c r="D135" s="1" t="inlineStr"/>
       <c r="E135" s="1" t="inlineStr"/>
       <c r="F135" s="1" t="inlineStr"/>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G135" s="1" t="inlineStr"/>
       <c r="H135" s="1" t="inlineStr"/>
-      <c r="I135" s="1" t="inlineStr"/>
+      <c r="I135" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J135" s="1" t="inlineStr"/>
       <c r="K135" s="1" t="inlineStr"/>
       <c r="L135" s="1" t="inlineStr"/>
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr"/>
-      <c r="O135" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P135" s="1" t="inlineStr">
+      <c r="O135" s="1" t="inlineStr"/>
+      <c r="P135" s="1" t="inlineStr"/>
+      <c r="Q135" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R135" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7403,24 +7655,26 @@
       <c r="D136" s="1" t="inlineStr"/>
       <c r="E136" s="1" t="inlineStr"/>
       <c r="F136" s="1" t="inlineStr"/>
-      <c r="G136" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G136" s="1" t="inlineStr"/>
       <c r="H136" s="1" t="inlineStr"/>
-      <c r="I136" s="1" t="inlineStr"/>
+      <c r="I136" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J136" s="1" t="inlineStr"/>
       <c r="K136" s="1" t="inlineStr"/>
       <c r="L136" s="1" t="inlineStr"/>
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr"/>
-      <c r="O136" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P136" s="1" t="inlineStr">
+      <c r="O136" s="1" t="inlineStr"/>
+      <c r="P136" s="1" t="inlineStr"/>
+      <c r="Q136" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R136" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7445,24 +7699,26 @@
       <c r="D137" s="1" t="inlineStr"/>
       <c r="E137" s="1" t="inlineStr"/>
       <c r="F137" s="1" t="inlineStr"/>
-      <c r="G137" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G137" s="1" t="inlineStr"/>
       <c r="H137" s="1" t="inlineStr"/>
-      <c r="I137" s="1" t="inlineStr"/>
+      <c r="I137" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J137" s="1" t="inlineStr"/>
       <c r="K137" s="1" t="inlineStr"/>
       <c r="L137" s="1" t="inlineStr"/>
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr"/>
-      <c r="O137" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P137" s="1" t="inlineStr">
+      <c r="O137" s="1" t="inlineStr"/>
+      <c r="P137" s="1" t="inlineStr"/>
+      <c r="Q137" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R137" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7491,24 +7747,26 @@
           <t>coucoutorino</t>
         </is>
       </c>
-      <c r="G138" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G138" s="1" t="inlineStr"/>
       <c r="H138" s="1" t="inlineStr"/>
-      <c r="I138" s="1" t="inlineStr"/>
+      <c r="I138" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J138" s="1" t="inlineStr"/>
       <c r="K138" s="1" t="inlineStr"/>
       <c r="L138" s="1" t="inlineStr"/>
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr"/>
-      <c r="O138" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P138" s="1" t="inlineStr">
+      <c r="O138" s="1" t="inlineStr"/>
+      <c r="P138" s="1" t="inlineStr"/>
+      <c r="Q138" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R138" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7533,24 +7791,26 @@
       <c r="D139" s="1" t="inlineStr"/>
       <c r="E139" s="1" t="inlineStr"/>
       <c r="F139" s="1" t="inlineStr"/>
-      <c r="G139" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G139" s="1" t="inlineStr"/>
       <c r="H139" s="1" t="inlineStr"/>
-      <c r="I139" s="1" t="inlineStr"/>
+      <c r="I139" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J139" s="1" t="inlineStr"/>
       <c r="K139" s="1" t="inlineStr"/>
       <c r="L139" s="1" t="inlineStr"/>
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr"/>
-      <c r="O139" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P139" s="1" t="inlineStr">
+      <c r="O139" s="1" t="inlineStr"/>
+      <c r="P139" s="1" t="inlineStr"/>
+      <c r="Q139" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R139" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7575,24 +7835,26 @@
       <c r="D140" s="1" t="inlineStr"/>
       <c r="E140" s="1" t="inlineStr"/>
       <c r="F140" s="1" t="inlineStr"/>
-      <c r="G140" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G140" s="1" t="inlineStr"/>
       <c r="H140" s="1" t="inlineStr"/>
-      <c r="I140" s="1" t="inlineStr"/>
+      <c r="I140" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J140" s="1" t="inlineStr"/>
       <c r="K140" s="1" t="inlineStr"/>
       <c r="L140" s="1" t="inlineStr"/>
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr"/>
-      <c r="O140" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P140" s="1" t="inlineStr">
+      <c r="O140" s="1" t="inlineStr"/>
+      <c r="P140" s="1" t="inlineStr"/>
+      <c r="Q140" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R140" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7617,24 +7879,26 @@
       <c r="D141" s="1" t="inlineStr"/>
       <c r="E141" s="1" t="inlineStr"/>
       <c r="F141" s="1" t="inlineStr"/>
-      <c r="G141" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G141" s="1" t="inlineStr"/>
       <c r="H141" s="1" t="inlineStr"/>
-      <c r="I141" s="1" t="inlineStr"/>
+      <c r="I141" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J141" s="1" t="inlineStr"/>
       <c r="K141" s="1" t="inlineStr"/>
       <c r="L141" s="1" t="inlineStr"/>
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr"/>
-      <c r="O141" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P141" s="1" t="inlineStr">
+      <c r="O141" s="1" t="inlineStr"/>
+      <c r="P141" s="1" t="inlineStr"/>
+      <c r="Q141" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R141" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7671,24 +7935,26 @@
           <t>recina-focaccia-e-cucina</t>
         </is>
       </c>
-      <c r="G142" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G142" s="1" t="inlineStr"/>
       <c r="H142" s="1" t="inlineStr"/>
-      <c r="I142" s="1" t="inlineStr"/>
+      <c r="I142" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J142" s="1" t="inlineStr"/>
       <c r="K142" s="1" t="inlineStr"/>
       <c r="L142" s="1" t="inlineStr"/>
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr"/>
-      <c r="O142" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P142" s="1" t="inlineStr">
+      <c r="O142" s="1" t="inlineStr"/>
+      <c r="P142" s="1" t="inlineStr"/>
+      <c r="Q142" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R142" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7713,24 +7979,26 @@
       <c r="D143" s="1" t="inlineStr"/>
       <c r="E143" s="1" t="inlineStr"/>
       <c r="F143" s="1" t="inlineStr"/>
-      <c r="G143" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G143" s="1" t="inlineStr"/>
       <c r="H143" s="1" t="inlineStr"/>
-      <c r="I143" s="1" t="inlineStr"/>
+      <c r="I143" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J143" s="1" t="inlineStr"/>
       <c r="K143" s="1" t="inlineStr"/>
       <c r="L143" s="1" t="inlineStr"/>
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr"/>
-      <c r="O143" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P143" s="1" t="inlineStr">
+      <c r="O143" s="1" t="inlineStr"/>
+      <c r="P143" s="1" t="inlineStr"/>
+      <c r="Q143" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R143" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7767,52 +8035,52 @@
           <t>affinitorino</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="J144" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="K144" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t>2026.0</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t>17:00 in poi</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="N144" t="inlineStr">
         <is>
           <t>Nessuno</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr">
+      <c r="O144" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr">
+      <c r="P144" t="inlineStr">
         <is>
           <t>Si (Yelp Feb 2026)</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr">
+      <c r="Q144" t="inlineStr">
         <is>
           <t>Cocktail bar in San Salvario.</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr">
+      <c r="R144" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -7837,24 +8105,26 @@
       <c r="D145" s="1" t="inlineStr"/>
       <c r="E145" s="1" t="inlineStr"/>
       <c r="F145" s="1" t="inlineStr"/>
-      <c r="G145" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G145" s="1" t="inlineStr"/>
       <c r="H145" s="1" t="inlineStr"/>
-      <c r="I145" s="1" t="inlineStr"/>
+      <c r="I145" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J145" s="1" t="inlineStr"/>
       <c r="K145" s="1" t="inlineStr"/>
       <c r="L145" s="1" t="inlineStr"/>
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr"/>
-      <c r="O145" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P145" s="1" t="inlineStr">
+      <c r="O145" s="1" t="inlineStr"/>
+      <c r="P145" s="1" t="inlineStr"/>
+      <c r="Q145" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R145" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7879,24 +8149,26 @@
       <c r="D146" s="1" t="inlineStr"/>
       <c r="E146" s="1" t="inlineStr"/>
       <c r="F146" s="1" t="inlineStr"/>
-      <c r="G146" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G146" s="1" t="inlineStr"/>
       <c r="H146" s="1" t="inlineStr"/>
-      <c r="I146" s="1" t="inlineStr"/>
+      <c r="I146" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J146" s="1" t="inlineStr"/>
       <c r="K146" s="1" t="inlineStr"/>
       <c r="L146" s="1" t="inlineStr"/>
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr"/>
-      <c r="O146" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P146" s="1" t="inlineStr">
+      <c r="O146" s="1" t="inlineStr"/>
+      <c r="P146" s="1" t="inlineStr"/>
+      <c r="Q146" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R146" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7929,24 +8201,26 @@
           <t>donetorino</t>
         </is>
       </c>
-      <c r="G147" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G147" s="1" t="inlineStr"/>
       <c r="H147" s="1" t="inlineStr"/>
-      <c r="I147" s="1" t="inlineStr"/>
+      <c r="I147" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J147" s="1" t="inlineStr"/>
       <c r="K147" s="1" t="inlineStr"/>
       <c r="L147" s="1" t="inlineStr"/>
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr"/>
-      <c r="O147" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P147" s="1" t="inlineStr">
+      <c r="O147" s="1" t="inlineStr"/>
+      <c r="P147" s="1" t="inlineStr"/>
+      <c r="Q147" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R147" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -7971,24 +8245,26 @@
       <c r="D148" s="1" t="inlineStr"/>
       <c r="E148" s="1" t="inlineStr"/>
       <c r="F148" s="1" t="inlineStr"/>
-      <c r="G148" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G148" s="1" t="inlineStr"/>
       <c r="H148" s="1" t="inlineStr"/>
-      <c r="I148" s="1" t="inlineStr"/>
+      <c r="I148" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J148" s="1" t="inlineStr"/>
       <c r="K148" s="1" t="inlineStr"/>
       <c r="L148" s="1" t="inlineStr"/>
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr"/>
-      <c r="O148" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P148" s="1" t="inlineStr">
+      <c r="O148" s="1" t="inlineStr"/>
+      <c r="P148" s="1" t="inlineStr"/>
+      <c r="Q148" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R148" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8025,24 +8301,26 @@
           <t>smile_tree_torino</t>
         </is>
       </c>
-      <c r="G149" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G149" s="1" t="inlineStr"/>
       <c r="H149" s="1" t="inlineStr"/>
-      <c r="I149" s="1" t="inlineStr"/>
+      <c r="I149" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J149" s="1" t="inlineStr"/>
       <c r="K149" s="1" t="inlineStr"/>
       <c r="L149" s="1" t="inlineStr"/>
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr"/>
-      <c r="O149" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P149" s="1" t="inlineStr">
+      <c r="O149" s="1" t="inlineStr"/>
+      <c r="P149" s="1" t="inlineStr"/>
+      <c r="Q149" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R149" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8067,24 +8345,26 @@
       <c r="D150" s="1" t="inlineStr"/>
       <c r="E150" s="1" t="inlineStr"/>
       <c r="F150" s="1" t="inlineStr"/>
-      <c r="G150" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G150" s="1" t="inlineStr"/>
       <c r="H150" s="1" t="inlineStr"/>
-      <c r="I150" s="1" t="inlineStr"/>
+      <c r="I150" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J150" s="1" t="inlineStr"/>
       <c r="K150" s="1" t="inlineStr"/>
       <c r="L150" s="1" t="inlineStr"/>
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr"/>
-      <c r="O150" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P150" s="1" t="inlineStr">
+      <c r="O150" s="1" t="inlineStr"/>
+      <c r="P150" s="1" t="inlineStr"/>
+      <c r="Q150" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R150" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8121,52 +8401,52 @@
           <t>alberto_marchetti_gelaterie</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t>APERTO</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="J151" t="inlineStr">
         <is>
           <t>Apr 2026</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="K151" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t>2026.0</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t>Gelateria aperta; pop-up apr-giu 2026</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="N151" t="inlineStr">
         <is>
           <t>Nessuno</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr">
+      <c r="O151" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr">
+      <c r="P151" t="inlineStr">
         <is>
           <t>Si (Ieri Oggi Domani apr 2026)</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr">
+      <c r="Q151" t="inlineStr">
         <is>
           <t>Pop-up tiramisu P.za CLN fino 21 giu 2026.</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr">
+      <c r="R151" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
@@ -8199,24 +8479,26 @@
           <t>aria_gelateria</t>
         </is>
       </c>
-      <c r="G152" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G152" s="1" t="inlineStr"/>
       <c r="H152" s="1" t="inlineStr"/>
-      <c r="I152" s="1" t="inlineStr"/>
+      <c r="I152" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J152" s="1" t="inlineStr"/>
       <c r="K152" s="1" t="inlineStr"/>
       <c r="L152" s="1" t="inlineStr"/>
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr"/>
-      <c r="O152" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P152" s="1" t="inlineStr">
+      <c r="O152" s="1" t="inlineStr"/>
+      <c r="P152" s="1" t="inlineStr"/>
+      <c r="Q152" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R152" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8241,24 +8523,26 @@
       <c r="D153" s="1" t="inlineStr"/>
       <c r="E153" s="1" t="inlineStr"/>
       <c r="F153" s="1" t="inlineStr"/>
-      <c r="G153" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G153" s="1" t="inlineStr"/>
       <c r="H153" s="1" t="inlineStr"/>
-      <c r="I153" s="1" t="inlineStr"/>
+      <c r="I153" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J153" s="1" t="inlineStr"/>
       <c r="K153" s="1" t="inlineStr"/>
       <c r="L153" s="1" t="inlineStr"/>
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr"/>
-      <c r="O153" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P153" s="1" t="inlineStr">
+      <c r="O153" s="1" t="inlineStr"/>
+      <c r="P153" s="1" t="inlineStr"/>
+      <c r="Q153" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R153" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8283,24 +8567,26 @@
       <c r="D154" s="1" t="inlineStr"/>
       <c r="E154" s="1" t="inlineStr"/>
       <c r="F154" s="1" t="inlineStr"/>
-      <c r="G154" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G154" s="1" t="inlineStr"/>
       <c r="H154" s="1" t="inlineStr"/>
-      <c r="I154" s="1" t="inlineStr"/>
+      <c r="I154" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J154" s="1" t="inlineStr"/>
       <c r="K154" s="1" t="inlineStr"/>
       <c r="L154" s="1" t="inlineStr"/>
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr"/>
-      <c r="O154" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P154" s="1" t="inlineStr">
+      <c r="O154" s="1" t="inlineStr"/>
+      <c r="P154" s="1" t="inlineStr"/>
+      <c r="Q154" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R154" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8337,24 +8623,26 @@
           <t>_conogelato_</t>
         </is>
       </c>
-      <c r="G155" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G155" s="1" t="inlineStr"/>
       <c r="H155" s="1" t="inlineStr"/>
-      <c r="I155" s="1" t="inlineStr"/>
+      <c r="I155" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J155" s="1" t="inlineStr"/>
       <c r="K155" s="1" t="inlineStr"/>
       <c r="L155" s="1" t="inlineStr"/>
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr"/>
-      <c r="O155" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P155" s="1" t="inlineStr">
+      <c r="O155" s="1" t="inlineStr"/>
+      <c r="P155" s="1" t="inlineStr"/>
+      <c r="Q155" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R155" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8379,24 +8667,26 @@
       <c r="D156" s="1" t="inlineStr"/>
       <c r="E156" s="1" t="inlineStr"/>
       <c r="F156" s="1" t="inlineStr"/>
-      <c r="G156" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G156" s="1" t="inlineStr"/>
       <c r="H156" s="1" t="inlineStr"/>
-      <c r="I156" s="1" t="inlineStr"/>
+      <c r="I156" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J156" s="1" t="inlineStr"/>
       <c r="K156" s="1" t="inlineStr"/>
       <c r="L156" s="1" t="inlineStr"/>
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr"/>
-      <c r="O156" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P156" s="1" t="inlineStr">
+      <c r="O156" s="1" t="inlineStr"/>
+      <c r="P156" s="1" t="inlineStr"/>
+      <c r="Q156" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R156" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8433,24 +8723,26 @@
           <t>gaspringelatoedelizie</t>
         </is>
       </c>
-      <c r="G157" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G157" s="1" t="inlineStr"/>
       <c r="H157" s="1" t="inlineStr"/>
-      <c r="I157" s="1" t="inlineStr"/>
+      <c r="I157" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J157" s="1" t="inlineStr"/>
       <c r="K157" s="1" t="inlineStr"/>
       <c r="L157" s="1" t="inlineStr"/>
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr"/>
-      <c r="O157" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P157" s="1" t="inlineStr">
+      <c r="O157" s="1" t="inlineStr"/>
+      <c r="P157" s="1" t="inlineStr"/>
+      <c r="Q157" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R157" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8475,24 +8767,26 @@
       <c r="D158" s="1" t="inlineStr"/>
       <c r="E158" s="1" t="inlineStr"/>
       <c r="F158" s="1" t="inlineStr"/>
-      <c r="G158" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G158" s="1" t="inlineStr"/>
       <c r="H158" s="1" t="inlineStr"/>
-      <c r="I158" s="1" t="inlineStr"/>
+      <c r="I158" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J158" s="1" t="inlineStr"/>
       <c r="K158" s="1" t="inlineStr"/>
       <c r="L158" s="1" t="inlineStr"/>
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr"/>
-      <c r="O158" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P158" s="1" t="inlineStr">
+      <c r="O158" s="1" t="inlineStr"/>
+      <c r="P158" s="1" t="inlineStr"/>
+      <c r="Q158" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R158" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8517,24 +8811,26 @@
       <c r="D159" s="1" t="inlineStr"/>
       <c r="E159" s="1" t="inlineStr"/>
       <c r="F159" s="1" t="inlineStr"/>
-      <c r="G159" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G159" s="1" t="inlineStr"/>
       <c r="H159" s="1" t="inlineStr"/>
-      <c r="I159" s="1" t="inlineStr"/>
+      <c r="I159" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J159" s="1" t="inlineStr"/>
       <c r="K159" s="1" t="inlineStr"/>
       <c r="L159" s="1" t="inlineStr"/>
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr"/>
-      <c r="O159" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P159" s="1" t="inlineStr">
+      <c r="O159" s="1" t="inlineStr"/>
+      <c r="P159" s="1" t="inlineStr"/>
+      <c r="Q159" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R159" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8571,24 +8867,26 @@
           <t>gelateria_miretti</t>
         </is>
       </c>
-      <c r="G160" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G160" s="1" t="inlineStr"/>
       <c r="H160" s="1" t="inlineStr"/>
-      <c r="I160" s="1" t="inlineStr"/>
+      <c r="I160" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J160" s="1" t="inlineStr"/>
       <c r="K160" s="1" t="inlineStr"/>
       <c r="L160" s="1" t="inlineStr"/>
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr"/>
-      <c r="O160" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P160" s="1" t="inlineStr">
+      <c r="O160" s="1" t="inlineStr"/>
+      <c r="P160" s="1" t="inlineStr"/>
+      <c r="Q160" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R160" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8613,24 +8911,26 @@
       <c r="D161" s="1" t="inlineStr"/>
       <c r="E161" s="1" t="inlineStr"/>
       <c r="F161" s="1" t="inlineStr"/>
-      <c r="G161" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G161" s="1" t="inlineStr"/>
       <c r="H161" s="1" t="inlineStr"/>
-      <c r="I161" s="1" t="inlineStr"/>
+      <c r="I161" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J161" s="1" t="inlineStr"/>
       <c r="K161" s="1" t="inlineStr"/>
       <c r="L161" s="1" t="inlineStr"/>
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr"/>
-      <c r="O161" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P161" s="1" t="inlineStr">
+      <c r="O161" s="1" t="inlineStr"/>
+      <c r="P161" s="1" t="inlineStr"/>
+      <c r="Q161" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R161" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8667,24 +8967,26 @@
           <t>gofreriapiemonteisa</t>
         </is>
       </c>
-      <c r="G162" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G162" s="1" t="inlineStr"/>
       <c r="H162" s="1" t="inlineStr"/>
-      <c r="I162" s="1" t="inlineStr"/>
+      <c r="I162" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J162" s="1" t="inlineStr"/>
       <c r="K162" s="1" t="inlineStr"/>
       <c r="L162" s="1" t="inlineStr"/>
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr"/>
-      <c r="O162" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P162" s="1" t="inlineStr">
+      <c r="O162" s="1" t="inlineStr"/>
+      <c r="P162" s="1" t="inlineStr"/>
+      <c r="Q162" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R162" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8709,24 +9011,26 @@
       <c r="D163" s="1" t="inlineStr"/>
       <c r="E163" s="1" t="inlineStr"/>
       <c r="F163" s="1" t="inlineStr"/>
-      <c r="G163" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G163" s="1" t="inlineStr"/>
       <c r="H163" s="1" t="inlineStr"/>
-      <c r="I163" s="1" t="inlineStr"/>
+      <c r="I163" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J163" s="1" t="inlineStr"/>
       <c r="K163" s="1" t="inlineStr"/>
       <c r="L163" s="1" t="inlineStr"/>
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr"/>
-      <c r="O163" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P163" s="1" t="inlineStr">
+      <c r="O163" s="1" t="inlineStr"/>
+      <c r="P163" s="1" t="inlineStr"/>
+      <c r="Q163" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R163" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8755,24 +9059,26 @@
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr"/>
-      <c r="G164" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G164" s="1" t="inlineStr"/>
       <c r="H164" s="1" t="inlineStr"/>
-      <c r="I164" s="1" t="inlineStr"/>
+      <c r="I164" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J164" s="1" t="inlineStr"/>
       <c r="K164" s="1" t="inlineStr"/>
       <c r="L164" s="1" t="inlineStr"/>
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr"/>
-      <c r="O164" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P164" s="1" t="inlineStr">
+      <c r="O164" s="1" t="inlineStr"/>
+      <c r="P164" s="1" t="inlineStr"/>
+      <c r="Q164" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R164" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8809,24 +9115,26 @@
           <t>macbun_official</t>
         </is>
       </c>
-      <c r="G165" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G165" s="1" t="inlineStr"/>
       <c r="H165" s="1" t="inlineStr"/>
-      <c r="I165" s="1" t="inlineStr"/>
+      <c r="I165" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J165" s="1" t="inlineStr"/>
       <c r="K165" s="1" t="inlineStr"/>
       <c r="L165" s="1" t="inlineStr"/>
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr"/>
-      <c r="O165" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P165" s="1" t="inlineStr">
+      <c r="O165" s="1" t="inlineStr"/>
+      <c r="P165" s="1" t="inlineStr"/>
+      <c r="Q165" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R165" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8863,24 +9171,26 @@
           <t>maradeiboschi</t>
         </is>
       </c>
-      <c r="G166" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G166" s="1" t="inlineStr"/>
       <c r="H166" s="1" t="inlineStr"/>
-      <c r="I166" s="1" t="inlineStr"/>
+      <c r="I166" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J166" s="1" t="inlineStr"/>
       <c r="K166" s="1" t="inlineStr"/>
       <c r="L166" s="1" t="inlineStr"/>
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr"/>
-      <c r="O166" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P166" s="1" t="inlineStr">
+      <c r="O166" s="1" t="inlineStr"/>
+      <c r="P166" s="1" t="inlineStr"/>
+      <c r="Q166" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R166" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8917,24 +9227,26 @@
           <t>margheripizza</t>
         </is>
       </c>
-      <c r="G167" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G167" s="1" t="inlineStr"/>
       <c r="H167" s="1" t="inlineStr"/>
-      <c r="I167" s="1" t="inlineStr"/>
+      <c r="I167" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J167" s="1" t="inlineStr"/>
       <c r="K167" s="1" t="inlineStr"/>
       <c r="L167" s="1" t="inlineStr"/>
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr"/>
-      <c r="O167" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P167" s="1" t="inlineStr">
+      <c r="O167" s="1" t="inlineStr"/>
+      <c r="P167" s="1" t="inlineStr"/>
+      <c r="Q167" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R167" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -8959,24 +9271,26 @@
       <c r="D168" s="1" t="inlineStr"/>
       <c r="E168" s="1" t="inlineStr"/>
       <c r="F168" s="1" t="inlineStr"/>
-      <c r="G168" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G168" s="1" t="inlineStr"/>
       <c r="H168" s="1" t="inlineStr"/>
-      <c r="I168" s="1" t="inlineStr"/>
+      <c r="I168" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J168" s="1" t="inlineStr"/>
       <c r="K168" s="1" t="inlineStr"/>
       <c r="L168" s="1" t="inlineStr"/>
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr"/>
-      <c r="O168" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P168" s="1" t="inlineStr">
+      <c r="O168" s="1" t="inlineStr"/>
+      <c r="P168" s="1" t="inlineStr"/>
+      <c r="Q168" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R168" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9009,24 +9323,26 @@
           <t>modo_gelato</t>
         </is>
       </c>
-      <c r="G169" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G169" s="1" t="inlineStr"/>
       <c r="H169" s="1" t="inlineStr"/>
-      <c r="I169" s="1" t="inlineStr"/>
+      <c r="I169" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J169" s="1" t="inlineStr"/>
       <c r="K169" s="1" t="inlineStr"/>
       <c r="L169" s="1" t="inlineStr"/>
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr"/>
-      <c r="O169" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P169" s="1" t="inlineStr">
+      <c r="O169" s="1" t="inlineStr"/>
+      <c r="P169" s="1" t="inlineStr"/>
+      <c r="Q169" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R169" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9063,24 +9379,26 @@
           <t>nivagelato</t>
         </is>
       </c>
-      <c r="G170" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G170" s="1" t="inlineStr"/>
       <c r="H170" s="1" t="inlineStr"/>
-      <c r="I170" s="1" t="inlineStr"/>
+      <c r="I170" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J170" s="1" t="inlineStr"/>
       <c r="K170" s="1" t="inlineStr"/>
       <c r="L170" s="1" t="inlineStr"/>
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr"/>
-      <c r="O170" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P170" s="1" t="inlineStr">
+      <c r="O170" s="1" t="inlineStr"/>
+      <c r="P170" s="1" t="inlineStr"/>
+      <c r="Q170" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R170" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9113,24 +9431,26 @@
           <t>ottimogelati</t>
         </is>
       </c>
-      <c r="G171" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G171" s="1" t="inlineStr"/>
       <c r="H171" s="1" t="inlineStr"/>
-      <c r="I171" s="1" t="inlineStr"/>
+      <c r="I171" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J171" s="1" t="inlineStr"/>
       <c r="K171" s="1" t="inlineStr"/>
       <c r="L171" s="1" t="inlineStr"/>
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr"/>
-      <c r="O171" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P171" s="1" t="inlineStr">
+      <c r="O171" s="1" t="inlineStr"/>
+      <c r="P171" s="1" t="inlineStr"/>
+      <c r="Q171" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R171" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9167,24 +9487,26 @@
           <t>papalele.gelatiepasticci</t>
         </is>
       </c>
-      <c r="G172" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G172" s="1" t="inlineStr"/>
       <c r="H172" s="1" t="inlineStr"/>
-      <c r="I172" s="1" t="inlineStr"/>
+      <c r="I172" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J172" s="1" t="inlineStr"/>
       <c r="K172" s="1" t="inlineStr"/>
       <c r="L172" s="1" t="inlineStr"/>
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr"/>
-      <c r="O172" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P172" s="1" t="inlineStr">
+      <c r="O172" s="1" t="inlineStr"/>
+      <c r="P172" s="1" t="inlineStr"/>
+      <c r="Q172" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R172" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9221,24 +9543,26 @@
           <t>piudiungelato</t>
         </is>
       </c>
-      <c r="G173" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G173" s="1" t="inlineStr"/>
       <c r="H173" s="1" t="inlineStr"/>
-      <c r="I173" s="1" t="inlineStr"/>
+      <c r="I173" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J173" s="1" t="inlineStr"/>
       <c r="K173" s="1" t="inlineStr"/>
       <c r="L173" s="1" t="inlineStr"/>
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr"/>
-      <c r="O173" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P173" s="1" t="inlineStr">
+      <c r="O173" s="1" t="inlineStr"/>
+      <c r="P173" s="1" t="inlineStr"/>
+      <c r="Q173" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R173" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9271,24 +9595,26 @@
           <t>robertafocacceria</t>
         </is>
       </c>
-      <c r="G174" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G174" s="1" t="inlineStr"/>
       <c r="H174" s="1" t="inlineStr"/>
-      <c r="I174" s="1" t="inlineStr"/>
+      <c r="I174" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J174" s="1" t="inlineStr"/>
       <c r="K174" s="1" t="inlineStr"/>
       <c r="L174" s="1" t="inlineStr"/>
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr"/>
-      <c r="O174" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P174" s="1" t="inlineStr">
+      <c r="O174" s="1" t="inlineStr"/>
+      <c r="P174" s="1" t="inlineStr"/>
+      <c r="Q174" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R174" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9313,24 +9639,26 @@
       <c r="D175" s="1" t="inlineStr"/>
       <c r="E175" s="1" t="inlineStr"/>
       <c r="F175" s="1" t="inlineStr"/>
-      <c r="G175" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G175" s="1" t="inlineStr"/>
       <c r="H175" s="1" t="inlineStr"/>
-      <c r="I175" s="1" t="inlineStr"/>
+      <c r="I175" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J175" s="1" t="inlineStr"/>
       <c r="K175" s="1" t="inlineStr"/>
       <c r="L175" s="1" t="inlineStr"/>
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr"/>
-      <c r="O175" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P175" s="1" t="inlineStr">
+      <c r="O175" s="1" t="inlineStr"/>
+      <c r="P175" s="1" t="inlineStr"/>
+      <c r="Q175" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R175" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9367,24 +9695,26 @@
           <t>silvanogelatodaltritempi</t>
         </is>
       </c>
-      <c r="G176" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G176" s="1" t="inlineStr"/>
       <c r="H176" s="1" t="inlineStr"/>
-      <c r="I176" s="1" t="inlineStr"/>
+      <c r="I176" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J176" s="1" t="inlineStr"/>
       <c r="K176" s="1" t="inlineStr"/>
       <c r="L176" s="1" t="inlineStr"/>
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr"/>
-      <c r="O176" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P176" s="1" t="inlineStr">
+      <c r="O176" s="1" t="inlineStr"/>
+      <c r="P176" s="1" t="inlineStr"/>
+      <c r="Q176" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R176" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9421,24 +9751,26 @@
           <t>taglioperfetta</t>
         </is>
       </c>
-      <c r="G177" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G177" s="1" t="inlineStr"/>
       <c r="H177" s="1" t="inlineStr"/>
-      <c r="I177" s="1" t="inlineStr"/>
+      <c r="I177" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J177" s="1" t="inlineStr"/>
       <c r="K177" s="1" t="inlineStr"/>
       <c r="L177" s="1" t="inlineStr"/>
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr"/>
-      <c r="O177" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P177" s="1" t="inlineStr">
+      <c r="O177" s="1" t="inlineStr"/>
+      <c r="P177" s="1" t="inlineStr"/>
+      <c r="Q177" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R177" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9475,24 +9807,26 @@
           <t>telliatorino</t>
         </is>
       </c>
-      <c r="G178" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G178" s="1" t="inlineStr"/>
       <c r="H178" s="1" t="inlineStr"/>
-      <c r="I178" s="1" t="inlineStr"/>
+      <c r="I178" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J178" s="1" t="inlineStr"/>
       <c r="K178" s="1" t="inlineStr"/>
       <c r="L178" s="1" t="inlineStr"/>
       <c r="M178" s="1" t="inlineStr"/>
       <c r="N178" s="1" t="inlineStr"/>
-      <c r="O178" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P178" s="1" t="inlineStr">
+      <c r="O178" s="1" t="inlineStr"/>
+      <c r="P178" s="1" t="inlineStr"/>
+      <c r="Q178" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R178" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9529,24 +9863,26 @@
           <t>Trapizzino</t>
         </is>
       </c>
-      <c r="G179" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G179" s="1" t="inlineStr"/>
       <c r="H179" s="1" t="inlineStr"/>
-      <c r="I179" s="1" t="inlineStr"/>
+      <c r="I179" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J179" s="1" t="inlineStr"/>
       <c r="K179" s="1" t="inlineStr"/>
       <c r="L179" s="1" t="inlineStr"/>
       <c r="M179" s="1" t="inlineStr"/>
       <c r="N179" s="1" t="inlineStr"/>
-      <c r="O179" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P179" s="1" t="inlineStr">
+      <c r="O179" s="1" t="inlineStr"/>
+      <c r="P179" s="1" t="inlineStr"/>
+      <c r="Q179" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R179" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>
@@ -9583,24 +9919,26 @@
           <t>vanillatorino</t>
         </is>
       </c>
-      <c r="G180" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
+      <c r="G180" s="1" t="inlineStr"/>
       <c r="H180" s="1" t="inlineStr"/>
-      <c r="I180" s="1" t="inlineStr"/>
+      <c r="I180" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
       <c r="J180" s="1" t="inlineStr"/>
       <c r="K180" s="1" t="inlineStr"/>
       <c r="L180" s="1" t="inlineStr"/>
       <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="inlineStr"/>
-      <c r="O180" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="P180" s="1" t="inlineStr">
+      <c r="O180" s="1" t="inlineStr"/>
+      <c r="P180" s="1" t="inlineStr"/>
+      <c r="Q180" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R180" s="1" t="inlineStr">
         <is>
           <t>18/04/2026</t>
         </is>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -566,6 +566,16 @@
           <t>chef-andrea-larossa</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -648,6 +658,16 @@
           <t>chiodilatininewfood</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -730,6 +750,16 @@
           <t>cannavacciuolobistrotorino</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -792,6 +822,16 @@
           <t>ristorantecondividere</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -854,6 +894,16 @@
           <t>lapistarestaurant</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -916,6 +966,16 @@
           <t>opera_torino</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -971,6 +1031,11 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>ristorante_santommaso10</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1074,6 +1139,11 @@
           <t>ballatoiobistrot</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -1156,8 +1226,16 @@
           <t>betweenristorante</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr"/>
-      <c r="H11" s="1" t="inlineStr"/>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1303,8 +1381,16 @@
           <t>contesto_alimentare</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr"/>
-      <c r="H14" s="1" t="inlineStr"/>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1359,8 +1445,16 @@
           <t>cubiquetorino</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr"/>
-      <c r="H15" s="1" t="inlineStr"/>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1415,8 +1509,16 @@
           <t>gaudenziovinoecucina</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr"/>
-      <c r="H16" s="1" t="inlineStr"/>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1471,8 +1573,16 @@
           <t>Ildepositobistrot</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr"/>
-      <c r="H17" s="1" t="inlineStr"/>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1527,8 +1637,16 @@
           <t>ristoranteinsieme</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr"/>
-      <c r="H18" s="1" t="inlineStr"/>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1583,8 +1701,16 @@
           <t>la_limonaia_</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr"/>
-      <c r="H19" s="1" t="inlineStr"/>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1639,8 +1765,16 @@
           <t>trattoria.la_madia</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1695,8 +1829,16 @@
           <t>magazzino52</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="inlineStr"/>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1795,8 +1937,16 @@
           <t>raffaleo_ristorante_enoteca</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr"/>
-      <c r="H23" s="1" t="inlineStr"/>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1847,8 +1997,16 @@
           <t>razzo__</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr"/>
-      <c r="H24" s="1" t="inlineStr"/>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1903,8 +2061,16 @@
           <t>costardibros</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr"/>
-      <c r="H25" s="1" t="inlineStr"/>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -1955,8 +2121,16 @@
           <t>siloscucinasincera</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr"/>
-      <c r="H26" s="1" t="inlineStr"/>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2099,8 +2273,16 @@
           <t>tuorloristorante</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr"/>
-      <c r="H29" s="1" t="inlineStr"/>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2155,6 +2337,16 @@
           <t>aroma_ristorante</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -2237,8 +2429,16 @@
           <t>ristoranteconsorzio</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr"/>
-      <c r="H31" s="1" t="inlineStr"/>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2293,8 +2493,16 @@
           <t>cucina_rambaldi</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr"/>
-      <c r="H32" s="1" t="inlineStr"/>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2393,8 +2601,16 @@
           <t>feliceatestaccio</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr"/>
-      <c r="H34" s="1" t="inlineStr"/>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2449,8 +2665,16 @@
           <t>gousto_torino</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr"/>
-      <c r="H35" s="1" t="inlineStr"/>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2725,8 +2949,16 @@
           <t>fanfaron_bistrot</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2781,8 +3013,16 @@
           <t>lescodelle_torino</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr"/>
-      <c r="H42" s="1" t="inlineStr"/>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2837,8 +3077,16 @@
           <t>le_vitel_etonne</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr"/>
-      <c r="H43" s="1" t="inlineStr"/>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2893,8 +3141,16 @@
           <t>madama_piola</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr"/>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -2949,8 +3205,16 @@
           <t>andirivieniosteria</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" s="1" t="inlineStr"/>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I45" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3005,8 +3269,16 @@
           <t>sangiorstorino</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr"/>
-      <c r="H46" s="1" t="inlineStr"/>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3061,8 +3333,16 @@
           <t>Scannabuecaffe</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I47" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3113,8 +3393,16 @@
           <t>smokingwinebar</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3169,8 +3457,16 @@
           <t>trattoria_amicizia</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr"/>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3357,8 +3653,16 @@
           <t>parlapatorino</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr"/>
-      <c r="H53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I53" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3403,6 +3707,11 @@
           <t>osteriaantichesere</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -3617,8 +3926,16 @@
           <t>ducesari</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr"/>
-      <c r="H58" s="1" t="inlineStr"/>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3673,8 +3990,16 @@
           <t>fratellibruzzone</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr"/>
-      <c r="H59" s="1" t="inlineStr"/>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3773,8 +4098,16 @@
           <t>le_ramine</t>
         </is>
       </c>
-      <c r="G61" s="1" t="inlineStr"/>
-      <c r="H61" s="1" t="inlineStr"/>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I61" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3873,8 +4206,16 @@
           <t>osteria_nuova_torino</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr"/>
-      <c r="H63" s="1" t="inlineStr"/>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -3970,7 +4311,11 @@
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr"/>
-      <c r="H65" s="1" t="inlineStr"/>
+      <c r="H65" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I65" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4113,6 +4458,16 @@
           <t>azotea_to</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -4239,8 +4594,16 @@
           <t>donburihouse_</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr"/>
-      <c r="H70" s="1" t="inlineStr"/>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H70" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4295,8 +4658,16 @@
           <t>elbeso_torino</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr"/>
-      <c r="H71" s="1" t="inlineStr"/>
+      <c r="G71" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H71" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4344,7 +4715,11 @@
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr"/>
-      <c r="H72" s="1" t="inlineStr"/>
+      <c r="H72" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I72" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4399,8 +4774,16 @@
           <t>Kayessenzaperuviana</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr"/>
-      <c r="H73" s="1" t="inlineStr"/>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I73" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4448,7 +4831,11 @@
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr"/>
-      <c r="H74" s="1" t="inlineStr"/>
+      <c r="H74" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I74" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4499,8 +4886,16 @@
           <t>lostranierotorino</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H75" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4555,8 +4950,16 @@
           <t>tuttofabrodo_official</t>
         </is>
       </c>
-      <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
+      <c r="G76" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H76" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I76" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4611,8 +5014,16 @@
           <t>ristorante.valeunperu</t>
         </is>
       </c>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4704,7 +5115,11 @@
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
+      <c r="H79" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I79" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -4759,7 +5174,11 @@
           <t>ristorante_zheng_yang_torino</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr"/>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
         <is>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -1109,7 +1109,7 @@
       </c>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="R11" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="R12" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1410,71 +1410,64 @@
       </c>
       <c r="R14" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Cubique</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Via Saluzzo 86/B</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>011/4149886</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>www.cubique.it</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>cubiquetorino</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>cubiquetorino</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr"/>
-      <c r="L15" s="1" t="inlineStr"/>
-      <c r="M15" s="1" t="inlineStr"/>
-      <c r="N15" s="1" t="inlineStr"/>
-      <c r="O15" s="1" t="inlineStr"/>
-      <c r="P15" s="1" t="inlineStr"/>
-      <c r="Q15" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R15" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 02/04/2026</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1531,7 @@
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1595,7 @@
       </c>
       <c r="R17" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1659,7 @@
       </c>
       <c r="R18" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1723,7 @@
       </c>
       <c r="R19" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1787,7 @@
       </c>
       <c r="R20" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1851,7 @@
       </c>
       <c r="R21" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1895,7 @@
       </c>
       <c r="R22" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1959,7 @@
       </c>
       <c r="R23" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2019,7 @@
       </c>
       <c r="R24" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2090,67 +2083,59 @@
       </c>
       <c r="R25" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Silos</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Via Santa Giulia, 21/A</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>011/7633404</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr"/>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>silos.torino</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>siloscucinasincera</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr"/>
-      <c r="L26" s="1" t="inlineStr"/>
-      <c r="M26" s="1" t="inlineStr"/>
-      <c r="N26" s="1" t="inlineStr"/>
-      <c r="O26" s="1" t="inlineStr"/>
-      <c r="P26" s="1" t="inlineStr"/>
-      <c r="Q26" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R26" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 15/04/2026</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2179,7 @@
       </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2223,7 @@
       </c>
       <c r="R28" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2287,7 @@
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2443,7 @@
       </c>
       <c r="R31" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2507,7 @@
       </c>
       <c r="R32" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2551,7 @@
       </c>
       <c r="R33" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2615,7 @@
       </c>
       <c r="R34" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2679,7 @@
       </c>
       <c r="R35" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2723,7 @@
       </c>
       <c r="R36" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2767,7 @@
       </c>
       <c r="R37" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2811,7 @@
       </c>
       <c r="R38" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2855,7 @@
       </c>
       <c r="R39" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2899,7 @@
       </c>
       <c r="R40" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2963,7 @@
       </c>
       <c r="R41" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3027,7 @@
       </c>
       <c r="R42" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3091,7 @@
       </c>
       <c r="R43" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3155,7 @@
       </c>
       <c r="R44" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3219,7 @@
       </c>
       <c r="R45" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3283,7 @@
       </c>
       <c r="R46" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3347,7 @@
       </c>
       <c r="R47" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3407,7 @@
       </c>
       <c r="R48" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3471,7 @@
       </c>
       <c r="R49" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3515,7 @@
       </c>
       <c r="R50" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3559,7 @@
       </c>
       <c r="R51" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3603,7 @@
       </c>
       <c r="R52" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3667,7 @@
       </c>
       <c r="R53" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3788,7 @@
       </c>
       <c r="R55" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3832,7 @@
       </c>
       <c r="R56" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3876,7 @@
       </c>
       <c r="R57" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3940,7 @@
       </c>
       <c r="R58" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4004,7 @@
       </c>
       <c r="R59" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4048,7 @@
       </c>
       <c r="R60" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4127,7 +4112,7 @@
       </c>
       <c r="R61" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4156,7 @@
       </c>
       <c r="R62" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4220,7 @@
       </c>
       <c r="R63" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4264,7 @@
       </c>
       <c r="R64" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4320,7 @@
       </c>
       <c r="R65" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4364,7 @@
       </c>
       <c r="R66" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4408,7 @@
       </c>
       <c r="R67" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4544,7 @@
       </c>
       <c r="R69" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4608,7 @@
       </c>
       <c r="R70" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4672,7 @@
       </c>
       <c r="R71" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4724,7 @@
       </c>
       <c r="R72" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4788,7 @@
       </c>
       <c r="R73" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4840,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4900,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4964,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5028,7 @@
       </c>
       <c r="R77" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5072,7 @@
       </c>
       <c r="R78" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5124,7 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5164,11 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr"/>
+      <c r="H80" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5199,7 +5188,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5232,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5264,11 @@
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
+      <c r="H82" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I82" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5295,7 +5288,7 @@
       </c>
       <c r="R82" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5330,8 +5323,16 @@
           <t>Berberepizzeria</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5351,7 +5352,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5386,8 +5387,16 @@
           <t>_da_zero</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5407,7 +5416,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5460,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5486,8 +5495,16 @@
           <t>fuzion_torino</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I86" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5507,7 +5524,7 @@
       </c>
       <c r="R86" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5568,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5600,11 @@
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
+      <c r="H88" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I88" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5603,7 +5624,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5638,8 +5659,16 @@
           <t>aforisma_pizzeria_gourmet</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I89" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5659,7 +5688,7 @@
       </c>
       <c r="R89" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5694,8 +5723,16 @@
           <t>sestogustotorino</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I90" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5715,7 +5752,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5784,11 @@
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
+      <c r="H91" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I91" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5767,7 +5808,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5852,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5846,8 +5887,16 @@
           <t>caffesancarlo_torino</t>
         </is>
       </c>
-      <c r="G93" s="1" t="inlineStr"/>
-      <c r="H93" s="1" t="inlineStr"/>
+      <c r="G93" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H93" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I93" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5867,7 +5916,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5960,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5946,8 +5995,16 @@
           <t>dappercoffeetorino</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr"/>
-      <c r="H95" s="1" t="inlineStr"/>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I95" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5967,7 +6024,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6068,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6046,8 +6103,16 @@
           <t>goccedicioccolato_torino</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr"/>
-      <c r="H97" s="1" t="inlineStr"/>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I97" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6067,7 +6132,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6102,8 +6167,16 @@
           <t>orsolaboratoriocaffe</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr"/>
-      <c r="H98" s="1" t="inlineStr"/>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I98" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6123,7 +6196,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6158,8 +6231,16 @@
           <t>pasticceriasabauda</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr"/>
-      <c r="H99" s="1" t="inlineStr"/>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H99" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I99" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6179,7 +6260,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6210,8 +6291,16 @@
           <t>pasticceriavenier</t>
         </is>
       </c>
-      <c r="G100" s="1" t="inlineStr"/>
-      <c r="H100" s="1" t="inlineStr"/>
+      <c r="G100" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H100" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6231,7 +6320,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6352,11 @@
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr"/>
-      <c r="H101" s="1" t="inlineStr"/>
+      <c r="H101" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I101" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6283,7 +6376,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6420,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6360,6 +6453,16 @@
       <c r="F103" t="inlineStr">
         <is>
           <t>adoniscreperie</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6453,7 +6556,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6488,8 +6591,16 @@
           <t>caffemulassano</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr"/>
-      <c r="H105" s="1" t="inlineStr"/>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I105" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6509,7 +6620,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6544,8 +6655,16 @@
           <t>koitorino</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr"/>
-      <c r="H106" s="1" t="inlineStr"/>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6565,7 +6684,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6596,8 +6715,16 @@
           <t>kokoroyatorino</t>
         </is>
       </c>
-      <c r="G107" s="1" t="inlineStr"/>
-      <c r="H107" s="1" t="inlineStr"/>
+      <c r="G107" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H107" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I107" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6617,7 +6744,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6788,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6832,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6859,11 @@
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr"/>
-      <c r="G110" s="1" t="inlineStr"/>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
@@ -6753,7 +6884,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6928,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6832,8 +6963,16 @@
           <t>beppe_gallina</t>
         </is>
       </c>
-      <c r="G112" s="1" t="inlineStr"/>
-      <c r="H112" s="1" t="inlineStr"/>
+      <c r="G112" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H112" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I112" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6853,7 +6992,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6897,7 +7036,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6932,8 +7071,16 @@
           <t>smithsbritish</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr"/>
-      <c r="H114" s="1" t="inlineStr"/>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I114" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6953,7 +7100,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -6997,7 +7144,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7032,8 +7179,16 @@
           <t>tiffanybistrot</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr"/>
-      <c r="H116" s="1" t="inlineStr"/>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I116" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7053,7 +7208,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7088,6 +7243,16 @@
           <t>bicerin.1763.torino</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -7170,8 +7335,16 @@
           <t>camellia.torino</t>
         </is>
       </c>
-      <c r="G118" s="1" t="inlineStr"/>
-      <c r="H118" s="1" t="inlineStr"/>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7191,7 +7364,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7412,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7270,8 +7443,16 @@
           <t>kintsugiteandcakes</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr"/>
-      <c r="H120" s="1" t="inlineStr"/>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I120" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7291,7 +7472,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7516,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7366,8 +7547,16 @@
           <t>tarta.teatorteria</t>
         </is>
       </c>
-      <c r="G122" s="1" t="inlineStr"/>
-      <c r="H122" s="1" t="inlineStr"/>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H122" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I122" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7387,7 +7576,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7422,8 +7611,16 @@
           <t>thetea.torino</t>
         </is>
       </c>
-      <c r="G123" s="1" t="inlineStr"/>
-      <c r="H123" s="1" t="inlineStr"/>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H123" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I123" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7443,7 +7640,7 @@
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7478,8 +7675,16 @@
           <t>olsentorteria</t>
         </is>
       </c>
-      <c r="G124" s="1" t="inlineStr"/>
-      <c r="H124" s="1" t="inlineStr"/>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H124" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I124" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7499,7 +7704,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7748,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7578,8 +7783,16 @@
           <t>caffedellorologiotorino</t>
         </is>
       </c>
-      <c r="G126" s="1" t="inlineStr"/>
-      <c r="H126" s="1" t="inlineStr"/>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H126" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I126" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7599,7 +7812,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7840,11 @@
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr"/>
-      <c r="H127" s="1" t="inlineStr"/>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I127" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7647,7 +7864,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7908,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7939,11 @@
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr"/>
-      <c r="G129" s="1" t="inlineStr"/>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
@@ -7743,7 +7964,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7778,8 +7999,16 @@
           <t>palto.torino</t>
         </is>
       </c>
-      <c r="G130" s="1" t="inlineStr"/>
-      <c r="H130" s="1" t="inlineStr"/>
+      <c r="G130" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H130" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I130" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7799,7 +8028,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7831,7 +8060,11 @@
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr"/>
-      <c r="H131" s="1" t="inlineStr"/>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I131" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7851,7 +8084,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7886,8 +8119,16 @@
           <t>rossorubino.enoteca</t>
         </is>
       </c>
-      <c r="G132" s="1" t="inlineStr"/>
-      <c r="H132" s="1" t="inlineStr"/>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H132" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I132" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7907,7 +8148,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7951,7 +8192,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -7986,8 +8227,16 @@
           <t>tastumatorino</t>
         </is>
       </c>
-      <c r="G134" s="1" t="inlineStr"/>
-      <c r="H134" s="1" t="inlineStr"/>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H134" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I134" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8007,7 +8256,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8300,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8095,7 +8344,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8388,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8416,11 @@
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr"/>
-      <c r="H138" s="1" t="inlineStr"/>
+      <c r="H138" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I138" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8187,7 +8440,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8484,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8275,7 +8528,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8572,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8354,8 +8607,16 @@
           <t>recina-focaccia-e-cucina</t>
         </is>
       </c>
-      <c r="G142" s="1" t="inlineStr"/>
-      <c r="H142" s="1" t="inlineStr"/>
+      <c r="G142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I142" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8375,7 +8636,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8680,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8452,6 +8713,16 @@
       <c r="F144" t="inlineStr">
         <is>
           <t>affinitorino</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8545,7 +8816,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8860,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8620,8 +8891,16 @@
           <t>donetorino</t>
         </is>
       </c>
-      <c r="G147" s="1" t="inlineStr"/>
-      <c r="H147" s="1" t="inlineStr"/>
+      <c r="G147" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H147" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I147" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8641,7 +8920,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8685,7 +8964,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8720,8 +8999,16 @@
           <t>smile_tree_torino</t>
         </is>
       </c>
-      <c r="G149" s="1" t="inlineStr"/>
-      <c r="H149" s="1" t="inlineStr"/>
+      <c r="G149" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H149" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I149" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8741,7 +9028,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8785,7 +9072,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8820,6 +9107,16 @@
           <t>alberto_marchetti_gelaterie</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -8898,8 +9195,16 @@
           <t>aria_gelateria</t>
         </is>
       </c>
-      <c r="G152" s="1" t="inlineStr"/>
-      <c r="H152" s="1" t="inlineStr"/>
+      <c r="G152" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H152" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I152" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8919,7 +9224,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -8963,7 +9268,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9312,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9042,8 +9347,16 @@
           <t>_conogelato_</t>
         </is>
       </c>
-      <c r="G155" s="1" t="inlineStr"/>
-      <c r="H155" s="1" t="inlineStr"/>
+      <c r="G155" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H155" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I155" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9063,7 +9376,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9420,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9142,8 +9455,16 @@
           <t>gaspringelatoedelizie</t>
         </is>
       </c>
-      <c r="G157" s="1" t="inlineStr"/>
-      <c r="H157" s="1" t="inlineStr"/>
+      <c r="G157" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H157" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I157" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9163,7 +9484,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9528,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9572,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9286,8 +9607,16 @@
           <t>gelateria_miretti</t>
         </is>
       </c>
-      <c r="G160" s="1" t="inlineStr"/>
-      <c r="H160" s="1" t="inlineStr"/>
+      <c r="G160" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H160" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I160" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9307,7 +9636,7 @@
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9680,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9386,8 +9715,16 @@
           <t>gofreriapiemonteisa</t>
         </is>
       </c>
-      <c r="G162" s="1" t="inlineStr"/>
-      <c r="H162" s="1" t="inlineStr"/>
+      <c r="G162" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H162" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I162" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9407,7 +9744,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9788,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9815,11 @@
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr"/>
-      <c r="G164" s="1" t="inlineStr"/>
+      <c r="G164" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H164" s="1" t="inlineStr"/>
       <c r="I164" s="1" t="inlineStr">
         <is>
@@ -9499,7 +9840,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9534,8 +9875,16 @@
           <t>macbun_official</t>
         </is>
       </c>
-      <c r="G165" s="1" t="inlineStr"/>
-      <c r="H165" s="1" t="inlineStr"/>
+      <c r="G165" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H165" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I165" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9555,7 +9904,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9590,8 +9939,16 @@
           <t>maradeiboschi</t>
         </is>
       </c>
-      <c r="G166" s="1" t="inlineStr"/>
-      <c r="H166" s="1" t="inlineStr"/>
+      <c r="G166" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H166" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I166" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9611,7 +9968,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9646,8 +10003,16 @@
           <t>margheripizza</t>
         </is>
       </c>
-      <c r="G167" s="1" t="inlineStr"/>
-      <c r="H167" s="1" t="inlineStr"/>
+      <c r="G167" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H167" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I167" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9667,7 +10032,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9711,7 +10076,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9742,8 +10107,16 @@
           <t>modo_gelato</t>
         </is>
       </c>
-      <c r="G169" s="1" t="inlineStr"/>
-      <c r="H169" s="1" t="inlineStr"/>
+      <c r="G169" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H169" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I169" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9763,7 +10136,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9798,8 +10171,16 @@
           <t>nivagelato</t>
         </is>
       </c>
-      <c r="G170" s="1" t="inlineStr"/>
-      <c r="H170" s="1" t="inlineStr"/>
+      <c r="G170" s="1" t="inlineStr">
+        <is>
+          <t>03/01/2026</t>
+        </is>
+      </c>
+      <c r="H170" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I170" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9819,115 +10200,111 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="inlineStr">
+      <c r="A171" t="inlineStr">
         <is>
           <t>Ottimo!</t>
         </is>
       </c>
-      <c r="B171" s="1" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Corso Stati Uniti, 6/C</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>340/6414542</t>
         </is>
       </c>
-      <c r="D171" s="1" t="inlineStr"/>
-      <c r="E171" s="1" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>ottimobuonononbasta</t>
         </is>
       </c>
-      <c r="F171" s="1" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>ottimogelati</t>
         </is>
       </c>
-      <c r="G171" s="1" t="inlineStr"/>
-      <c r="H171" s="1" t="inlineStr"/>
-      <c r="I171" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J171" s="1" t="inlineStr"/>
-      <c r="K171" s="1" t="inlineStr"/>
-      <c r="L171" s="1" t="inlineStr"/>
-      <c r="M171" s="1" t="inlineStr"/>
-      <c r="N171" s="1" t="inlineStr"/>
-      <c r="O171" s="1" t="inlineStr"/>
-      <c r="P171" s="1" t="inlineStr"/>
-      <c r="Q171" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R171" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 05/04/2026</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="inlineStr">
+      <c r="A172" t="inlineStr">
         <is>
           <t>Papalele</t>
         </is>
       </c>
-      <c r="B172" s="1" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Corso Guglielmo Marconi, 23/A</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>011/9776990</t>
         </is>
       </c>
-      <c r="D172" s="1" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>www.papalele.it</t>
         </is>
       </c>
-      <c r="E172" s="1" t="inlineStr">
+      <c r="E172" t="inlineStr">
         <is>
           <t>papalele.gelatiepasticci</t>
         </is>
       </c>
-      <c r="F172" s="1" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>papalele.gelatiepasticci</t>
         </is>
       </c>
-      <c r="G172" s="1" t="inlineStr"/>
-      <c r="H172" s="1" t="inlineStr"/>
-      <c r="I172" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J172" s="1" t="inlineStr"/>
-      <c r="K172" s="1" t="inlineStr"/>
-      <c r="L172" s="1" t="inlineStr"/>
-      <c r="M172" s="1" t="inlineStr"/>
-      <c r="N172" s="1" t="inlineStr"/>
-      <c r="O172" s="1" t="inlineStr"/>
-      <c r="P172" s="1" t="inlineStr"/>
-      <c r="Q172" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R172" s="1" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 12/04/2026</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -9983,7 +10360,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10412,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10456,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10512,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10191,7 +10568,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10624,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10680,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10736,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1070,46 +1070,39 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Via Valprato, 68</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>348/7837783</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr"/>
-      <c r="E9" s="1" t="inlineStr"/>
-      <c r="F9" s="1" t="inlineStr"/>
-      <c r="G9" s="1" t="inlineStr"/>
-      <c r="H9" s="1" t="inlineStr"/>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr"/>
-      <c r="L9" s="1" t="inlineStr"/>
-      <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
-      <c r="O9" s="1" t="inlineStr"/>
-      <c r="P9" s="1" t="inlineStr"/>
-      <c r="Q9" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R9" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>GBP aperto, inaugurato gen 2026 ai Docks Dora, attivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1196,110 +1189,101 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Between</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Viale Partigiani d’Italia, 98/C</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>011/9451900 - 328/6425306</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>www.betweenristorante.it</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>betweenristorante</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>betweenristorante</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr"/>
-      <c r="L11" s="1" t="inlineStr"/>
-      <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr"/>
-      <c r="O11" s="1" t="inlineStr"/>
-      <c r="P11" s="1" t="inlineStr"/>
-      <c r="Q11" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R11" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2025 a Rivoli, TripAdvisor attivo apr 2026</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Brace Pura</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Via Roero di Cortanze, 2</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>011/8600124</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr"/>
-      <c r="E12" s="1" t="inlineStr"/>
-      <c r="F12" s="1" t="inlineStr"/>
-      <c r="G12" s="1" t="inlineStr"/>
-      <c r="H12" s="1" t="inlineStr"/>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr"/>
-      <c r="L12" s="1" t="inlineStr"/>
-      <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
-      <c r="O12" s="1" t="inlineStr"/>
-      <c r="P12" s="1" t="inlineStr"/>
-      <c r="Q12" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R12" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>GBP aperto, articolo Piazza Pinerolese 11/03/2026, chef Trentini attivo</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1351,66 +1335,64 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Contesto Alimentare</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Via Accademia Albertina, 21/E</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>011/8178698</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>www.contestoalimentare.it</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>contestoalimentare</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>contesto_alimentare</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr"/>
-      <c r="L14" s="1" t="inlineStr"/>
-      <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="1" t="inlineStr"/>
-      <c r="O14" s="1" t="inlineStr"/>
-      <c r="P14" s="1" t="inlineStr"/>
-      <c r="Q14" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R14" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin BibGourmand 2025, TheFork attivo, sito attivo</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1429,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1460,630 +1442,609 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Promosso ad APERTO: post Facebook del 02/04/2026</t>
+          <t>GBP aperto, sito cubique.it attivo, orari disponibili</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Gaudenzio Vino e Cucina</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Via Gaudenzio Ferrari, 2/H</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>011/8600242</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>www.gaudenziovinoecucina.it</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>gaudenziovinoecucina</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>gaudenziovinoecucina</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr"/>
-      <c r="L16" s="1" t="inlineStr"/>
-      <c r="M16" s="1" t="inlineStr"/>
-      <c r="N16" s="1" t="inlineStr"/>
-      <c r="O16" s="1" t="inlineStr"/>
-      <c r="P16" s="1" t="inlineStr"/>
-      <c r="Q16" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R16" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>GBP aperto, menù 2026 su TheFork, sito gaudenziovinoecucina.it attivo</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Il Deposito</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Via Ercole Ricotti, 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>011/0200239</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>www.ildepositobistrot.it</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>ildepositobistrot</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Ildepositobistrot</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr"/>
-      <c r="L17" s="1" t="inlineStr"/>
-      <c r="M17" s="1" t="inlineStr"/>
-      <c r="N17" s="1" t="inlineStr"/>
-      <c r="O17" s="1" t="inlineStr"/>
-      <c r="P17" s="1" t="inlineStr"/>
-      <c r="Q17" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R17" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>GBP aperto, sito ildepositobistrot.it attivo, Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Insieme dal Clandestino</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Via Provana, 3/B</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>011/889494</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>www.ristoranteinsieme.it</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>ristoranteinsiemetorino</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>ristoranteinsieme</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H18" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr"/>
-      <c r="L18" s="1" t="inlineStr"/>
-      <c r="M18" s="1" t="inlineStr"/>
-      <c r="N18" s="1" t="inlineStr"/>
-      <c r="O18" s="1" t="inlineStr"/>
-      <c r="P18" s="1" t="inlineStr"/>
-      <c r="Q18" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R18" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>GBP aperto, articolo Gambero Rosso apr 2026, tra migliori pranzi Torino</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>La Limonaia</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Via Mario Ponzio, 10</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>011/7041887</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>www.lalimonaia.org</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>lalimonaiaFoodasCulture</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>la_limonaia_</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H19" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr"/>
-      <c r="L19" s="1" t="inlineStr"/>
-      <c r="M19" s="1" t="inlineStr"/>
-      <c r="N19" s="1" t="inlineStr"/>
-      <c r="O19" s="1" t="inlineStr"/>
-      <c r="P19" s="1" t="inlineStr"/>
-      <c r="Q19" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R19" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, JRE associato, sito lalimonaia.org attivo</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>La Madia</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Corso Quintino Sella, 85/A</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>011/8190028</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>www.ristorantelamadiatorino.it</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>trattorialamadia</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>trattoria.la_madia</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr"/>
-      <c r="L20" s="1" t="inlineStr"/>
-      <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="inlineStr"/>
-      <c r="O20" s="1" t="inlineStr"/>
-      <c r="P20" s="1" t="inlineStr"/>
-      <c r="Q20" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R20" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>GBP aperto, TheFork attivo, sito ristorantelamadiatorino.it attivo</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Magazzino 52</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Via Giolitti, 52/A</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>011/4271938</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>www.magazzino52.it</t>
         </is>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>magazzino52</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>magazzino52</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr"/>
-      <c r="L21" s="1" t="inlineStr"/>
-      <c r="M21" s="1" t="inlineStr"/>
-      <c r="N21" s="1" t="inlineStr"/>
-      <c r="O21" s="1" t="inlineStr"/>
-      <c r="P21" s="1" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R21" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin BibGourmand 2025, Yelp apr 2026</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Marchese</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Via Massena, 5</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>011/3358869</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr"/>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr"/>
-      <c r="G22" s="1" t="inlineStr"/>
-      <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr"/>
-      <c r="L22" s="1" t="inlineStr"/>
-      <c r="M22" s="1" t="inlineStr"/>
-      <c r="N22" s="1" t="inlineStr"/>
-      <c r="O22" s="1" t="inlineStr"/>
-      <c r="P22" s="1" t="inlineStr"/>
-      <c r="Q22" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R22" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>GBP aperto, prenotazioni attive da 06/02/2026, sito ristorantemarchese.it</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Raffaleo</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Via Piave, 5/M</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>011/18925548</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>www.raffaleo.it</t>
         </is>
       </c>
-      <c r="E23" s="1" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>raffaleoristoranteenoteca</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>raffaleo_ristorante_enoteca</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr"/>
-      <c r="L23" s="1" t="inlineStr"/>
-      <c r="M23" s="1" t="inlineStr"/>
-      <c r="N23" s="1" t="inlineStr"/>
-      <c r="O23" s="1" t="inlineStr"/>
-      <c r="P23" s="1" t="inlineStr"/>
-      <c r="Q23" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R23" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>GBP aperto, sito raffaleo.it attivo, TripAdvisor attivo</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Razzo</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Via Andrea Doria, 17/F</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>011/0201580</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr"/>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>RAZZO</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>razzo__</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr"/>
-      <c r="L24" s="1" t="inlineStr"/>
-      <c r="M24" s="1" t="inlineStr"/>
-      <c r="N24" s="1" t="inlineStr"/>
-      <c r="O24" s="1" t="inlineStr"/>
-      <c r="P24" s="1" t="inlineStr"/>
-      <c r="Q24" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R24" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, sito attivo, orari confermati</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Scatto</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Piazza San Carlo, 156</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>011/0267460</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>www.costardibros.it</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>CostardiBros</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>costardibros</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H25" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr"/>
-      <c r="L25" s="1" t="inlineStr"/>
-      <c r="M25" s="1" t="inlineStr"/>
-      <c r="N25" s="1" t="inlineStr"/>
-      <c r="O25" s="1" t="inlineStr"/>
-      <c r="P25" s="1" t="inlineStr"/>
-      <c r="Q25" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R25" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, Costardi Bros alle Gallerie d'Italia, attivo</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2128,166 +2089,155 @@
           <t>APERTO</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Promosso ad APERTO: post Facebook del 15/04/2026</t>
+          <t>GBP aperto, Wheree apr 2026, TheFork attivo</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Spirito Osteria</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Via Corte d'Appello, 13</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>011/4143523</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr"/>
-      <c r="G27" s="1" t="inlineStr"/>
-      <c r="H27" s="1" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr"/>
-      <c r="L27" s="1" t="inlineStr"/>
-      <c r="M27" s="1" t="inlineStr"/>
-      <c r="N27" s="1" t="inlineStr"/>
-      <c r="O27" s="1" t="inlineStr"/>
-      <c r="P27" s="1" t="inlineStr"/>
-      <c r="Q27" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R27" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>GBP aperto, articolo Tasting Life 24/03/2026, OpenTable prenotazioni</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Tratto</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Via Andrea Doria, 12</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>331/4694961</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr"/>
-      <c r="E28" s="1" t="inlineStr"/>
-      <c r="F28" s="1" t="inlineStr"/>
-      <c r="G28" s="1" t="inlineStr"/>
-      <c r="H28" s="1" t="inlineStr"/>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr"/>
-      <c r="L28" s="1" t="inlineStr"/>
-      <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="inlineStr"/>
-      <c r="O28" s="1" t="inlineStr"/>
-      <c r="P28" s="1" t="inlineStr"/>
-      <c r="Q28" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R28" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>GBP aperto, sito trattotorino.it attivo, TheFork 2026</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Tuorlo - vino e cucina</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Via Sant'Agostino, 15/B</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>011/19018061</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>www.tuorloristorante.it</t>
         </is>
       </c>
-      <c r="E29" s="1" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>tuorlovinoecucina</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>tuorloristorante</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr"/>
-      <c r="L29" s="1" t="inlineStr"/>
-      <c r="M29" s="1" t="inlineStr"/>
-      <c r="N29" s="1" t="inlineStr"/>
-      <c r="O29" s="1" t="inlineStr"/>
-      <c r="P29" s="1" t="inlineStr"/>
-      <c r="Q29" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R29" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin 2026, TheFork menù 2026, sito tuorloristorante.it</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -2384,1182 +2334,1099 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Consorzio</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Via Monte di Pietà, 23</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>011/2767661</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>www.ristoranteconsorzio.it</t>
         </is>
       </c>
-      <c r="E31" s="1" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>ConsorzioTorino</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>ristoranteconsorzio</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I31" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr"/>
-      <c r="L31" s="1" t="inlineStr"/>
-      <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr"/>
-      <c r="O31" s="1" t="inlineStr"/>
-      <c r="P31" s="1" t="inlineStr"/>
-      <c r="Q31" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R31" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GBP aperto, Michelin BibGourmand 2026, sito ristoranteconsorzio.it attivo</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Cucina Rambaldi</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Via Sant'Ambrogio, 55</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>011/0161808</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>www.cucinarambaldi.com</t>
         </is>
       </c>
-      <c r="E32" s="1" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>cucinarambaldi</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>cucina_rambaldi</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H32" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I32" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr"/>
-      <c r="L32" s="1" t="inlineStr"/>
-      <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="inlineStr"/>
-      <c r="O32" s="1" t="inlineStr"/>
-      <c r="P32" s="1" t="inlineStr"/>
-      <c r="Q32" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R32" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GBP aperto; recensioni 4-10 aprile 2026 (sede Villar Dora TO)</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>De Amicis Art Bistrot</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Corso Casale, 134</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>348/3716636</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr"/>
-      <c r="E33" s="1" t="inlineStr"/>
-      <c r="F33" s="1" t="inlineStr"/>
-      <c r="G33" s="1" t="inlineStr"/>
-      <c r="H33" s="1" t="inlineStr"/>
-      <c r="I33" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr"/>
-      <c r="L33" s="1" t="inlineStr"/>
-      <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr"/>
-      <c r="O33" s="1" t="inlineStr"/>
-      <c r="P33" s="1" t="inlineStr"/>
-      <c r="Q33" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R33" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>GBP aperto; orari aggiornati 20/02/2026; Wheree Updated April 2026</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Felice a Testaccio</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Via Pietro Micca, 17</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>011/0746328</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>www.feliceatestaccio.com</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Felice a Testaccio Torino</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>feliceatestaccio</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr"/>
-      <c r="L34" s="1" t="inlineStr"/>
-      <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr"/>
-      <c r="P34" s="1" t="inlineStr"/>
-      <c r="Q34" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R34" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>GBP aperto; TripAdvisor attivo; articolo Torino Magazine</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Goustò</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Piazza della Repubblica, 4</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>329/9415437</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>www.gousto.eu</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Goustò</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>gousto_torino</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H35" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I35" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr"/>
-      <c r="L35" s="1" t="inlineStr"/>
-      <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr"/>
-      <c r="O35" s="1" t="inlineStr"/>
-      <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R35" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>GBP aperto; TheFork 9.6/10 attivo</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Il Barbabuc</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Via Principe Tommaso, 16/A</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>011/2762804</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr"/>
-      <c r="E36" s="1" t="inlineStr"/>
-      <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="1" t="inlineStr"/>
-      <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr"/>
-      <c r="L36" s="1" t="inlineStr"/>
-      <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr"/>
-      <c r="O36" s="1" t="inlineStr"/>
-      <c r="P36" s="1" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R36" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>GBP aperto; TheFork Verified Reviews 2026; OpenTable Updated 2026</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>La cucina di Lido</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Corso Novara, 35</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>011/2075527</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr"/>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr"/>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr"/>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr"/>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R37" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>GBP aperto; sito attivo; 905 rec. RestaurantGuru</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>La Ferramenta del Gusto Emiliano</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Via Giuseppe Giacosa, 10/A</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>011/0607225</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr"/>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr"/>
-      <c r="L38" s="1" t="inlineStr"/>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr"/>
-      <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R38" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>GBP aperto; TheFork 9.6/10; recensioni 2026</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>La Locanda del Bollito</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Corso Palermo, 22</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>392/9306936</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr"/>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr"/>
-      <c r="L39" s="1" t="inlineStr"/>
-      <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr"/>
-      <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R39" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>GBP aperto; sito attivo; TripAdvisor attivo</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>La Via del Sale</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Via San Francesco da Paola, 2</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>011/888389</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr"/>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr"/>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R40" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated February 2026</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Le Fanfaron Bistrot</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Via Piave, 5/D</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>011/0410161</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>www.fanfaron.it</t>
         </is>
       </c>
-      <c r="E41" s="1" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>lefanfaronbistrot</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>fanfaron_bistrot</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H41" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I41" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr"/>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R41" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>GBP aperto; sito attivo; RestaurantGuru 3387 rec.</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Le Scodelle</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Via Stampatori, 16/C</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>011/7641623</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>www.lescodelle.com</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>LeScodelle</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>lescodelle_torino</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H42" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I42" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr"/>
-      <c r="L42" s="1" t="inlineStr"/>
-      <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr"/>
-      <c r="P42" s="1" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R42" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>GBP aperto; TheFork Verified Reviews 2026; rec. 25 marzo 2026</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Le Vitel Étonné</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Via San Francesco da Paola, 4</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>011/8124621</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>www.leviteletonne.com</t>
         </is>
       </c>
-      <c r="E43" s="1" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>VITELLOGIOELE</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>le_vitel_etonne</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H43" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I43" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr"/>
-      <c r="L43" s="1" t="inlineStr"/>
-      <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr"/>
-      <c r="P43" s="1" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R43" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated April 2026</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Madama Piola</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Via Ormea, 6/bis</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>011/0209588</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>www.madamapiolatorino.it</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>madamapiola2019</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>madama_piola</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H44" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I44" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr"/>
-      <c r="L44" s="1" t="inlineStr"/>
-      <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr"/>
-      <c r="P44" s="1" t="inlineStr"/>
-      <c r="Q44" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R44" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>GBP aperto; Michelin 2026; 1271 rec. RestaurantGuru</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Osteria Andirivieni</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Via Edoardo Rubino, 43/A</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>011/19503860</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>www.andirivienitorino.it</t>
         </is>
       </c>
-      <c r="E45" s="1" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>andirivieniosteria</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>andirivieniosteria</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H45" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I45" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr"/>
-      <c r="L45" s="1" t="inlineStr"/>
-      <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr"/>
-      <c r="P45" s="1" t="inlineStr"/>
-      <c r="Q45" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R45" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>GBP aperto; Osterie d'Italia 2026; sito attivo</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>San Giors</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Via Borgo Dora, 3/A</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>011/5216357</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>www.sangiors.it</t>
         </is>
       </c>
-      <c r="E46" s="1" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>sangiorstorino</t>
         </is>
       </c>
-      <c r="F46" s="1" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>sangiorstorino</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H46" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I46" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr"/>
-      <c r="L46" s="1" t="inlineStr"/>
-      <c r="M46" s="1" t="inlineStr"/>
-      <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr"/>
-      <c r="P46" s="1" t="inlineStr"/>
-      <c r="Q46" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R46" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>GBP aperto; sito attivo; TripAdvisor attivo</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Scannabue</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Largo Saluzzo, 25/H</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>011/6696693</t>
         </is>
       </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>www.scannabue.it</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Scannabue</t>
         </is>
       </c>
-      <c r="F47" s="1" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Scannabuecaffe</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H47" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I47" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr"/>
-      <c r="L47" s="1" t="inlineStr"/>
-      <c r="M47" s="1" t="inlineStr"/>
-      <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
-      <c r="P47" s="1" t="inlineStr"/>
-      <c r="Q47" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R47" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated September 2025; Bib Gourmand Michelin</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Smoking Bar</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Strada Comunale Val San Martino, 4</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>349/1799842</t>
         </is>
       </c>
-      <c r="D48" s="1" t="inlineStr"/>
-      <c r="E48" s="1" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>smokingbartorino</t>
         </is>
       </c>
-      <c r="F48" s="1" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>smokingwinebar</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H48" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I48" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr"/>
-      <c r="L48" s="1" t="inlineStr"/>
-      <c r="M48" s="1" t="inlineStr"/>
-      <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr"/>
-      <c r="P48" s="1" t="inlineStr"/>
-      <c r="Q48" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R48" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>GBP aperto; Facebook/Instagram attivi; eventi 2026</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Trattoria Amicizia</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Via Cardinal Massaia, 7</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>011/290912</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>www.trattoriamicizia.it</t>
         </is>
       </c>
-      <c r="E49" s="1" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>trattoriamicizia</t>
         </is>
       </c>
-      <c r="F49" s="1" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>trattoria_amicizia</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H49" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I49" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr"/>
-      <c r="L49" s="1" t="inlineStr"/>
-      <c r="M49" s="1" t="inlineStr"/>
-      <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr"/>
-      <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R49" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>GBP aperto; Wheree Updated April 2026; TheFork 9.2/10</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Trattoria Tarassaco</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Via Avigliana, 13</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>011/4112565</t>
         </is>
       </c>
-      <c r="D50" s="1" t="inlineStr"/>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr"/>
-      <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr"/>
-      <c r="L50" s="1" t="inlineStr"/>
-      <c r="M50" s="1" t="inlineStr"/>
-      <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr"/>
-      <c r="P50" s="1" t="inlineStr"/>
-      <c r="Q50" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R50" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>GBP aperto; articolo Monsubarachin 3 feb 2026; I Cento di Torino 2026</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Tre Galli</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Via Sant'Agostino, 25</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>011/5216027</t>
         </is>
       </c>
-      <c r="D51" s="1" t="inlineStr"/>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr"/>
-      <c r="G51" s="1" t="inlineStr"/>
-      <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr"/>
-      <c r="L51" s="1" t="inlineStr"/>
-      <c r="M51" s="1" t="inlineStr"/>
-      <c r="N51" s="1" t="inlineStr"/>
-      <c r="O51" s="1" t="inlineStr"/>
-      <c r="P51" s="1" t="inlineStr"/>
-      <c r="Q51" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R51" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>GBP aperto; Yelp Updated April 2026; sito attivo</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -5164,11 +5031,7 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5264,11 +5127,7 @@
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5323,16 +5182,8 @@
           <t>Berberepizzeria</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H83" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G83" s="1" t="inlineStr"/>
+      <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5387,16 +5238,8 @@
           <t>_da_zero</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H84" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G84" s="1" t="inlineStr"/>
+      <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5495,16 +5338,8 @@
           <t>fuzion_torino</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H86" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G86" s="1" t="inlineStr"/>
+      <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5600,11 +5435,7 @@
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5659,16 +5490,8 @@
           <t>aforisma_pizzeria_gourmet</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H89" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G89" s="1" t="inlineStr"/>
+      <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5723,16 +5546,8 @@
           <t>sestogustotorino</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H90" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G90" s="1" t="inlineStr"/>
+      <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5784,11 +5599,7 @@
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5887,16 +5698,8 @@
           <t>caffesancarlo_torino</t>
         </is>
       </c>
-      <c r="G93" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H93" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G93" s="1" t="inlineStr"/>
+      <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5995,16 +5798,8 @@
           <t>dappercoffeetorino</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H95" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G95" s="1" t="inlineStr"/>
+      <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6103,16 +5898,8 @@
           <t>goccedicioccolato_torino</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H97" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G97" s="1" t="inlineStr"/>
+      <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6167,16 +5954,8 @@
           <t>orsolaboratoriocaffe</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H98" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G98" s="1" t="inlineStr"/>
+      <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6231,16 +6010,8 @@
           <t>pasticceriasabauda</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H99" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G99" s="1" t="inlineStr"/>
+      <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6291,16 +6062,8 @@
           <t>pasticceriavenier</t>
         </is>
       </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H100" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G100" s="1" t="inlineStr"/>
+      <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6352,11 +6115,7 @@
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr"/>
-      <c r="H101" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6455,16 +6214,6 @@
           <t>adoniscreperie</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I103" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -6591,16 +6340,8 @@
           <t>caffemulassano</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H105" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G105" s="1" t="inlineStr"/>
+      <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6655,16 +6396,8 @@
           <t>koitorino</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H106" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G106" s="1" t="inlineStr"/>
+      <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6715,16 +6448,8 @@
           <t>kokoroyatorino</t>
         </is>
       </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H107" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G107" s="1" t="inlineStr"/>
+      <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6859,11 +6584,7 @@
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr"/>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G110" s="1" t="inlineStr"/>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
@@ -6963,16 +6684,8 @@
           <t>beppe_gallina</t>
         </is>
       </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H112" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G112" s="1" t="inlineStr"/>
+      <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7071,16 +6784,8 @@
           <t>smithsbritish</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H114" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G114" s="1" t="inlineStr"/>
+      <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7179,16 +6884,8 @@
           <t>tiffanybistrot</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H116" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G116" s="1" t="inlineStr"/>
+      <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7243,16 +6940,6 @@
           <t>bicerin.1763.torino</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -7335,16 +7022,8 @@
           <t>camellia.torino</t>
         </is>
       </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H118" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G118" s="1" t="inlineStr"/>
+      <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7443,16 +7122,8 @@
           <t>kintsugiteandcakes</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G120" s="1" t="inlineStr"/>
+      <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7547,16 +7218,8 @@
           <t>tarta.teatorteria</t>
         </is>
       </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H122" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G122" s="1" t="inlineStr"/>
+      <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7611,16 +7274,8 @@
           <t>thetea.torino</t>
         </is>
       </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H123" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G123" s="1" t="inlineStr"/>
+      <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7675,16 +7330,8 @@
           <t>olsentorteria</t>
         </is>
       </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H124" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G124" s="1" t="inlineStr"/>
+      <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7783,16 +7430,8 @@
           <t>caffedellorologiotorino</t>
         </is>
       </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H126" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G126" s="1" t="inlineStr"/>
+      <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7840,11 +7479,7 @@
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr"/>
-      <c r="H127" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7939,11 +7574,7 @@
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr"/>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G129" s="1" t="inlineStr"/>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
@@ -7999,16 +7630,8 @@
           <t>palto.torino</t>
         </is>
       </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G130" s="1" t="inlineStr"/>
+      <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8060,11 +7683,7 @@
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr"/>
-      <c r="H131" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8119,16 +7738,8 @@
           <t>rossorubino.enoteca</t>
         </is>
       </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H132" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G132" s="1" t="inlineStr"/>
+      <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8227,16 +7838,8 @@
           <t>tastumatorino</t>
         </is>
       </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H134" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G134" s="1" t="inlineStr"/>
+      <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8416,11 +8019,7 @@
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr"/>
-      <c r="H138" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8607,16 +8206,8 @@
           <t>recina-focaccia-e-cucina</t>
         </is>
       </c>
-      <c r="G142" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H142" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G142" s="1" t="inlineStr"/>
+      <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8715,16 +8306,6 @@
           <t>affinitorino</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I144" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -8891,16 +8472,8 @@
           <t>donetorino</t>
         </is>
       </c>
-      <c r="G147" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H147" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G147" s="1" t="inlineStr"/>
+      <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8999,16 +8572,8 @@
           <t>smile_tree_torino</t>
         </is>
       </c>
-      <c r="G149" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H149" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G149" s="1" t="inlineStr"/>
+      <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9107,16 +8672,6 @@
           <t>alberto_marchetti_gelaterie</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
       <c r="I151" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -9195,16 +8750,8 @@
           <t>aria_gelateria</t>
         </is>
       </c>
-      <c r="G152" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H152" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G152" s="1" t="inlineStr"/>
+      <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9347,16 +8894,8 @@
           <t>_conogelato_</t>
         </is>
       </c>
-      <c r="G155" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H155" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G155" s="1" t="inlineStr"/>
+      <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9455,16 +8994,8 @@
           <t>gaspringelatoedelizie</t>
         </is>
       </c>
-      <c r="G157" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H157" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G157" s="1" t="inlineStr"/>
+      <c r="H157" s="1" t="inlineStr"/>
       <c r="I157" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9607,16 +9138,8 @@
           <t>gelateria_miretti</t>
         </is>
       </c>
-      <c r="G160" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H160" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G160" s="1" t="inlineStr"/>
+      <c r="H160" s="1" t="inlineStr"/>
       <c r="I160" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9715,16 +9238,8 @@
           <t>gofreriapiemonteisa</t>
         </is>
       </c>
-      <c r="G162" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H162" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G162" s="1" t="inlineStr"/>
+      <c r="H162" s="1" t="inlineStr"/>
       <c r="I162" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9815,11 +9330,7 @@
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr"/>
-      <c r="G164" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G164" s="1" t="inlineStr"/>
       <c r="H164" s="1" t="inlineStr"/>
       <c r="I164" s="1" t="inlineStr">
         <is>
@@ -9875,16 +9386,8 @@
           <t>macbun_official</t>
         </is>
       </c>
-      <c r="G165" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H165" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G165" s="1" t="inlineStr"/>
+      <c r="H165" s="1" t="inlineStr"/>
       <c r="I165" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9939,16 +9442,8 @@
           <t>maradeiboschi</t>
         </is>
       </c>
-      <c r="G166" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H166" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G166" s="1" t="inlineStr"/>
+      <c r="H166" s="1" t="inlineStr"/>
       <c r="I166" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10003,16 +9498,8 @@
           <t>margheripizza</t>
         </is>
       </c>
-      <c r="G167" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H167" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G167" s="1" t="inlineStr"/>
+      <c r="H167" s="1" t="inlineStr"/>
       <c r="I167" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10107,16 +9594,8 @@
           <t>modo_gelato</t>
         </is>
       </c>
-      <c r="G169" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H169" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G169" s="1" t="inlineStr"/>
+      <c r="H169" s="1" t="inlineStr"/>
       <c r="I169" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10171,16 +9650,8 @@
           <t>nivagelato</t>
         </is>
       </c>
-      <c r="G170" s="1" t="inlineStr">
-        <is>
-          <t>03/01/2026</t>
-        </is>
-      </c>
-      <c r="H170" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
+      <c r="G170" s="1" t="inlineStr"/>
+      <c r="H170" s="1" t="inlineStr"/>
       <c r="I170" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10205,104 +9676,108 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="1" t="inlineStr">
         <is>
           <t>Ottimo!</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B171" s="1" t="inlineStr">
         <is>
           <t>Corso Stati Uniti, 6/C</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C171" s="1" t="inlineStr">
         <is>
           <t>340/6414542</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="D171" s="1" t="inlineStr"/>
+      <c r="E171" s="1" t="inlineStr">
         <is>
           <t>ottimobuonononbasta</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F171" s="1" t="inlineStr">
         <is>
           <t>ottimogelati</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 05/04/2026</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
+      <c r="G171" s="1" t="inlineStr"/>
+      <c r="H171" s="1" t="inlineStr"/>
+      <c r="I171" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J171" s="1" t="inlineStr"/>
+      <c r="K171" s="1" t="inlineStr"/>
+      <c r="L171" s="1" t="inlineStr"/>
+      <c r="M171" s="1" t="inlineStr"/>
+      <c r="N171" s="1" t="inlineStr"/>
+      <c r="O171" s="1" t="inlineStr"/>
+      <c r="P171" s="1" t="inlineStr"/>
+      <c r="Q171" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R171" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="1" t="inlineStr">
         <is>
           <t>Papalele</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B172" s="1" t="inlineStr">
         <is>
           <t>Corso Guglielmo Marconi, 23/A</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C172" s="1" t="inlineStr">
         <is>
           <t>011/9776990</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D172" s="1" t="inlineStr">
         <is>
           <t>www.papalele.it</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="E172" s="1" t="inlineStr">
         <is>
           <t>papalele.gelatiepasticci</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F172" s="1" t="inlineStr">
         <is>
           <t>papalele.gelatiepasticci</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>Promosso ad APERTO: post Facebook del 12/04/2026</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
+      <c r="G172" s="1" t="inlineStr"/>
+      <c r="H172" s="1" t="inlineStr"/>
+      <c r="I172" s="1" t="inlineStr">
+        <is>
+          <t>INCERTO</t>
+        </is>
+      </c>
+      <c r="J172" s="1" t="inlineStr"/>
+      <c r="K172" s="1" t="inlineStr"/>
+      <c r="L172" s="1" t="inlineStr"/>
+      <c r="M172" s="1" t="inlineStr"/>
+      <c r="N172" s="1" t="inlineStr"/>
+      <c r="O172" s="1" t="inlineStr"/>
+      <c r="P172" s="1" t="inlineStr"/>
+      <c r="Q172" s="1" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione</t>
+        </is>
+      </c>
+      <c r="R172" s="1" t="inlineStr">
         <is>
           <t>20/04/2026</t>
         </is>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -3470,7 +3470,7 @@
       </c>
       <c r="R52" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="R53" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="R55" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="R56" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="R57" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="R58" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="R59" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="R60" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="R61" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="R62" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="R63" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="R64" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="R65" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="R66" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="R67" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="R69" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="R70" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="R71" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="R72" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="R73" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="R77" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="R78" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,11 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr"/>
+      <c r="H80" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5051,7 +5055,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5099,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5131,11 @@
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
+      <c r="H82" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I82" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5147,7 +5155,7 @@
       </c>
       <c r="R82" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5182,8 +5190,16 @@
           <t>Berberepizzeria</t>
         </is>
       </c>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I83" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5203,7 +5219,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5238,8 +5254,16 @@
           <t>_da_zero</t>
         </is>
       </c>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I84" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5259,7 +5283,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5303,63 +5327,64 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Fuzion Food</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>Via Alessandro Volta, 4/B</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>346/2124341</t>
         </is>
       </c>
-      <c r="D86" s="1" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>www.fuzionfood.it</t>
         </is>
       </c>
-      <c r="E86" s="1" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>fuzionfood</t>
         </is>
       </c>
-      <c r="F86" s="1" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>fuzion_torino</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr"/>
-      <c r="L86" s="1" t="inlineStr"/>
-      <c r="M86" s="1" t="inlineStr"/>
-      <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr"/>
-      <c r="P86" s="1" t="inlineStr"/>
-      <c r="Q86" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R86" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 18/04/2026</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5428,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5460,11 @@
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
+      <c r="H88" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I88" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5455,7 +5484,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5490,8 +5519,16 @@
           <t>aforisma_pizzeria_gourmet</t>
         </is>
       </c>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I89" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5511,7 +5548,7 @@
       </c>
       <c r="R89" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5546,8 +5583,16 @@
           <t>sestogustotorino</t>
         </is>
       </c>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I90" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5567,7 +5612,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5644,11 @@
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
+      <c r="H91" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I91" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5619,7 +5668,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5712,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5698,8 +5747,16 @@
           <t>caffesancarlo_torino</t>
         </is>
       </c>
-      <c r="G93" s="1" t="inlineStr"/>
-      <c r="H93" s="1" t="inlineStr"/>
+      <c r="G93" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H93" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I93" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5719,7 +5776,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5820,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5798,8 +5855,16 @@
           <t>dappercoffeetorino</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr"/>
-      <c r="H95" s="1" t="inlineStr"/>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I95" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5819,7 +5884,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5928,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5898,8 +5963,16 @@
           <t>goccedicioccolato_torino</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr"/>
-      <c r="H97" s="1" t="inlineStr"/>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I97" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5919,7 +5992,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -5954,8 +6027,16 @@
           <t>orsolaboratoriocaffe</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr"/>
-      <c r="H98" s="1" t="inlineStr"/>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I98" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -5975,7 +6056,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6010,8 +6091,16 @@
           <t>pasticceriasabauda</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr"/>
-      <c r="H99" s="1" t="inlineStr"/>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H99" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I99" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6031,7 +6120,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6062,8 +6151,16 @@
           <t>pasticceriavenier</t>
         </is>
       </c>
-      <c r="G100" s="1" t="inlineStr"/>
-      <c r="H100" s="1" t="inlineStr"/>
+      <c r="G100" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H100" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6083,7 +6180,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6212,11 @@
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr"/>
-      <c r="H101" s="1" t="inlineStr"/>
+      <c r="H101" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I101" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6135,7 +6236,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6280,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6212,6 +6313,16 @@
       <c r="F103" t="inlineStr">
         <is>
           <t>adoniscreperie</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6305,7 +6416,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6340,8 +6451,16 @@
           <t>caffemulassano</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr"/>
-      <c r="H105" s="1" t="inlineStr"/>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>12/02/2019</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I105" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6361,7 +6480,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6396,8 +6515,16 @@
           <t>koitorino</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr"/>
-      <c r="H106" s="1" t="inlineStr"/>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6417,7 +6544,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6448,8 +6575,16 @@
           <t>kokoroyatorino</t>
         </is>
       </c>
-      <c r="G107" s="1" t="inlineStr"/>
-      <c r="H107" s="1" t="inlineStr"/>
+      <c r="G107" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H107" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I107" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6469,7 +6604,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6648,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6692,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6719,11 @@
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr"/>
-      <c r="G110" s="1" t="inlineStr"/>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
@@ -6605,7 +6744,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6788,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6684,8 +6823,16 @@
           <t>beppe_gallina</t>
         </is>
       </c>
-      <c r="G112" s="1" t="inlineStr"/>
-      <c r="H112" s="1" t="inlineStr"/>
+      <c r="G112" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H112" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I112" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6705,7 +6852,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6896,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6784,8 +6931,16 @@
           <t>smithsbritish</t>
         </is>
       </c>
-      <c r="G114" s="1" t="inlineStr"/>
-      <c r="H114" s="1" t="inlineStr"/>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H114" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I114" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6805,7 +6960,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6849,7 +7004,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6884,8 +7039,16 @@
           <t>tiffanybistrot</t>
         </is>
       </c>
-      <c r="G116" s="1" t="inlineStr"/>
-      <c r="H116" s="1" t="inlineStr"/>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H116" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I116" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -6905,7 +7068,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -6940,6 +7103,16 @@
           <t>bicerin.1763.torino</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -7022,8 +7195,16 @@
           <t>camellia.torino</t>
         </is>
       </c>
-      <c r="G118" s="1" t="inlineStr"/>
-      <c r="H118" s="1" t="inlineStr"/>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7043,7 +7224,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7272,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7122,8 +7303,16 @@
           <t>kintsugiteandcakes</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr"/>
-      <c r="H120" s="1" t="inlineStr"/>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I120" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7143,7 +7332,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7376,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7218,8 +7407,16 @@
           <t>tarta.teatorteria</t>
         </is>
       </c>
-      <c r="G122" s="1" t="inlineStr"/>
-      <c r="H122" s="1" t="inlineStr"/>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H122" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I122" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7239,63 +7436,64 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="inlineStr">
+      <c r="A123" t="inlineStr">
         <is>
           <t>The Tea</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>Via Corte d’Appello, 2</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>011/4364973</t>
         </is>
       </c>
-      <c r="D123" s="1" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>www.thetea.it</t>
         </is>
       </c>
-      <c r="E123" s="1" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>thetea.torino</t>
         </is>
       </c>
-      <c r="F123" s="1" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>thetea.torino</t>
         </is>
       </c>
-      <c r="G123" s="1" t="inlineStr"/>
-      <c r="H123" s="1" t="inlineStr"/>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J123" s="1" t="inlineStr"/>
-      <c r="K123" s="1" t="inlineStr"/>
-      <c r="L123" s="1" t="inlineStr"/>
-      <c r="M123" s="1" t="inlineStr"/>
-      <c r="N123" s="1" t="inlineStr"/>
-      <c r="O123" s="1" t="inlineStr"/>
-      <c r="P123" s="1" t="inlineStr"/>
-      <c r="Q123" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R123" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 21/04/2026</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7330,8 +7528,16 @@
           <t>olsentorteria</t>
         </is>
       </c>
-      <c r="G124" s="1" t="inlineStr"/>
-      <c r="H124" s="1" t="inlineStr"/>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H124" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I124" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7351,7 +7557,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7601,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7430,8 +7636,16 @@
           <t>caffedellorologiotorino</t>
         </is>
       </c>
-      <c r="G126" s="1" t="inlineStr"/>
-      <c r="H126" s="1" t="inlineStr"/>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H126" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I126" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7451,7 +7665,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7693,11 @@
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr"/>
-      <c r="H127" s="1" t="inlineStr"/>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I127" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7499,7 +7717,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7761,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7792,11 @@
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr"/>
-      <c r="G129" s="1" t="inlineStr"/>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
@@ -7595,7 +7817,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7630,8 +7852,16 @@
           <t>palto.torino</t>
         </is>
       </c>
-      <c r="G130" s="1" t="inlineStr"/>
-      <c r="H130" s="1" t="inlineStr"/>
+      <c r="G130" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H130" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I130" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7651,7 +7881,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7913,11 @@
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr"/>
-      <c r="H131" s="1" t="inlineStr"/>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I131" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7703,7 +7937,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7738,8 +7972,16 @@
           <t>rossorubino.enoteca</t>
         </is>
       </c>
-      <c r="G132" s="1" t="inlineStr"/>
-      <c r="H132" s="1" t="inlineStr"/>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H132" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I132" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7759,7 +8001,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7803,7 +8045,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7838,8 +8080,16 @@
           <t>tastumatorino</t>
         </is>
       </c>
-      <c r="G134" s="1" t="inlineStr"/>
-      <c r="H134" s="1" t="inlineStr"/>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H134" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I134" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -7859,7 +8109,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7903,7 +8153,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7947,7 +8197,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -7991,7 +8241,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8269,11 @@
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr"/>
-      <c r="H138" s="1" t="inlineStr"/>
+      <c r="H138" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I138" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8039,7 +8293,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8337,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8381,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8425,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8206,8 +8460,16 @@
           <t>recina-focaccia-e-cucina</t>
         </is>
       </c>
-      <c r="G142" s="1" t="inlineStr"/>
-      <c r="H142" s="1" t="inlineStr"/>
+      <c r="G142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H142" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I142" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8227,7 +8489,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8533,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8304,6 +8566,16 @@
       <c r="F144" t="inlineStr">
         <is>
           <t>affinitorino</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>N/D</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8397,7 +8669,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8713,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8472,8 +8744,16 @@
           <t>donetorino</t>
         </is>
       </c>
-      <c r="G147" s="1" t="inlineStr"/>
-      <c r="H147" s="1" t="inlineStr"/>
+      <c r="G147" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H147" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I147" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8493,7 +8773,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8817,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8572,8 +8852,16 @@
           <t>smile_tree_torino</t>
         </is>
       </c>
-      <c r="G149" s="1" t="inlineStr"/>
-      <c r="H149" s="1" t="inlineStr"/>
+      <c r="G149" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H149" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I149" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8593,7 +8881,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8925,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8672,6 +8960,16 @@
           <t>alberto_marchetti_gelaterie</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr">
         <is>
           <t>APERTO</t>
@@ -8750,8 +9048,16 @@
           <t>aria_gelateria</t>
         </is>
       </c>
-      <c r="G152" s="1" t="inlineStr"/>
-      <c r="H152" s="1" t="inlineStr"/>
+      <c r="G152" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H152" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I152" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8771,7 +9077,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8815,7 +9121,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8859,7 +9165,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8894,8 +9200,16 @@
           <t>_conogelato_</t>
         </is>
       </c>
-      <c r="G155" s="1" t="inlineStr"/>
-      <c r="H155" s="1" t="inlineStr"/>
+      <c r="G155" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H155" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I155" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -8915,7 +9229,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8959,7 +9273,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -8994,8 +9308,16 @@
           <t>gaspringelatoedelizie</t>
         </is>
       </c>
-      <c r="G157" s="1" t="inlineStr"/>
-      <c r="H157" s="1" t="inlineStr"/>
+      <c r="G157" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H157" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I157" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9015,7 +9337,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9381,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9103,63 +9425,64 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="inlineStr">
+      <c r="A160" t="inlineStr">
         <is>
           <t>Gelati Miretti</t>
         </is>
       </c>
-      <c r="B160" s="1" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Corso Giacomo Matteotti, 5</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>011/533687</t>
         </is>
       </c>
-      <c r="D160" s="1" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>www.gelateriamiretti.it</t>
         </is>
       </c>
-      <c r="E160" s="1" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>profile.php?id=100066744575332</t>
         </is>
       </c>
-      <c r="F160" s="1" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>gelateria_miretti</t>
         </is>
       </c>
-      <c r="G160" s="1" t="inlineStr"/>
-      <c r="H160" s="1" t="inlineStr"/>
-      <c r="I160" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J160" s="1" t="inlineStr"/>
-      <c r="K160" s="1" t="inlineStr"/>
-      <c r="L160" s="1" t="inlineStr"/>
-      <c r="M160" s="1" t="inlineStr"/>
-      <c r="N160" s="1" t="inlineStr"/>
-      <c r="O160" s="1" t="inlineStr"/>
-      <c r="P160" s="1" t="inlineStr"/>
-      <c r="Q160" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R160" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 22/04/2026</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9203,7 +9526,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9238,8 +9561,16 @@
           <t>gofreriapiemonteisa</t>
         </is>
       </c>
-      <c r="G162" s="1" t="inlineStr"/>
-      <c r="H162" s="1" t="inlineStr"/>
+      <c r="G162" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H162" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I162" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9259,7 +9590,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9634,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9661,11 @@
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr"/>
-      <c r="G164" s="1" t="inlineStr"/>
+      <c r="G164" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H164" s="1" t="inlineStr"/>
       <c r="I164" s="1" t="inlineStr">
         <is>
@@ -9351,7 +9686,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9386,8 +9721,16 @@
           <t>macbun_official</t>
         </is>
       </c>
-      <c r="G165" s="1" t="inlineStr"/>
-      <c r="H165" s="1" t="inlineStr"/>
+      <c r="G165" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H165" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I165" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9407,7 +9750,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9442,8 +9785,16 @@
           <t>maradeiboschi</t>
         </is>
       </c>
-      <c r="G166" s="1" t="inlineStr"/>
-      <c r="H166" s="1" t="inlineStr"/>
+      <c r="G166" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H166" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I166" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9463,7 +9814,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9498,8 +9849,16 @@
           <t>margheripizza</t>
         </is>
       </c>
-      <c r="G167" s="1" t="inlineStr"/>
-      <c r="H167" s="1" t="inlineStr"/>
+      <c r="G167" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H167" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I167" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9519,7 +9878,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9563,59 +9922,59 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="inlineStr">
+      <c r="A169" t="inlineStr">
         <is>
           <t>Modo</t>
         </is>
       </c>
-      <c r="B169" s="1" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>Via Madama Cristina, 18/F</t>
         </is>
       </c>
-      <c r="C169" s="1" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>348/7784538</t>
         </is>
       </c>
-      <c r="D169" s="1" t="inlineStr"/>
-      <c r="E169" s="1" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t>modogelateria</t>
         </is>
       </c>
-      <c r="F169" s="1" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>modo_gelato</t>
         </is>
       </c>
-      <c r="G169" s="1" t="inlineStr"/>
-      <c r="H169" s="1" t="inlineStr"/>
-      <c r="I169" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J169" s="1" t="inlineStr"/>
-      <c r="K169" s="1" t="inlineStr"/>
-      <c r="L169" s="1" t="inlineStr"/>
-      <c r="M169" s="1" t="inlineStr"/>
-      <c r="N169" s="1" t="inlineStr"/>
-      <c r="O169" s="1" t="inlineStr"/>
-      <c r="P169" s="1" t="inlineStr"/>
-      <c r="Q169" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R169" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 17/04/2026</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9650,8 +10009,16 @@
           <t>nivagelato</t>
         </is>
       </c>
-      <c r="G170" s="1" t="inlineStr"/>
-      <c r="H170" s="1" t="inlineStr"/>
+      <c r="G170" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H170" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I170" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -9671,59 +10038,59 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="inlineStr">
+      <c r="A171" t="inlineStr">
         <is>
           <t>Ottimo!</t>
         </is>
       </c>
-      <c r="B171" s="1" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Corso Stati Uniti, 6/C</t>
         </is>
       </c>
-      <c r="C171" s="1" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>340/6414542</t>
         </is>
       </c>
-      <c r="D171" s="1" t="inlineStr"/>
-      <c r="E171" s="1" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>ottimobuonononbasta</t>
         </is>
       </c>
-      <c r="F171" s="1" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>ottimogelati</t>
         </is>
       </c>
-      <c r="G171" s="1" t="inlineStr"/>
-      <c r="H171" s="1" t="inlineStr"/>
-      <c r="I171" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J171" s="1" t="inlineStr"/>
-      <c r="K171" s="1" t="inlineStr"/>
-      <c r="L171" s="1" t="inlineStr"/>
-      <c r="M171" s="1" t="inlineStr"/>
-      <c r="N171" s="1" t="inlineStr"/>
-      <c r="O171" s="1" t="inlineStr"/>
-      <c r="P171" s="1" t="inlineStr"/>
-      <c r="Q171" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R171" s="1" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Promosso ad APERTO: post Facebook del 05/04/2026</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9758,7 +10125,11 @@
           <t>papalele.gelatiepasticci</t>
         </is>
       </c>
-      <c r="G172" s="1" t="inlineStr"/>
+      <c r="G172" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="H172" s="1" t="inlineStr"/>
       <c r="I172" s="1" t="inlineStr">
         <is>
@@ -9779,7 +10150,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9835,7 +10206,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9887,7 +10258,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9931,7 +10302,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -9987,7 +10358,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10043,7 +10414,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10470,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10155,7 +10526,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10582,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -3470,7 +3470,7 @@
       </c>
       <c r="R52" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="R53" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="R55" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="R56" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="R57" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="R58" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="R59" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="R60" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="R61" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="R62" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="R63" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="R64" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="R65" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="R66" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="R67" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="R69" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="R70" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="R71" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="R72" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="R73" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="R77" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="R78" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="R82" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="R89" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5668,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8533,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9337,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9634,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10130,7 +10130,11 @@
           <t>N/D</t>
         </is>
       </c>
-      <c r="H172" s="1" t="inlineStr"/>
+      <c r="H172" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I172" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10150,7 +10154,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10185,8 +10189,16 @@
           <t>piudiungelato</t>
         </is>
       </c>
-      <c r="G173" s="1" t="inlineStr"/>
-      <c r="H173" s="1" t="inlineStr"/>
+      <c r="G173" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H173" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I173" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10206,7 +10218,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10237,8 +10249,16 @@
           <t>robertafocacceria</t>
         </is>
       </c>
-      <c r="G174" s="1" t="inlineStr"/>
-      <c r="H174" s="1" t="inlineStr"/>
+      <c r="G174" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H174" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I174" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10258,7 +10278,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10322,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10337,8 +10357,16 @@
           <t>silvanogelatodaltritempi</t>
         </is>
       </c>
-      <c r="G176" s="1" t="inlineStr"/>
-      <c r="H176" s="1" t="inlineStr"/>
+      <c r="G176" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H176" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I176" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10358,7 +10386,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10393,8 +10421,16 @@
           <t>taglioperfetta</t>
         </is>
       </c>
-      <c r="G177" s="1" t="inlineStr"/>
-      <c r="H177" s="1" t="inlineStr"/>
+      <c r="G177" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H177" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I177" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10414,7 +10450,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10449,8 +10485,16 @@
           <t>telliatorino</t>
         </is>
       </c>
-      <c r="G178" s="1" t="inlineStr"/>
-      <c r="H178" s="1" t="inlineStr"/>
+      <c r="G178" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H178" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I178" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10470,7 +10514,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10505,8 +10549,16 @@
           <t>Trapizzino</t>
         </is>
       </c>
-      <c r="G179" s="1" t="inlineStr"/>
-      <c r="H179" s="1" t="inlineStr"/>
+      <c r="G179" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H179" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I179" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10526,7 +10578,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>
@@ -10561,8 +10613,16 @@
           <t>vanillatorino</t>
         </is>
       </c>
-      <c r="G180" s="1" t="inlineStr"/>
-      <c r="H180" s="1" t="inlineStr"/>
+      <c r="G180" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H180" s="1" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
       <c r="I180" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
@@ -10582,7 +10642,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -3431,108 +3431,99 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Tre Galline</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Via Gian Francesco Bellezia, 37</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>011/4366553</t>
         </is>
       </c>
-      <c r="D52" s="1" t="inlineStr"/>
-      <c r="E52" s="1" t="inlineStr"/>
-      <c r="F52" s="1" t="inlineStr"/>
-      <c r="G52" s="1" t="inlineStr"/>
-      <c r="H52" s="1" t="inlineStr"/>
-      <c r="I52" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr"/>
-      <c r="L52" s="1" t="inlineStr"/>
-      <c r="M52" s="1" t="inlineStr"/>
-      <c r="N52" s="1" t="inlineStr"/>
-      <c r="O52" s="1" t="inlineStr"/>
-      <c r="P52" s="1" t="inlineStr"/>
-      <c r="Q52" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R52" s="1" t="inlineStr">
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated February 2026', Michelin Guide attiva</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Enoteca Parlapà</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Corso Principe Eugenio, 17</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>011/4365899</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>www.parlapa.com</t>
         </is>
       </c>
-      <c r="E53" s="1" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>parlapatorino</t>
         </is>
       </c>
-      <c r="F53" s="1" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>parlapatorino</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H53" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I53" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr"/>
-      <c r="L53" s="1" t="inlineStr"/>
-      <c r="M53" s="1" t="inlineStr"/>
-      <c r="N53" s="1" t="inlineStr"/>
-      <c r="O53" s="1" t="inlineStr"/>
-      <c r="P53" s="1" t="inlineStr"/>
-      <c r="Q53" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R53" s="1" t="inlineStr">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Wheree menu 'Updated 2026', Tripadvisor 4.2/5</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -3616,664 +3607,596 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Barbagusto</t>
         </is>
       </c>
-      <c r="B55" s="1" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Via Belfiore, 36</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>011/2760233</t>
         </is>
       </c>
-      <c r="D55" s="1" t="inlineStr"/>
-      <c r="E55" s="1" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="1" t="inlineStr"/>
-      <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr"/>
-      <c r="L55" s="1" t="inlineStr"/>
-      <c r="M55" s="1" t="inlineStr"/>
-      <c r="N55" s="1" t="inlineStr"/>
-      <c r="O55" s="1" t="inlineStr"/>
-      <c r="P55" s="1" t="inlineStr"/>
-      <c r="Q55" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R55" s="1" t="inlineStr">
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Tripadvisor 4.3/5 attivo, Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Cantinone San Paolo</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Via Vigone, 24</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>339/7875509</t>
         </is>
       </c>
-      <c r="D56" s="1" t="inlineStr"/>
-      <c r="E56" s="1" t="inlineStr"/>
-      <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="1" t="inlineStr"/>
-      <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr"/>
-      <c r="L56" s="1" t="inlineStr"/>
-      <c r="M56" s="1" t="inlineStr"/>
-      <c r="N56" s="1" t="inlineStr"/>
-      <c r="O56" s="1" t="inlineStr"/>
-      <c r="P56" s="1" t="inlineStr"/>
-      <c r="Q56" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R56" s="1" t="inlineStr">
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, sito Buonissima Torino attivo, orari aggiornati</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Come a Casa</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Via Crevacuore, 60</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>011/5692226</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr"/>
-      <c r="E57" s="1" t="inlineStr"/>
-      <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr"/>
-      <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr"/>
-      <c r="L57" s="1" t="inlineStr"/>
-      <c r="M57" s="1" t="inlineStr"/>
-      <c r="N57" s="1" t="inlineStr"/>
-      <c r="O57" s="1" t="inlineStr"/>
-      <c r="P57" s="1" t="inlineStr"/>
-      <c r="Q57" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R57" s="1" t="inlineStr">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Tripadvisor 4.6/5, location set film 2024</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Dù Cesari</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Via Giovanni Spano, 16</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>011/3187993</t>
         </is>
       </c>
-      <c r="D58" s="1" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>www.ducesari.com</t>
         </is>
       </c>
-      <c r="E58" s="1" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>trattoriaducesari</t>
         </is>
       </c>
-      <c r="F58" s="1" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>ducesari</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H58" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I58" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr"/>
-      <c r="L58" s="1" t="inlineStr"/>
-      <c r="M58" s="1" t="inlineStr"/>
-      <c r="N58" s="1" t="inlineStr"/>
-      <c r="O58" s="1" t="inlineStr"/>
-      <c r="P58" s="1" t="inlineStr"/>
-      <c r="Q58" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R58" s="1" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, sito ducesari.com attivo, Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>F.lli Bruzzone</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Via Maria Vittoria, 34/A</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>011/7633447</t>
         </is>
       </c>
-      <c r="D59" s="1" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>www.fratellibruzzone.com</t>
         </is>
       </c>
-      <c r="E59" s="1" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>fratellibruzzone</t>
         </is>
       </c>
-      <c r="F59" s="1" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>fratellibruzzone</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H59" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I59" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr"/>
-      <c r="L59" s="1" t="inlineStr"/>
-      <c r="M59" s="1" t="inlineStr"/>
-      <c r="N59" s="1" t="inlineStr"/>
-      <c r="O59" s="1" t="inlineStr"/>
-      <c r="P59" s="1" t="inlineStr"/>
-      <c r="Q59" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R59" s="1" t="inlineStr">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Michelin Guide attiva, sito attivo</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Le Putrelle</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Via Valperga Caluso, 11</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>011/6599630</t>
         </is>
       </c>
-      <c r="D60" s="1" t="inlineStr"/>
-      <c r="E60" s="1" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr"/>
-      <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr"/>
-      <c r="L60" s="1" t="inlineStr"/>
-      <c r="M60" s="1" t="inlineStr"/>
-      <c r="N60" s="1" t="inlineStr"/>
-      <c r="O60" s="1" t="inlineStr"/>
-      <c r="P60" s="1" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R60" s="1" t="inlineStr">
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated February 2026', TheFork menu 2026</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Le Ramine</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Via Isonzo, 64</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>011/3804067</t>
         </is>
       </c>
-      <c r="D61" s="1" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>www.leramine.it</t>
         </is>
       </c>
-      <c r="E61" s="1" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Osterialeramine</t>
         </is>
       </c>
-      <c r="F61" s="1" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>le_ramine</t>
         </is>
       </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H61" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I61" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr"/>
-      <c r="L61" s="1" t="inlineStr"/>
-      <c r="M61" s="1" t="inlineStr"/>
-      <c r="N61" s="1" t="inlineStr"/>
-      <c r="O61" s="1" t="inlineStr"/>
-      <c r="P61" s="1" t="inlineStr"/>
-      <c r="Q61" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R61" s="1" t="inlineStr">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated March 2026', sito attivo</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>L'Uliveto</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Via Saluzzo, 57/bis C</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>389/9938771</t>
         </is>
       </c>
-      <c r="D62" s="1" t="inlineStr"/>
-      <c r="E62" s="1" t="inlineStr"/>
-      <c r="F62" s="1" t="inlineStr"/>
-      <c r="G62" s="1" t="inlineStr"/>
-      <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr"/>
-      <c r="L62" s="1" t="inlineStr"/>
-      <c r="M62" s="1" t="inlineStr"/>
-      <c r="N62" s="1" t="inlineStr"/>
-      <c r="O62" s="1" t="inlineStr"/>
-      <c r="P62" s="1" t="inlineStr"/>
-      <c r="Q62" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R62" s="1" t="inlineStr">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, TheFork 9.1/10 menu 2026, prenotazioni attive</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Osteria Nuova</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Via XX settembre, 2/M</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>327/0608010</t>
         </is>
       </c>
-      <c r="D63" s="1" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>www.osterianuovatorino.it</t>
         </is>
       </c>
-      <c r="E63" s="1" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>osterianuovatorino</t>
         </is>
       </c>
-      <c r="F63" s="1" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>osteria_nuova_torino</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H63" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I63" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr"/>
-      <c r="L63" s="1" t="inlineStr"/>
-      <c r="M63" s="1" t="inlineStr"/>
-      <c r="N63" s="1" t="inlineStr"/>
-      <c r="O63" s="1" t="inlineStr"/>
-      <c r="P63" s="1" t="inlineStr"/>
-      <c r="Q63" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R63" s="1" t="inlineStr">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated February 2026', sito attivo</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Piola 1706</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Via Andrea Provana, 7</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>011/7804183</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr"/>
-      <c r="E64" s="1" t="inlineStr"/>
-      <c r="F64" s="1" t="inlineStr"/>
-      <c r="G64" s="1" t="inlineStr"/>
-      <c r="H64" s="1" t="inlineStr"/>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr"/>
-      <c r="L64" s="1" t="inlineStr"/>
-      <c r="M64" s="1" t="inlineStr"/>
-      <c r="N64" s="1" t="inlineStr"/>
-      <c r="O64" s="1" t="inlineStr"/>
-      <c r="P64" s="1" t="inlineStr"/>
-      <c r="Q64" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R64" s="1" t="inlineStr">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Instagram attivo, TikTok recente</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Senza Pretese</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Via Stampatori, 10</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>011/18972834</t>
         </is>
       </c>
-      <c r="D65" s="1" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>www.senzapretese.org</t>
         </is>
       </c>
-      <c r="E65" s="1" t="inlineStr"/>
-      <c r="F65" s="1" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>hostariasenzapretese</t>
         </is>
       </c>
-      <c r="G65" s="1" t="inlineStr"/>
-      <c r="H65" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I65" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr"/>
-      <c r="L65" s="1" t="inlineStr"/>
-      <c r="M65" s="1" t="inlineStr"/>
-      <c r="N65" s="1" t="inlineStr"/>
-      <c r="O65" s="1" t="inlineStr"/>
-      <c r="P65" s="1" t="inlineStr"/>
-      <c r="Q65" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R65" s="1" t="inlineStr">
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto (apertura marzo 2025), Tripadvisor attivo</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Trattoria Bon Bon</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Via Renato Martorelli, 43</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>011/2052155</t>
         </is>
       </c>
-      <c r="D66" s="1" t="inlineStr"/>
-      <c r="E66" s="1" t="inlineStr"/>
-      <c r="F66" s="1" t="inlineStr"/>
-      <c r="G66" s="1" t="inlineStr"/>
-      <c r="H66" s="1" t="inlineStr"/>
-      <c r="I66" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr"/>
-      <c r="L66" s="1" t="inlineStr"/>
-      <c r="M66" s="1" t="inlineStr"/>
-      <c r="N66" s="1" t="inlineStr"/>
-      <c r="O66" s="1" t="inlineStr"/>
-      <c r="P66" s="1" t="inlineStr"/>
-      <c r="Q66" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R66" s="1" t="inlineStr">
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Yelp 'Updated April 2026', recensione gennaio 2026</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Alma Latina</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Via Giuseppe Baretti, 8 bis</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>011/6692554</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr"/>
-      <c r="E67" s="1" t="inlineStr"/>
-      <c r="F67" s="1" t="inlineStr"/>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr"/>
-      <c r="L67" s="1" t="inlineStr"/>
-      <c r="M67" s="1" t="inlineStr"/>
-      <c r="N67" s="1" t="inlineStr"/>
-      <c r="O67" s="1" t="inlineStr"/>
-      <c r="P67" s="1" t="inlineStr"/>
-      <c r="Q67" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R67" s="1" t="inlineStr">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, sito almalatina.to.it attivo, attivo da 30+ anni</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -4372,288 +4295,270 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Casa Armenia</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Via Giovanni Francesco Napione, 33</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>351/7441444</t>
         </is>
       </c>
-      <c r="D69" s="1" t="inlineStr"/>
-      <c r="E69" s="1" t="inlineStr"/>
-      <c r="F69" s="1" t="inlineStr"/>
-      <c r="G69" s="1" t="inlineStr"/>
-      <c r="H69" s="1" t="inlineStr"/>
-      <c r="I69" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr"/>
-      <c r="L69" s="1" t="inlineStr"/>
-      <c r="M69" s="1" t="inlineStr"/>
-      <c r="N69" s="1" t="inlineStr"/>
-      <c r="O69" s="1" t="inlineStr"/>
-      <c r="P69" s="1" t="inlineStr"/>
-      <c r="Q69" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R69" s="1" t="inlineStr">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, TheFork 9.1/10 con 477 recensioni 2026</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Donburi House</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Via Stampatori, 12</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>375/8432594</t>
         </is>
       </c>
-      <c r="D70" s="1" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>www.donburihouse.it</t>
         </is>
       </c>
-      <c r="E70" s="1" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>donburitorino</t>
         </is>
       </c>
-      <c r="F70" s="1" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>donburihouse_</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H70" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I70" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr"/>
-      <c r="L70" s="1" t="inlineStr"/>
-      <c r="M70" s="1" t="inlineStr"/>
-      <c r="N70" s="1" t="inlineStr"/>
-      <c r="O70" s="1" t="inlineStr"/>
-      <c r="P70" s="1" t="inlineStr"/>
-      <c r="Q70" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R70" s="1" t="inlineStr">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, espansione 2026 multi-città, Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>El Beso</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Via Bernardino Galliari, 22</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>011/19715606</t>
         </is>
       </c>
-      <c r="D71" s="1" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>www.ristoranteelbeso.it</t>
         </is>
       </c>
-      <c r="E71" s="1" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>elbesotorino</t>
         </is>
       </c>
-      <c r="F71" s="1" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>elbeso_torino</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H71" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I71" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr"/>
-      <c r="L71" s="1" t="inlineStr"/>
-      <c r="M71" s="1" t="inlineStr"/>
-      <c r="N71" s="1" t="inlineStr"/>
-      <c r="O71" s="1" t="inlineStr"/>
-      <c r="P71" s="1" t="inlineStr"/>
-      <c r="Q71" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R71" s="1" t="inlineStr">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, TheFork 9.9/10, articolo Sarah Scaparone 5/2/2026</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Kadeh Meze Wine Bar</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Via della Basilica, 1/D</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>011/5695305</t>
         </is>
       </c>
-      <c r="D72" s="1" t="inlineStr"/>
-      <c r="E72" s="1" t="inlineStr"/>
-      <c r="F72" s="1" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>kadeh.torino</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr"/>
-      <c r="H72" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I72" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr"/>
-      <c r="L72" s="1" t="inlineStr"/>
-      <c r="M72" s="1" t="inlineStr"/>
-      <c r="N72" s="1" t="inlineStr"/>
-      <c r="O72" s="1" t="inlineStr"/>
-      <c r="P72" s="1" t="inlineStr"/>
-      <c r="Q72" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R72" s="1" t="inlineStr">
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, articolo Torino Oggi 11/2/2026, nuovo chef gennaio 2026</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Kay - essenza peruviana e piscobar</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Via Evangelista Torricelli, 59/D</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>011/4118866</t>
         </is>
       </c>
-      <c r="D73" s="1" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>kayessenzaperuvianapiscobar.business.site</t>
         </is>
       </c>
-      <c r="E73" s="1" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>kayessenzaperuviana</t>
         </is>
       </c>
-      <c r="F73" s="1" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Kayessenzaperuviana</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H73" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr"/>
-      <c r="L73" s="1" t="inlineStr"/>
-      <c r="M73" s="1" t="inlineStr"/>
-      <c r="N73" s="1" t="inlineStr"/>
-      <c r="O73" s="1" t="inlineStr"/>
-      <c r="P73" s="1" t="inlineStr"/>
-      <c r="Q73" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R73" s="1" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Non verificato in questa sessione | Verifica 30/04/2026: GBP aperto, Wheree menu 'Updated 2026', Instagram attivo</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
         <is>
           <t>27/04/2026</t>
         </is>
@@ -4707,7 +4612,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4672,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4736,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4800,7 @@
       </c>
       <c r="R77" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4844,7 @@
       </c>
       <c r="R78" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4896,7 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5055,7 +4960,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5004,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5060,7 @@
       </c>
       <c r="R82" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5124,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5188,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5232,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5333,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5389,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5453,7 @@
       </c>
       <c r="R89" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5517,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5573,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5712,7 +5617,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5681,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5725,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5789,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5833,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5897,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6056,7 +5961,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6025,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6085,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6141,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6185,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6321,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6385,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6449,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6509,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6553,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6597,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6649,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6693,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6757,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6801,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6865,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7004,7 +6909,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7068,7 +6973,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7129,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7177,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7237,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7281,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7341,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7462,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7506,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7570,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7622,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7666,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7722,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7786,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -7937,7 +7842,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8001,7 +7906,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8045,7 +7950,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8014,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8058,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8102,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8146,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8198,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8337,7 +8242,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8286,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8330,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8394,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8438,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8574,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8618,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8678,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8722,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8786,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8830,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9077,7 +8982,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9026,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9070,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9134,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9178,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9242,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9286,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9330,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9431,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9495,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9539,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9591,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9655,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9719,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9783,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -9922,7 +9827,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10038,7 +9943,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10059,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10123,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10183,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10227,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10291,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10355,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10419,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10483,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10547,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -4612,7 +4612,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="R77" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="R78" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="R82" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="R89" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -4612,7 +4612,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="R77" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="R78" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="R82" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="R89" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -4612,7 +4612,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="R77" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="R78" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="R82" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="R89" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -4612,7 +4612,7 @@
       </c>
       <c r="R74" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="R75" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="R76" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="R77" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="R78" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="R79" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="R81" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="R82" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="R83" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="R84" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="R85" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="R87" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="R88" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="R89" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="R91" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="R93" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="R94" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="R97" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="R98" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="R99" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="R101" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="R102" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="R104" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="R105" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="R106" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="R108" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="R109" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="R110" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="R111" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="R112" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="R113" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="R114" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="R115" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="R116" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="R118" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="R121" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="R122" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="R127" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="R128" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="R130" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="R145" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="R149" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="R150" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="R154" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="R155" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="R156" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="R161" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="R163" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="R164" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="R165" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="R166" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="R167" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="R174" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Torino_2027.xlsx
+++ b/Verifica_Torino_2027.xlsx
@@ -7181,826 +7181,847 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="inlineStr">
+      <c r="A117" t="inlineStr">
         <is>
           <t>Mei Shi Mei Ke</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>Corso Francia, 263</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>333/4402845</t>
         </is>
       </c>
-      <c r="D117" s="1" t="inlineStr"/>
-      <c r="E117" s="1" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>MEI-SHI-MEI-KE-100055217327593/?locale=it_IT</t>
         </is>
       </c>
-      <c r="F117" s="1" t="inlineStr"/>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H117" s="1" t="inlineStr"/>
-      <c r="I117" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J117" s="1" t="inlineStr"/>
-      <c r="K117" s="1" t="inlineStr"/>
-      <c r="L117" s="1" t="inlineStr"/>
-      <c r="M117" s="1" t="inlineStr"/>
-      <c r="N117" s="1" t="inlineStr"/>
-      <c r="O117" s="1" t="inlineStr"/>
-      <c r="P117" s="1" t="inlineStr"/>
-      <c r="Q117" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R117" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (MEI-SHI-MEI-KE-100055217327593/?locale=it_IT) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="inlineStr">
+      <c r="A118" t="inlineStr">
         <is>
           <t>Pastificio Baretti</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>Via Giuseppe Baretti,18/E</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>011/6691673</t>
         </is>
       </c>
-      <c r="D118" s="1" t="inlineStr"/>
-      <c r="E118" s="1" t="inlineStr"/>
-      <c r="F118" s="1" t="inlineStr"/>
-      <c r="G118" s="1" t="inlineStr"/>
-      <c r="H118" s="1" t="inlineStr"/>
-      <c r="I118" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J118" s="1" t="inlineStr"/>
-      <c r="K118" s="1" t="inlineStr"/>
-      <c r="L118" s="1" t="inlineStr"/>
-      <c r="M118" s="1" t="inlineStr"/>
-      <c r="N118" s="1" t="inlineStr"/>
-      <c r="O118" s="1" t="inlineStr"/>
-      <c r="P118" s="1" t="inlineStr"/>
-      <c r="Q118" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R118" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10', 'closes': '19'}, 'martedì': {'opens': '09:30', 'close</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>Pescheria Gallina</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Via Baretti, 25</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>011/19210346</t>
         </is>
       </c>
-      <c r="D119" s="1" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>www.pescheriagallina.com</t>
         </is>
       </c>
-      <c r="E119" s="1" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>PescheriaGallina</t>
         </is>
       </c>
-      <c r="F119" s="1" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>beppe_gallina</t>
         </is>
       </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H119" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J119" s="1" t="inlineStr"/>
-      <c r="K119" s="1" t="inlineStr"/>
-      <c r="L119" s="1" t="inlineStr"/>
-      <c r="M119" s="1" t="inlineStr"/>
-      <c r="N119" s="1" t="inlineStr"/>
-      <c r="O119" s="1" t="inlineStr"/>
-      <c r="P119" s="1" t="inlineStr"/>
-      <c r="Q119" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R119" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: trovato (PescheriaGallina) | IG: non trovato (beppe_gallina)</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="inlineStr">
+      <c r="A120" t="inlineStr">
         <is>
           <t>Petronilla</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>Corso Verona, 38/E</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>011/233012</t>
         </is>
       </c>
-      <c r="D120" s="1" t="inlineStr"/>
-      <c r="E120" s="1" t="inlineStr"/>
-      <c r="F120" s="1" t="inlineStr"/>
-      <c r="G120" s="1" t="inlineStr"/>
-      <c r="H120" s="1" t="inlineStr"/>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J120" s="1" t="inlineStr"/>
-      <c r="K120" s="1" t="inlineStr"/>
-      <c r="L120" s="1" t="inlineStr"/>
-      <c r="M120" s="1" t="inlineStr"/>
-      <c r="N120" s="1" t="inlineStr"/>
-      <c r="O120" s="1" t="inlineStr"/>
-      <c r="P120" s="1" t="inlineStr"/>
-      <c r="Q120" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R120" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12, 18', 'closes': '16, 23</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="inlineStr">
+      <c r="A121" t="inlineStr">
         <is>
           <t>Smith's British</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Via Virle, 19</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>​346/6844598</t>
         </is>
       </c>
-      <c r="D121" s="1" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>www.smithsbritish.it</t>
         </is>
       </c>
-      <c r="E121" s="1" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>Smithsbritish</t>
         </is>
       </c>
-      <c r="F121" s="1" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>smithsbritish</t>
         </is>
       </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H121" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J121" s="1" t="inlineStr"/>
-      <c r="K121" s="1" t="inlineStr"/>
-      <c r="L121" s="1" t="inlineStr"/>
-      <c r="M121" s="1" t="inlineStr"/>
-      <c r="N121" s="1" t="inlineStr"/>
-      <c r="O121" s="1" t="inlineStr"/>
-      <c r="P121" s="1" t="inlineStr"/>
-      <c r="Q121" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R121" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (Smithsbritish) | IG: non trovato (smithsbritish)</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="inlineStr">
+      <c r="A122" t="inlineStr">
         <is>
           <t>Tauer Bakery</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>Via Madama Cristina, 22</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>366/1269001</t>
         </is>
       </c>
-      <c r="D122" s="1" t="inlineStr"/>
-      <c r="E122" s="1" t="inlineStr"/>
-      <c r="F122" s="1" t="inlineStr"/>
-      <c r="G122" s="1" t="inlineStr"/>
-      <c r="H122" s="1" t="inlineStr"/>
-      <c r="I122" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J122" s="1" t="inlineStr"/>
-      <c r="K122" s="1" t="inlineStr"/>
-      <c r="L122" s="1" t="inlineStr"/>
-      <c r="M122" s="1" t="inlineStr"/>
-      <c r="N122" s="1" t="inlineStr"/>
-      <c r="O122" s="1" t="inlineStr"/>
-      <c r="P122" s="1" t="inlineStr"/>
-      <c r="Q122" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R122" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="inlineStr">
+      <c r="A123" t="inlineStr">
         <is>
           <t>Tiffany bistrot di mare</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>Via Publio Elvio Pertinace, 19</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>3287080965</t>
         </is>
       </c>
-      <c r="D123" s="1" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>www.ristorantetiffanybistrot.it</t>
         </is>
       </c>
-      <c r="E123" s="1" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>Tiffanybistrotdimare</t>
         </is>
       </c>
-      <c r="F123" s="1" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>tiffanybistrot</t>
         </is>
       </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H123" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J123" s="1" t="inlineStr"/>
-      <c r="K123" s="1" t="inlineStr"/>
-      <c r="L123" s="1" t="inlineStr"/>
-      <c r="M123" s="1" t="inlineStr"/>
-      <c r="N123" s="1" t="inlineStr"/>
-      <c r="O123" s="1" t="inlineStr"/>
-      <c r="P123" s="1" t="inlineStr"/>
-      <c r="Q123" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R123" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12', 'closes': '16'}, 'martedì': {'opens': '12', 'closes':</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (Tiffanybistrotdimare) | IG: non trovato (tiffanybistrot)</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="inlineStr">
+      <c r="A124" t="inlineStr">
         <is>
           <t>Camellia il Tempo del tè</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>Via Catania, 24</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>011/7651876</t>
         </is>
       </c>
-      <c r="D124" s="1" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>www.camelliate.it</t>
         </is>
       </c>
-      <c r="E124" s="1" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>camelliatetorino</t>
         </is>
       </c>
-      <c r="F124" s="1" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>camellia.torino</t>
         </is>
       </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H124" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J124" s="1" t="inlineStr"/>
-      <c r="K124" s="1" t="inlineStr"/>
-      <c r="L124" s="1" t="inlineStr"/>
-      <c r="M124" s="1" t="inlineStr"/>
-      <c r="N124" s="1" t="inlineStr"/>
-      <c r="O124" s="1" t="inlineStr"/>
-      <c r="P124" s="1" t="inlineStr"/>
-      <c r="Q124" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R124" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12', 'closes': '19'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: trovato (camelliatetorino) | IG: non trovato (camellia.torino)</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="inlineStr">
+      <c r="A125" t="inlineStr">
         <is>
           <t>Convitto Cafè</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>Via San Francesco da Paola, 8/D</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>011/8154070</t>
         </is>
       </c>
-      <c r="D125" s="1" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>www.convittocafe.it</t>
         </is>
       </c>
-      <c r="E125" s="1" t="inlineStr"/>
-      <c r="F125" s="1" t="inlineStr"/>
-      <c r="G125" s="1" t="inlineStr"/>
-      <c r="H125" s="1" t="inlineStr"/>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J125" s="1" t="inlineStr"/>
-      <c r="K125" s="1" t="inlineStr"/>
-      <c r="L125" s="1" t="inlineStr"/>
-      <c r="M125" s="1" t="inlineStr"/>
-      <c r="N125" s="1" t="inlineStr"/>
-      <c r="O125" s="1" t="inlineStr"/>
-      <c r="P125" s="1" t="inlineStr"/>
-      <c r="Q125" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R125" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '08:30', 'closes': '19:30'}, 'martedì': {'opens': '08:30',</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="inlineStr">
+      <c r="A126" t="inlineStr">
         <is>
           <t>Kintsugi tea&amp;cakes</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Via Monte di Pietà, 17/C</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>011/3352342</t>
         </is>
       </c>
-      <c r="D126" s="1" t="inlineStr"/>
-      <c r="E126" s="1" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>kintsugiteandcakes</t>
         </is>
       </c>
-      <c r="F126" s="1" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>kintsugiteandcakes</t>
         </is>
       </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H126" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I126" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J126" s="1" t="inlineStr"/>
-      <c r="K126" s="1" t="inlineStr"/>
-      <c r="L126" s="1" t="inlineStr"/>
-      <c r="M126" s="1" t="inlineStr"/>
-      <c r="N126" s="1" t="inlineStr"/>
-      <c r="O126" s="1" t="inlineStr"/>
-      <c r="P126" s="1" t="inlineStr"/>
-      <c r="Q126" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R126" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30', 'closes': '19'}, 'martedì': {'opens': '12:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (kintsugiteandcakes) | IG: non trovato (kintsugiteandcakes)</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="inlineStr">
+      <c r="A127" t="inlineStr">
         <is>
           <t>Oishii Coffee</t>
         </is>
       </c>
-      <c r="B127" s="1" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Via dell'Arsenale, 41</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>n.d.</t>
         </is>
       </c>
-      <c r="D127" s="1" t="inlineStr"/>
-      <c r="E127" s="1" t="inlineStr"/>
-      <c r="F127" s="1" t="inlineStr"/>
-      <c r="G127" s="1" t="inlineStr"/>
-      <c r="H127" s="1" t="inlineStr"/>
-      <c r="I127" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J127" s="1" t="inlineStr"/>
-      <c r="K127" s="1" t="inlineStr"/>
-      <c r="L127" s="1" t="inlineStr"/>
-      <c r="M127" s="1" t="inlineStr"/>
-      <c r="N127" s="1" t="inlineStr"/>
-      <c r="O127" s="1" t="inlineStr"/>
-      <c r="P127" s="1" t="inlineStr"/>
-      <c r="Q127" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R127" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '09', 'closes': '18'}, 'mer</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Rating Google: 5.0 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="inlineStr">
+      <c r="A128" t="inlineStr">
         <is>
           <t>Tartatea Torteria</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Via XX Settembre, 17</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>351/6271679</t>
         </is>
       </c>
-      <c r="D128" s="1" t="inlineStr"/>
-      <c r="E128" s="1" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>artateatorteria</t>
         </is>
       </c>
-      <c r="F128" s="1" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>tarta.teatorteria</t>
         </is>
       </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H128" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I128" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J128" s="1" t="inlineStr"/>
-      <c r="K128" s="1" t="inlineStr"/>
-      <c r="L128" s="1" t="inlineStr"/>
-      <c r="M128" s="1" t="inlineStr"/>
-      <c r="N128" s="1" t="inlineStr"/>
-      <c r="O128" s="1" t="inlineStr"/>
-      <c r="P128" s="1" t="inlineStr"/>
-      <c r="Q128" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R128" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: trovato (artateatorteria) | IG: non trovato (tarta.teatorteria)</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="inlineStr">
+      <c r="A129" t="inlineStr">
         <is>
           <t>Torteria Olsen</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Via Sant'Agostino, 4/B</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>011/4361573</t>
         </is>
       </c>
-      <c r="D129" s="1" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>www.torteriaolsen.it</t>
         </is>
       </c>
-      <c r="E129" s="1" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>torteriaolsen</t>
         </is>
       </c>
-      <c r="F129" s="1" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>olsentorteria</t>
         </is>
       </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr"/>
-      <c r="K129" s="1" t="inlineStr"/>
-      <c r="L129" s="1" t="inlineStr"/>
-      <c r="M129" s="1" t="inlineStr"/>
-      <c r="N129" s="1" t="inlineStr"/>
-      <c r="O129" s="1" t="inlineStr"/>
-      <c r="P129" s="1" t="inlineStr"/>
-      <c r="Q129" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R129" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': 'Chiuso'}, 'mercoledì': {'o</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (torteriaolsen) | IG: non trovato (olsentorteria)</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>BeR Enoteca</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Via Giambattista Gropello, 21</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>328/0431744</t>
         </is>
       </c>
-      <c r="D130" s="1" t="inlineStr"/>
-      <c r="E130" s="1" t="inlineStr"/>
-      <c r="F130" s="1" t="inlineStr"/>
-      <c r="G130" s="1" t="inlineStr"/>
-      <c r="H130" s="1" t="inlineStr"/>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr"/>
-      <c r="K130" s="1" t="inlineStr"/>
-      <c r="L130" s="1" t="inlineStr"/>
-      <c r="M130" s="1" t="inlineStr"/>
-      <c r="N130" s="1" t="inlineStr"/>
-      <c r="O130" s="1" t="inlineStr"/>
-      <c r="P130" s="1" t="inlineStr"/>
-      <c r="Q130" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R130" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '17:30', 'closes': '23'}, '</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="inlineStr">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Caffè dell'Orologio</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Via Oddino Morgari, 16/A</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>011/2644254</t>
         </is>
       </c>
-      <c r="D131" s="1" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>www.caffedellorologio.net</t>
         </is>
       </c>
-      <c r="E131" s="1" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>caffeorologiotorino</t>
         </is>
       </c>
-      <c r="F131" s="1" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>caffedellorologiotorino</t>
         </is>
       </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H131" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J131" s="1" t="inlineStr"/>
-      <c r="K131" s="1" t="inlineStr"/>
-      <c r="L131" s="1" t="inlineStr"/>
-      <c r="M131" s="1" t="inlineStr"/>
-      <c r="N131" s="1" t="inlineStr"/>
-      <c r="O131" s="1" t="inlineStr"/>
-      <c r="P131" s="1" t="inlineStr"/>
-      <c r="Q131" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R131" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '12:30, 17', 'closes': '14:30, 21:30', 'break': '14:30–17'}</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: trovato (caffeorologiotorino) | IG: non trovato (caffedellorologiotorino)</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
@@ -8047,916 +8068,918 @@
       <c r="P132" s="1" t="inlineStr"/>
       <c r="Q132" s="1" t="inlineStr">
         <is>
-          <t>Non verificato in questa sessione</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: non trovato (cru.torino)</t>
         </is>
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="inlineStr">
+      <c r="A133" t="inlineStr">
         <is>
           <t>La petite cave</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Corso Alcide De Gasperi, 2/b</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>011/595208</t>
         </is>
       </c>
-      <c r="D133" s="1" t="inlineStr"/>
-      <c r="E133" s="1" t="inlineStr"/>
-      <c r="F133" s="1" t="inlineStr"/>
-      <c r="G133" s="1" t="inlineStr"/>
-      <c r="H133" s="1" t="inlineStr"/>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr"/>
-      <c r="K133" s="1" t="inlineStr"/>
-      <c r="L133" s="1" t="inlineStr"/>
-      <c r="M133" s="1" t="inlineStr"/>
-      <c r="N133" s="1" t="inlineStr"/>
-      <c r="O133" s="1" t="inlineStr"/>
-      <c r="P133" s="1" t="inlineStr"/>
-      <c r="Q133" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R133" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="inlineStr">
+      <c r="A134" t="inlineStr">
         <is>
           <t>Orma vini</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Via Sant'Ottavio, 52/D</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>011/0567367</t>
         </is>
       </c>
-      <c r="D134" s="1" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>www.ormabistrot.it</t>
         </is>
       </c>
-      <c r="E134" s="1" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>OrmaVini</t>
         </is>
       </c>
-      <c r="F134" s="1" t="inlineStr"/>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H134" s="1" t="inlineStr"/>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J134" s="1" t="inlineStr"/>
-      <c r="K134" s="1" t="inlineStr"/>
-      <c r="L134" s="1" t="inlineStr"/>
-      <c r="M134" s="1" t="inlineStr"/>
-      <c r="N134" s="1" t="inlineStr"/>
-      <c r="O134" s="1" t="inlineStr"/>
-      <c r="P134" s="1" t="inlineStr"/>
-      <c r="Q134" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R134" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18:30', 'closes': '01'}, 'martedì': {'opens': '18:30', 'cl</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (OrmaVini) | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="inlineStr">
+      <c r="A135" t="inlineStr">
         <is>
           <t>Paltò</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Via della Rocca, 17</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>351/6229996</t>
         </is>
       </c>
-      <c r="D135" s="1" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>www.paltotorino.it</t>
         </is>
       </c>
-      <c r="E135" s="1" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>paltocaffevini</t>
         </is>
       </c>
-      <c r="F135" s="1" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>palto.torino</t>
         </is>
       </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr"/>
-      <c r="K135" s="1" t="inlineStr"/>
-      <c r="L135" s="1" t="inlineStr"/>
-      <c r="M135" s="1" t="inlineStr"/>
-      <c r="N135" s="1" t="inlineStr"/>
-      <c r="O135" s="1" t="inlineStr"/>
-      <c r="P135" s="1" t="inlineStr"/>
-      <c r="Q135" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R135" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '00'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (paltocaffevini) | IG: non trovato (palto.torino)</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="inlineStr">
+      <c r="A136" t="inlineStr">
         <is>
           <t>Piattini - Caffè e Vini</t>
         </is>
       </c>
-      <c r="B136" s="1" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Via Corte d'Appello, 9/A</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>331/3843390</t>
         </is>
       </c>
-      <c r="D136" s="1" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>piattini.eatbu.com</t>
         </is>
       </c>
-      <c r="E136" s="1" t="inlineStr"/>
-      <c r="F136" s="1" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>piattinicaffevini</t>
         </is>
       </c>
-      <c r="G136" s="1" t="inlineStr"/>
-      <c r="H136" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I136" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J136" s="1" t="inlineStr"/>
-      <c r="K136" s="1" t="inlineStr"/>
-      <c r="L136" s="1" t="inlineStr"/>
-      <c r="M136" s="1" t="inlineStr"/>
-      <c r="N136" s="1" t="inlineStr"/>
-      <c r="O136" s="1" t="inlineStr"/>
-      <c r="P136" s="1" t="inlineStr"/>
-      <c r="Q136" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R136" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '23'}, 'martedì': {'opens': '09:30, 18', 'c</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.7 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (piattinicaffevini)</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="inlineStr">
+      <c r="A137" t="inlineStr">
         <is>
           <t>Rossorubino</t>
         </is>
       </c>
-      <c r="B137" s="1" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Via Monferrato, 14</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>011/6502183</t>
         </is>
       </c>
-      <c r="D137" s="1" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>www.rossorubino.net</t>
         </is>
       </c>
-      <c r="E137" s="1" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>rossorubino.enoteca</t>
         </is>
       </c>
-      <c r="F137" s="1" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>rossorubino.enoteca</t>
         </is>
       </c>
-      <c r="G137" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H137" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I137" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J137" s="1" t="inlineStr"/>
-      <c r="K137" s="1" t="inlineStr"/>
-      <c r="L137" s="1" t="inlineStr"/>
-      <c r="M137" s="1" t="inlineStr"/>
-      <c r="N137" s="1" t="inlineStr"/>
-      <c r="O137" s="1" t="inlineStr"/>
-      <c r="P137" s="1" t="inlineStr"/>
-      <c r="Q137" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R137" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10', 'closes': '21'}, 'martedì': {'opens': '10', 'closes':</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: trovato (rossorubino.enoteca) | IG: trovato (rossorubino.enoteca)</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="inlineStr">
+      <c r="A138" t="inlineStr">
         <is>
           <t>Sodo</t>
         </is>
       </c>
-      <c r="B138" s="1" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Via Giambattista Bodoni, 5</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>392/1257116</t>
         </is>
       </c>
-      <c r="D138" s="1" t="inlineStr"/>
-      <c r="E138" s="1" t="inlineStr"/>
-      <c r="F138" s="1" t="inlineStr"/>
-      <c r="G138" s="1" t="inlineStr"/>
-      <c r="H138" s="1" t="inlineStr"/>
-      <c r="I138" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J138" s="1" t="inlineStr"/>
-      <c r="K138" s="1" t="inlineStr"/>
-      <c r="L138" s="1" t="inlineStr"/>
-      <c r="M138" s="1" t="inlineStr"/>
-      <c r="N138" s="1" t="inlineStr"/>
-      <c r="O138" s="1" t="inlineStr"/>
-      <c r="P138" s="1" t="inlineStr"/>
-      <c r="Q138" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R138" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '18', 'closes': '22'}, 'martedì': {'opens': '18', 'closes':</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.3 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="inlineStr">
+      <c r="A139" t="inlineStr">
         <is>
           <t>Tastuma</t>
         </is>
       </c>
-      <c r="B139" s="1" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Via della Consolata, 12</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>011/19887600</t>
         </is>
       </c>
-      <c r="D139" s="1" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>www.tastuma.it</t>
         </is>
       </c>
-      <c r="E139" s="1" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>Tastumacheeseandwinebar</t>
         </is>
       </c>
-      <c r="F139" s="1" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>tastumatorino</t>
         </is>
       </c>
-      <c r="G139" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H139" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I139" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J139" s="1" t="inlineStr"/>
-      <c r="K139" s="1" t="inlineStr"/>
-      <c r="L139" s="1" t="inlineStr"/>
-      <c r="M139" s="1" t="inlineStr"/>
-      <c r="N139" s="1" t="inlineStr"/>
-      <c r="O139" s="1" t="inlineStr"/>
-      <c r="P139" s="1" t="inlineStr"/>
-      <c r="Q139" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R139" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18', 'closes': '00'}, 'mer</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (Tastumacheeseandwinebar) | IG: trovato (tastumatorino)</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="inlineStr">
+      <c r="A140" t="inlineStr">
         <is>
           <t>Tut Vin</t>
         </is>
       </c>
-      <c r="B140" s="1" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Via Borgo Dora, 12/B</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>347/4478959</t>
         </is>
       </c>
-      <c r="D140" s="1" t="inlineStr"/>
-      <c r="E140" s="1" t="inlineStr"/>
-      <c r="F140" s="1" t="inlineStr"/>
-      <c r="G140" s="1" t="inlineStr"/>
-      <c r="H140" s="1" t="inlineStr"/>
-      <c r="I140" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J140" s="1" t="inlineStr"/>
-      <c r="K140" s="1" t="inlineStr"/>
-      <c r="L140" s="1" t="inlineStr"/>
-      <c r="M140" s="1" t="inlineStr"/>
-      <c r="N140" s="1" t="inlineStr"/>
-      <c r="O140" s="1" t="inlineStr"/>
-      <c r="P140" s="1" t="inlineStr"/>
-      <c r="Q140" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R140" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="inlineStr">
+      <c r="A141" t="inlineStr">
         <is>
           <t>51 Manifattura Alimentare</t>
         </is>
       </c>
-      <c r="B141" s="1" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Lungo Dora Firenze, 51/A</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>011/237359</t>
         </is>
       </c>
-      <c r="D141" s="1" t="inlineStr"/>
-      <c r="E141" s="1" t="inlineStr"/>
-      <c r="F141" s="1" t="inlineStr"/>
-      <c r="G141" s="1" t="inlineStr"/>
-      <c r="H141" s="1" t="inlineStr"/>
-      <c r="I141" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J141" s="1" t="inlineStr"/>
-      <c r="K141" s="1" t="inlineStr"/>
-      <c r="L141" s="1" t="inlineStr"/>
-      <c r="M141" s="1" t="inlineStr"/>
-      <c r="N141" s="1" t="inlineStr"/>
-      <c r="O141" s="1" t="inlineStr"/>
-      <c r="P141" s="1" t="inlineStr"/>
-      <c r="Q141" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R141" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '10', 'closes': '15'}, 'martedì': {'opens': '10, 18:30', 'c</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="inlineStr">
+      <c r="A142" t="inlineStr">
         <is>
           <t>Adelaide!</t>
         </is>
       </c>
-      <c r="B142" s="1" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Via Giuseppe Mazzini, 58</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>011/3358459</t>
         </is>
       </c>
-      <c r="D142" s="1" t="inlineStr"/>
-      <c r="E142" s="1" t="inlineStr"/>
-      <c r="F142" s="1" t="inlineStr"/>
-      <c r="G142" s="1" t="inlineStr"/>
-      <c r="H142" s="1" t="inlineStr"/>
-      <c r="I142" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J142" s="1" t="inlineStr"/>
-      <c r="K142" s="1" t="inlineStr"/>
-      <c r="L142" s="1" t="inlineStr"/>
-      <c r="M142" s="1" t="inlineStr"/>
-      <c r="N142" s="1" t="inlineStr"/>
-      <c r="O142" s="1" t="inlineStr"/>
-      <c r="P142" s="1" t="inlineStr"/>
-      <c r="Q142" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R142" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '07', 'closes': '00'}, 'martedì': {'opens': '07', 'closes':</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="inlineStr">
+      <c r="A143" t="inlineStr">
         <is>
           <t>CouCou</t>
         </is>
       </c>
-      <c r="B143" s="1" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Via Carlo Ignazio Giulio, 2/G</t>
         </is>
       </c>
-      <c r="C143" s="1" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>011/18837059</t>
         </is>
       </c>
-      <c r="D143" s="1" t="inlineStr"/>
-      <c r="E143" s="1" t="inlineStr"/>
-      <c r="F143" s="1" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>coucoutorino</t>
         </is>
       </c>
-      <c r="G143" s="1" t="inlineStr"/>
-      <c r="H143" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I143" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J143" s="1" t="inlineStr"/>
-      <c r="K143" s="1" t="inlineStr"/>
-      <c r="L143" s="1" t="inlineStr"/>
-      <c r="M143" s="1" t="inlineStr"/>
-      <c r="N143" s="1" t="inlineStr"/>
-      <c r="O143" s="1" t="inlineStr"/>
-      <c r="P143" s="1" t="inlineStr"/>
-      <c r="Q143" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R143" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '18:30', 'closes': '00'}, '</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.9 ( rec.) | TF: non trovato | FB: nessun handle | IG: trovato (coucoutorino)</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="inlineStr">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Magazzini Oz</t>
         </is>
       </c>
-      <c r="B144" s="1" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Via Giovanni Giolitti, 19/A</t>
         </is>
       </c>
-      <c r="C144" s="1" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>011/0812816</t>
         </is>
       </c>
-      <c r="D144" s="1" t="inlineStr"/>
-      <c r="E144" s="1" t="inlineStr"/>
-      <c r="F144" s="1" t="inlineStr"/>
-      <c r="G144" s="1" t="inlineStr"/>
-      <c r="H144" s="1" t="inlineStr"/>
-      <c r="I144" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J144" s="1" t="inlineStr"/>
-      <c r="K144" s="1" t="inlineStr"/>
-      <c r="L144" s="1" t="inlineStr"/>
-      <c r="M144" s="1" t="inlineStr"/>
-      <c r="N144" s="1" t="inlineStr"/>
-      <c r="O144" s="1" t="inlineStr"/>
-      <c r="P144" s="1" t="inlineStr"/>
-      <c r="Q144" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R144" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': '08:30', 'closes': '15'}, 'martedì': {'opens': '08:30', 'cl</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="inlineStr">
+      <c r="A145" t="inlineStr">
         <is>
           <t>Muro - osteria contemporanea</t>
         </is>
       </c>
-      <c r="B145" s="1" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Via Cigna, 114/E</t>
         </is>
       </c>
-      <c r="C145" s="1" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>375/7700654</t>
         </is>
       </c>
-      <c r="D145" s="1" t="inlineStr"/>
-      <c r="E145" s="1" t="inlineStr"/>
-      <c r="F145" s="1" t="inlineStr"/>
-      <c r="G145" s="1" t="inlineStr"/>
-      <c r="H145" s="1" t="inlineStr"/>
-      <c r="I145" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J145" s="1" t="inlineStr"/>
-      <c r="K145" s="1" t="inlineStr"/>
-      <c r="L145" s="1" t="inlineStr"/>
-      <c r="M145" s="1" t="inlineStr"/>
-      <c r="N145" s="1" t="inlineStr"/>
-      <c r="O145" s="1" t="inlineStr"/>
-      <c r="P145" s="1" t="inlineStr"/>
-      <c r="Q145" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R145" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '12', 'closes': '15'}, 'mer</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="inlineStr">
+      <c r="A146" t="inlineStr">
         <is>
           <t>Rabarè</t>
         </is>
       </c>
-      <c r="B146" s="1" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Via Maria Vittoria, 58/H</t>
         </is>
       </c>
-      <c r="C146" s="1" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>366/1443776</t>
         </is>
       </c>
-      <c r="D146" s="1" t="inlineStr"/>
-      <c r="E146" s="1" t="inlineStr"/>
-      <c r="F146" s="1" t="inlineStr"/>
-      <c r="G146" s="1" t="inlineStr"/>
-      <c r="H146" s="1" t="inlineStr"/>
-      <c r="I146" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J146" s="1" t="inlineStr"/>
-      <c r="K146" s="1" t="inlineStr"/>
-      <c r="L146" s="1" t="inlineStr"/>
-      <c r="M146" s="1" t="inlineStr"/>
-      <c r="N146" s="1" t="inlineStr"/>
-      <c r="O146" s="1" t="inlineStr"/>
-      <c r="P146" s="1" t="inlineStr"/>
-      <c r="Q146" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R146" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': '19', 'closes': '00'}, 'mer</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.8 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="inlineStr">
+      <c r="A147" t="inlineStr">
         <is>
           <t>Recina - focaccia e cucina</t>
         </is>
       </c>
-      <c r="B147" s="1" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Via della Misericordia, 4/F</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>011/6997385</t>
         </is>
       </c>
-      <c r="D147" s="1" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>www.gaudenziovinoecucina.it/recina</t>
         </is>
       </c>
-      <c r="E147" s="1" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>recinafocacciaecucina</t>
         </is>
       </c>
-      <c r="F147" s="1" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>recina-focaccia-e-cucina</t>
         </is>
       </c>
-      <c r="G147" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="H147" s="1" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="I147" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J147" s="1" t="inlineStr"/>
-      <c r="K147" s="1" t="inlineStr"/>
-      <c r="L147" s="1" t="inlineStr"/>
-      <c r="M147" s="1" t="inlineStr"/>
-      <c r="N147" s="1" t="inlineStr"/>
-      <c r="O147" s="1" t="inlineStr"/>
-      <c r="P147" s="1" t="inlineStr"/>
-      <c r="Q147" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R147" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: trovato (recinafocacciaecucina) | IG: trovato (recina-focaccia-e-cucina)</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="inlineStr">
+      <c r="A148" t="inlineStr">
         <is>
           <t>Sciarada</t>
         </is>
       </c>
-      <c r="B148" s="1" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Via Claudio Luigi Berthollet, 20/D</t>
         </is>
       </c>
-      <c r="C148" s="1" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>340/9599722</t>
         </is>
       </c>
-      <c r="D148" s="1" t="inlineStr"/>
-      <c r="E148" s="1" t="inlineStr"/>
-      <c r="F148" s="1" t="inlineStr"/>
-      <c r="G148" s="1" t="inlineStr"/>
-      <c r="H148" s="1" t="inlineStr"/>
-      <c r="I148" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J148" s="1" t="inlineStr"/>
-      <c r="K148" s="1" t="inlineStr"/>
-      <c r="L148" s="1" t="inlineStr"/>
-      <c r="M148" s="1" t="inlineStr"/>
-      <c r="N148" s="1" t="inlineStr"/>
-      <c r="O148" s="1" t="inlineStr"/>
-      <c r="P148" s="1" t="inlineStr"/>
-      <c r="Q148" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R148" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>{'lunedì': {'opens': 'Chiuso'}, 'martedì': {'opens': 'Chiuso'}, 'mercoledì': {'o</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.6 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="inlineStr">
+      <c r="A149" t="inlineStr">
         <is>
           <t>Bar Cavour</t>
         </is>
       </c>
-      <c r="B149" s="1" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>Piazza Carignano, 2</t>
         </is>
       </c>
-      <c r="C149" s="1" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>011/19211270</t>
         </is>
       </c>
-      <c r="D149" s="1" t="inlineStr"/>
-      <c r="E149" s="1" t="inlineStr"/>
-      <c r="F149" s="1" t="inlineStr"/>
-      <c r="G149" s="1" t="inlineStr"/>
-      <c r="H149" s="1" t="inlineStr"/>
-      <c r="I149" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J149" s="1" t="inlineStr"/>
-      <c r="K149" s="1" t="inlineStr"/>
-      <c r="L149" s="1" t="inlineStr"/>
-      <c r="M149" s="1" t="inlineStr"/>
-      <c r="N149" s="1" t="inlineStr"/>
-      <c r="O149" s="1" t="inlineStr"/>
-      <c r="P149" s="1" t="inlineStr"/>
-      <c r="Q149" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R149" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.4 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="inlineStr">
+      <c r="A150" t="inlineStr">
         <is>
           <t>Barz8</t>
         </is>
       </c>
-      <c r="B150" s="1" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>Corso Moncalieri, 5/A</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>349/3175425</t>
         </is>
       </c>
-      <c r="D150" s="1" t="inlineStr"/>
-      <c r="E150" s="1" t="inlineStr"/>
-      <c r="F150" s="1" t="inlineStr"/>
-      <c r="G150" s="1" t="inlineStr"/>
-      <c r="H150" s="1" t="inlineStr"/>
-      <c r="I150" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J150" s="1" t="inlineStr"/>
-      <c r="K150" s="1" t="inlineStr"/>
-      <c r="L150" s="1" t="inlineStr"/>
-      <c r="M150" s="1" t="inlineStr"/>
-      <c r="N150" s="1" t="inlineStr"/>
-      <c r="O150" s="1" t="inlineStr"/>
-      <c r="P150" s="1" t="inlineStr"/>
-      <c r="Q150" s="1" t="inlineStr">
-        <is>
-          <t>Non verificato in questa sessione</t>
-        </is>
-      </c>
-      <c r="R150" s="1" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Rating Google: 4.5 ( rec.) | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
         </is>
       </c>
     </row>
